--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -1260,7 +1260,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.78932113852</v>
+        <v>46224.81394085352</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.59</v>
+        <v>1.632</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>2358.79</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.181</v>
+        <v>1.175</v>
       </c>
       <c r="H9" s="91" t="n">
         <v>555.83</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>1.147</v>
+        <v>1.157</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>284.57</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.696</v>
+        <v>0.725</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>2258.51</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.576</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>1565.38</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.54</v>
+        <v>0.547</v>
       </c>
       <c r="H13" s="91" t="n">
         <v>1892.54</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.453</v>
+        <v>0.451</v>
       </c>
       <c r="H14" s="90" t="n">
         <v>53011.04</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="H15" s="91" t="n">
         <v>2385.76</v>
@@ -1739,33 +1739,33 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>K-Bro Linen Inc.</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.398</v>
+        <v>0.377</v>
       </c>
       <c r="H16" s="91" t="n">
-        <v>681.6799999999999</v>
+        <v>390.27</v>
       </c>
       <c r="I16" s="54" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
       <c r="J16" s="28" t="n"/>
@@ -1777,33 +1777,33 @@
       </c>
       <c r="C17" s="38" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>BMO</t>
         </is>
       </c>
       <c r="D17" s="39" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc.</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="E17" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="40" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.373</v>
+        <v>0.357</v>
       </c>
       <c r="H17" s="90" t="n">
-        <v>390.27</v>
+        <v>116001.23</v>
       </c>
       <c r="I17" s="53" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
         </is>
       </c>
       <c r="J17" s="36" t="n"/>
@@ -1815,33 +1815,33 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D18" s="31" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc.</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.348</v>
+        <v>0.341</v>
       </c>
       <c r="H18" s="91" t="n">
-        <v>41467.31</v>
+        <v>681.6799999999999</v>
       </c>
       <c r="I18" s="54" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
       <c r="J18" s="28" t="n"/>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C19" s="38" t="inlineStr">
         <is>
-          <t>BMO</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="D19" s="39" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Power Corporation of Canada</t>
         </is>
       </c>
       <c r="E19" s="40" t="inlineStr">
@@ -1868,18 +1868,18 @@
       </c>
       <c r="F19" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.341</v>
+        <v>0.337</v>
       </c>
       <c r="H19" s="90" t="n">
-        <v>116001.23</v>
+        <v>38174.66</v>
       </c>
       <c r="I19" s="53" t="inlineStr">
         <is>
-          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
         </is>
       </c>
       <c r="J19" s="36" t="n"/>
@@ -1891,33 +1891,33 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="D20" s="31" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation</t>
+          <t>Sun Life Financial Inc.</t>
         </is>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="H20" s="91" t="n">
-        <v>28518.97</v>
+        <v>41467.31</v>
       </c>
       <c r="I20" s="54" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
       <c r="J20" s="28" t="n"/>
@@ -1929,33 +1929,33 @@
       </c>
       <c r="C21" s="38" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="D21" s="39" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada</t>
+          <t>Canadian National Railway Company</t>
         </is>
       </c>
       <c r="E21" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="H21" s="90" t="n">
-        <v>38174.66</v>
+        <v>72839.50999999999</v>
       </c>
       <c r="I21" s="53" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
       <c r="J21" s="36" t="n"/>
@@ -2043,33 +2043,33 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>EQB</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company</t>
+          <t>EQB Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.318</v>
+        <v>0.314</v>
       </c>
       <c r="H24" s="90" t="n">
-        <v>72839.50999999999</v>
+        <v>3018.47</v>
       </c>
       <c r="I24" s="53" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
+          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
         </is>
       </c>
       <c r="J24" s="36" t="n"/>
@@ -2081,33 +2081,33 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited</t>
+          <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.301</v>
+        <v>0.31</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>79823.21000000001</v>
+        <v>28518.97</v>
       </c>
       <c r="I25" s="54" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="J25" s="28" t="n"/>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>EQB</t>
+          <t>IGM</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>EQB Inc.</t>
+          <t>IGM Financial Inc.</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
@@ -2134,18 +2134,18 @@
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.3</v>
+        <v>0.305</v>
       </c>
       <c r="H26" s="90" t="n">
-        <v>3018.47</v>
+        <v>13303.41</v>
       </c>
       <c r="I26" s="53" t="inlineStr">
         <is>
-          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
+          <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
         </is>
       </c>
       <c r="J26" s="36" t="n"/>
@@ -2157,33 +2157,33 @@
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="D27" s="39" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Canadian Pacific Kansas City Limited</t>
         </is>
       </c>
       <c r="E27" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
         <v>0.298</v>
       </c>
       <c r="H27" s="90" t="n">
-        <v>275998.42</v>
+        <v>79823.21000000001</v>
       </c>
       <c r="I27" s="53" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
       <c r="J27" s="36" t="n"/>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="D28" s="31" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E28" s="32" t="inlineStr">
@@ -2210,18 +2210,18 @@
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.286</v>
+        <v>0.295</v>
       </c>
       <c r="H28" s="91" t="n">
-        <v>976.67</v>
+        <v>275998.42</v>
       </c>
       <c r="I28" s="54" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
       <c r="J28" s="28" t="n"/>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="C29" s="38" t="inlineStr">
         <is>
-          <t>IGM</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D29" s="39" t="inlineStr">
         <is>
-          <t>IGM Financial Inc.</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E29" s="40" t="inlineStr">
@@ -2252,14 +2252,14 @@
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.278</v>
+        <v>0.269</v>
       </c>
       <c r="H29" s="90" t="n">
-        <v>13303.41</v>
+        <v>976.67</v>
       </c>
       <c r="I29" s="53" t="inlineStr">
         <is>
-          <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
         </is>
       </c>
       <c r="J29" s="36" t="n"/>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.272</v>
+        <v>0.264</v>
       </c>
       <c r="H30" s="90" t="n">
         <v>10045.65</v>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>BDGI</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>Badger Infrastructure Solutions Ltd.</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
@@ -2324,18 +2324,18 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Construction and Engineering</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.231</v>
+        <v>0.252</v>
       </c>
       <c r="H31" s="91" t="n">
-        <v>576.85</v>
+        <v>2215.94</v>
       </c>
       <c r="I31" s="54" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
       </c>
       <c r="J31" s="28" t="n"/>
@@ -2347,33 +2347,33 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.226</v>
+        <v>0.234</v>
       </c>
       <c r="H32" s="90" t="n">
-        <v>100391.39</v>
+        <v>576.85</v>
       </c>
       <c r="I32" s="53" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J32" s="36" t="n"/>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.225</v>
+        <v>0.234</v>
       </c>
       <c r="H33" s="91" t="n">
         <v>11282.66</v>
@@ -2423,33 +2423,33 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.221</v>
+        <v>0.223</v>
       </c>
       <c r="H34" s="90" t="n">
-        <v>927.72</v>
+        <v>100391.39</v>
       </c>
       <c r="I34" s="53" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="J34" s="36" t="n"/>
@@ -2461,33 +2461,33 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Black Diamond Group Limited</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.215</v>
+        <v>0.217</v>
       </c>
       <c r="H35" s="91" t="n">
-        <v>65572.44</v>
+        <v>927.72</v>
       </c>
       <c r="I35" s="54" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
       <c r="J35" s="28" t="n"/>
@@ -2499,33 +2499,33 @@
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
-          <t>BDGI</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D36" s="39" t="inlineStr">
         <is>
-          <t>Badger Infrastructure Solutions Ltd.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>Construction and Engineering</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.204</v>
+        <v>0.215</v>
       </c>
       <c r="H36" s="90" t="n">
-        <v>2215.94</v>
+        <v>65572.44</v>
       </c>
       <c r="I36" s="53" t="inlineStr">
         <is>
-          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J36" s="36" t="n"/>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.2</v>
+        <v>0.191</v>
       </c>
       <c r="H37" s="91" t="n">
         <v>501.72</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.184</v>
+        <v>0.178</v>
       </c>
       <c r="H38" s="90" t="n">
         <v>1330.28</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.155</v>
+        <v>0.14</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>676.4400000000001</v>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="G40" s="89" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="H40" s="90" t="n">
         <v>6226.62</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.174</v>
+        <v>1.192</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>12725.72</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.859</v>
+        <v>0.899</v>
       </c>
       <c r="H9" s="91" t="n">
         <v>213908.98</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.834</v>
+        <v>0.833</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>77721.12</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.697</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>77190.64999999999</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.45</v>
+        <v>0.477</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>44725.83</v>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>J.B. Hunt Transport Services Inc.</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
@@ -4148,14 +4148,14 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.408</v>
+        <v>0.418</v>
       </c>
       <c r="H13" s="91" t="n">
-        <v>86617.14</v>
+        <v>26566.73</v>
       </c>
       <c r="I13" s="54" t="inlineStr">
         <is>
-          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+          <t>J</t>
         </is>
       </c>
       <c r="J13" s="28" t="n"/>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Services Inc.</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E14" s="40" t="inlineStr">
@@ -4186,14 +4186,14 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.393</v>
+        <v>0.375</v>
       </c>
       <c r="H14" s="90" t="n">
-        <v>26566.73</v>
+        <v>86617.14</v>
       </c>
       <c r="I14" s="53" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
       <c r="J14" s="36" t="n"/>
@@ -4205,33 +4205,33 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>Globe Life Inc.</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="H15" s="91" t="n">
-        <v>148209.56</v>
+        <v>12644.53</v>
       </c>
       <c r="I15" s="54" t="inlineStr">
         <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
       <c r="J15" s="28" t="n"/>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc.</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
@@ -4258,18 +4258,18 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.339</v>
+        <v>0.351</v>
       </c>
       <c r="H16" s="90" t="n">
-        <v>64533.41</v>
+        <v>96186.41</v>
       </c>
       <c r="I16" s="53" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J16" s="36" t="n"/>
@@ -4281,33 +4281,33 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Globe Life Inc.</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.338</v>
+        <v>0.348</v>
       </c>
       <c r="H17" s="91" t="n">
-        <v>12644.53</v>
+        <v>148209.56</v>
       </c>
       <c r="I17" s="54" t="inlineStr">
         <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J17" s="28" t="n"/>
@@ -4319,33 +4319,33 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>The Travelers Companies Inc.</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="H18" s="90" t="n">
-        <v>125211.85</v>
+        <v>64533.41</v>
       </c>
       <c r="I18" s="53" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J18" s="36" t="n"/>
@@ -4357,33 +4357,33 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.33</v>
+        <v>0.339</v>
       </c>
       <c r="H19" s="91" t="n">
-        <v>96186.41</v>
+        <v>125211.85</v>
       </c>
       <c r="I19" s="54" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J19" s="28" t="n"/>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="H20" s="90" t="n">
         <v>4309578.68</v>
@@ -4433,33 +4433,33 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.305</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="91" t="n">
-        <v>39380.19</v>
+        <v>16078.79</v>
       </c>
       <c r="I21" s="54" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J21" s="28" t="n"/>
@@ -4471,33 +4471,33 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.305</v>
+        <v>0.298</v>
       </c>
       <c r="H22" s="90" t="n">
-        <v>14353.95</v>
+        <v>158667.48</v>
       </c>
       <c r="I22" s="53" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J22" s="36" t="n"/>
@@ -4509,33 +4509,33 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>Archer-Daniels-Midland Company</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.299</v>
+        <v>0.295</v>
       </c>
       <c r="H23" s="91" t="n">
-        <v>16078.79</v>
+        <v>39380.19</v>
       </c>
       <c r="I23" s="54" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>W.W. Grainger Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
@@ -4562,18 +4562,18 @@
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.288</v>
+        <v>0.294</v>
       </c>
       <c r="H24" s="90" t="n">
-        <v>158667.48</v>
+        <v>62147.38</v>
       </c>
       <c r="I24" s="53" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J24" s="36" t="n"/>
@@ -4585,33 +4585,33 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>W.W. Grainger Inc.</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>62147.38</v>
+        <v>14353.95</v>
       </c>
       <c r="I25" s="54" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
       <c r="J25" s="28" t="n"/>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Northern Trust Corporation</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
@@ -4638,18 +4638,18 @@
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.23</v>
+        <v>0.257</v>
       </c>
       <c r="H26" s="90" t="n">
-        <v>55851.6</v>
+        <v>30713.22</v>
       </c>
       <c r="I26" s="53" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
         </is>
       </c>
       <c r="J26" s="36" t="n"/>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Block Inc.</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
@@ -4676,18 +4676,18 @@
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.23</v>
+        <v>0.248</v>
       </c>
       <c r="H27" s="91" t="n">
-        <v>40474.89</v>
+        <v>55851.6</v>
       </c>
       <c r="I27" s="54" t="inlineStr">
         <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J27" s="28" t="n"/>
@@ -4699,12 +4699,12 @@
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation</t>
+          <t>Principal Financial Group Inc.</t>
         </is>
       </c>
       <c r="E28" s="40" t="inlineStr">
@@ -4714,18 +4714,18 @@
       </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
         <v>0.219</v>
       </c>
       <c r="H28" s="90" t="n">
-        <v>30713.22</v>
+        <v>23624.19</v>
       </c>
       <c r="I28" s="53" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
       <c r="J28" s="36" t="n"/>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc.</t>
+          <t>Block Inc.</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
@@ -4752,18 +4752,18 @@
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.209</v>
+        <v>0.202</v>
       </c>
       <c r="H29" s="91" t="n">
-        <v>23624.19</v>
+        <v>40474.89</v>
       </c>
       <c r="I29" s="54" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J29" s="28" t="n"/>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>Everest Group Ltd.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
@@ -4790,18 +4790,18 @@
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.185</v>
+        <v>0.197</v>
       </c>
       <c r="H30" s="90" t="n">
-        <v>13320.91</v>
+        <v>388502.86</v>
       </c>
       <c r="I30" s="53" t="inlineStr">
         <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
       <c r="J30" s="36" t="n"/>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>The Goldman Sachs Group Inc.</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
@@ -4828,18 +4828,18 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.181</v>
+        <v>0.19</v>
       </c>
       <c r="H31" s="91" t="n">
-        <v>388502.86</v>
+        <v>308648.81</v>
       </c>
       <c r="I31" s="54" t="inlineStr">
         <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
         </is>
       </c>
       <c r="J31" s="28" t="n"/>
@@ -4851,33 +4851,33 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Everest Group Ltd.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.176</v>
+        <v>0.182</v>
       </c>
       <c r="H32" s="90" t="n">
-        <v>89144.46000000001</v>
+        <v>13320.91</v>
       </c>
       <c r="I32" s="53" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J32" s="36" t="n"/>
@@ -4889,33 +4889,33 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.148</v>
+        <v>0.159</v>
       </c>
       <c r="H33" s="91" t="n">
-        <v>47955.66</v>
+        <v>89144.46000000001</v>
       </c>
       <c r="I33" s="54" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
       <c r="J33" s="28" t="n"/>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group Inc.</t>
+          <t>Citizens Financial Group Inc.</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
@@ -4942,18 +4942,18 @@
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.145</v>
+        <v>0.158</v>
       </c>
       <c r="H34" s="90" t="n">
-        <v>308648.81</v>
+        <v>27585.86</v>
       </c>
       <c r="I34" s="53" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
       <c r="J34" s="36" t="n"/>
@@ -4965,12 +4965,12 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc.</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
@@ -4984,14 +4984,14 @@
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.131</v>
+        <v>0.152</v>
       </c>
       <c r="H35" s="91" t="n">
-        <v>27585.86</v>
+        <v>47955.66</v>
       </c>
       <c r="I35" s="54" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
       <c r="J35" s="28" t="n"/>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H36" s="90" t="n">
         <v>21453.67</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.119</v>
+        <v>0.129</v>
       </c>
       <c r="H37" s="91" t="n">
         <v>36717.82</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>36258.68</v>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="G40" s="89" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="H40" s="90" t="n">
         <v>11826.25</v>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1260,7 +1260,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.81394085352</v>
+        <v>46224.8272040635</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1282,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.632</v>
+        <v>1.631</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>2358.79</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>1.157</v>
+        <v>1.153</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>284.57</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.725</v>
+        <v>0.732</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>2258.51</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>1565.38</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.547</v>
+        <v>0.544</v>
       </c>
       <c r="H13" s="91" t="n">
         <v>1892.54</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.451</v>
+        <v>0.456</v>
       </c>
       <c r="H14" s="90" t="n">
         <v>53011.04</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.437</v>
+        <v>0.443</v>
       </c>
       <c r="H15" s="91" t="n">
         <v>2385.76</v>
@@ -1734,36 +1734,36 @@
     </row>
     <row r="16" ht="20.4" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="48" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>KBL</t>
         </is>
       </c>
-      <c r="D16" s="31" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>K-Bro Linen Inc.</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="H16" s="91" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="H16" s="90" t="n">
         <v>390.27</v>
       </c>
-      <c r="I16" s="54" t="inlineStr">
+      <c r="I16" s="53" t="inlineStr">
         <is>
           <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
@@ -1772,36 +1772,36 @@
     </row>
     <row r="17" ht="40.8" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="48" t="n">
+      <c r="B17" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>BMO</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>Bank of Montreal</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F17" s="40" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="H17" s="90" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H17" s="91" t="n">
         <v>116001.23</v>
       </c>
-      <c r="I17" s="53" t="inlineStr">
+      <c r="I17" s="54" t="inlineStr">
         <is>
           <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
         </is>
@@ -1810,36 +1810,36 @@
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>ARG</t>
         </is>
       </c>
-      <c r="D18" s="31" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="40" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="H18" s="91" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H18" s="90" t="n">
         <v>681.6799999999999</v>
       </c>
-      <c r="I18" s="54" t="inlineStr">
+      <c r="I18" s="53" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
@@ -1848,36 +1848,36 @@
     </row>
     <row r="19" ht="30.6" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="48" t="n">
+      <c r="B19" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>POW</t>
         </is>
       </c>
-      <c r="D19" s="39" t="inlineStr">
+      <c r="D19" s="31" t="inlineStr">
         <is>
           <t>Power Corporation of Canada</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="H19" s="90" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H19" s="91" t="n">
         <v>38174.66</v>
       </c>
-      <c r="I19" s="53" t="inlineStr">
+      <c r="I19" s="54" t="inlineStr">
         <is>
           <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
         </is>
@@ -1886,36 +1886,36 @@
     </row>
     <row r="20" ht="30.6" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="48" t="n">
         <v>13</v>
       </c>
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>SLF</t>
         </is>
       </c>
-      <c r="D20" s="31" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc.</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="40" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H20" s="91" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="H20" s="90" t="n">
         <v>41467.31</v>
       </c>
-      <c r="I20" s="54" t="inlineStr">
+      <c r="I20" s="53" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
@@ -1924,36 +1924,36 @@
     </row>
     <row r="21" ht="30.6" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="48" t="n">
+      <c r="B21" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>CNR</t>
         </is>
       </c>
-      <c r="D21" s="39" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>Canadian National Railway Company</t>
         </is>
       </c>
-      <c r="E21" s="40" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F21" s="40" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="H21" s="90" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="H21" s="91" t="n">
         <v>72839.50999999999</v>
       </c>
-      <c r="I21" s="53" t="inlineStr">
+      <c r="I21" s="54" t="inlineStr">
         <is>
           <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
@@ -1962,38 +1962,38 @@
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="48" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="30" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="H22" s="91" t="n">
-        <v>189567.97</v>
-      </c>
-      <c r="I22" s="54" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
+        <v>0.324</v>
+      </c>
+      <c r="H22" s="90" t="n">
+        <v>101497.85</v>
+      </c>
+      <c r="I22" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J22" s="28" t="n"/>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
@@ -2024,14 +2024,14 @@
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.32</v>
+        <v>0.324</v>
       </c>
       <c r="H23" s="91" t="n">
-        <v>101497.85</v>
+        <v>189567.97</v>
       </c>
       <c r="I23" s="54" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
+          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.314</v>
+        <v>0.317</v>
       </c>
       <c r="H24" s="90" t="n">
         <v>3018.47</v>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.305</v>
+        <v>0.309</v>
       </c>
       <c r="H26" s="90" t="n">
         <v>13303.41</v>
@@ -2152,112 +2152,112 @@
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="48" t="n">
+      <c r="B27" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="C27" s="38" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="D27" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited</t>
-        </is>
-      </c>
-      <c r="E27" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F27" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Royal Bank of Canada</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
         <v>0.298</v>
       </c>
-      <c r="H27" s="90" t="n">
-        <v>79823.21000000001</v>
-      </c>
-      <c r="I27" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+      <c r="H27" s="91" t="n">
+        <v>275998.42</v>
+      </c>
+      <c r="I27" s="54" t="inlineStr">
+        <is>
+          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
       <c r="J27" s="36" t="n"/>
     </row>
     <row r="28" ht="20.4" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="49" t="n">
+      <c r="B28" s="48" t="n">
         <v>21</v>
       </c>
-      <c r="C28" s="30" t="inlineStr">
-        <is>
-          <t>RY</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>Royal Bank of Canada</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F28" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H28" s="91" t="n">
-        <v>275998.42</v>
-      </c>
-      <c r="I28" s="54" t="inlineStr">
-        <is>
-          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
+        <v>0.296</v>
+      </c>
+      <c r="H28" s="90" t="n">
+        <v>79823.21000000001</v>
+      </c>
+      <c r="I28" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
       <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="48" t="n">
+      <c r="B29" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="D29" s="39" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
-      <c r="E29" s="40" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F29" s="40" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="H29" s="90" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="H29" s="91" t="n">
         <v>976.67</v>
       </c>
-      <c r="I29" s="53" t="inlineStr">
+      <c r="I29" s="54" t="inlineStr">
         <is>
           <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
         </is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.264</v>
+        <v>0.265</v>
       </c>
       <c r="H30" s="90" t="n">
         <v>10045.65</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.252</v>
+        <v>0.257</v>
       </c>
       <c r="H31" s="91" t="n">
         <v>2215.94</v>
@@ -2347,33 +2347,33 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="H32" s="90" t="n">
-        <v>576.85</v>
+        <v>11282.66</v>
       </c>
       <c r="I32" s="53" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="J32" s="36" t="n"/>
@@ -2385,33 +2385,33 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc.</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="H33" s="91" t="n">
-        <v>11282.66</v>
+        <v>576.85</v>
       </c>
       <c r="I33" s="54" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J33" s="28" t="n"/>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.223</v>
+        <v>0.227</v>
       </c>
       <c r="H34" s="90" t="n">
         <v>100391.39</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.217</v>
+        <v>0.219</v>
       </c>
       <c r="H35" s="91" t="n">
         <v>927.72</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.191</v>
+        <v>0.201</v>
       </c>
       <c r="H37" s="91" t="n">
         <v>501.72</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.178</v>
+        <v>0.174</v>
       </c>
       <c r="H38" s="90" t="n">
         <v>1330.28</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>676.4400000000001</v>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="G40" s="89" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="H40" s="90" t="n">
         <v>6226.62</v>
@@ -2684,170 +2684,228 @@
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="69" t="n">
-        <v>34</v>
-      </c>
-      <c r="C41" s="70" t="inlineStr">
-        <is>
-          <t>ASCU</t>
-        </is>
-      </c>
-      <c r="D41" s="71" t="inlineStr">
-        <is>
-          <t>Arizona Sonoran Copper Company Inc.</t>
-        </is>
-      </c>
-      <c r="E41" s="72" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F41" s="72" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G41" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="93" t="n">
-        <v>1264.79</v>
-      </c>
-      <c r="I41" s="74" t="inlineStr">
-        <is>
-          <t>Arizona Sonoran Copper Company Inc engages in the identification acquisition exploration and development of base metal properties</t>
-        </is>
-      </c>
+      <c r="B41" s="49" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="89" t="n"/>
+      <c r="H41" s="91" t="n"/>
+      <c r="I41" s="54" t="n"/>
       <c r="J41" s="68" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="26.4" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="C42" s="43" t="inlineStr">
-        <is>
-          <t>RUP</t>
-        </is>
-      </c>
-      <c r="D42" s="43" t="inlineStr">
-        <is>
-          <t>Rupert Resources Ltd.</t>
-        </is>
-      </c>
-      <c r="E42" s="43" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F42" s="43" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G42" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="43" t="n">
-        <v>1488.84</v>
-      </c>
-      <c r="I42" s="43" t="inlineStr">
-        <is>
-          <t>Rupert Resources Ltd together with its subsidiaries engages in the acquisition and exploration of mineral properties in Finland</t>
-        </is>
-      </c>
+      <c r="B42" s="48" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="90" t="n"/>
+      <c r="I42" s="53" t="n"/>
       <c r="J42" s="43" t="n"/>
     </row>
-    <row r="43" ht="15.6" customHeight="1" thickBot="1">
+    <row r="43" ht="26.4" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="91" t="n"/>
+      <c r="I43" s="54" t="n"/>
       <c r="J43" s="43" t="n"/>
     </row>
-    <row r="44" ht="12" customHeight="1">
+    <row r="44" ht="26.4" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="58" t="n"/>
-      <c r="C44" s="59" t="n"/>
-      <c r="D44" s="59" t="n"/>
-      <c r="E44" s="59" t="n"/>
-      <c r="F44" s="59" t="n"/>
-      <c r="G44" s="59" t="n"/>
-      <c r="H44" s="59" t="n"/>
-      <c r="I44" s="60" t="n"/>
+      <c r="B44" s="48" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="40" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="89" t="n"/>
+      <c r="H44" s="90" t="n"/>
+      <c r="I44" s="53" t="n"/>
       <c r="J44" s="43" t="n"/>
     </row>
-    <row r="45" ht="15.6" customHeight="1">
+    <row r="45" ht="26.4" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="67" t="n"/>
-      <c r="C45" s="64" t="n"/>
-      <c r="D45" s="66" t="n"/>
-      <c r="E45" s="64" t="n"/>
-      <c r="F45" s="64" t="n"/>
-      <c r="G45" s="64" t="n"/>
-      <c r="H45" s="64" t="n"/>
-      <c r="I45" s="65" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="89" t="n"/>
+      <c r="H45" s="91" t="n"/>
+      <c r="I45" s="54" t="n"/>
       <c r="J45" s="43" t="n"/>
     </row>
-    <row r="46" ht="9.6" customHeight="1" thickBot="1">
+    <row r="46" ht="26.4" customHeight="1" thickBot="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="61" t="n"/>
-      <c r="C46" s="62" t="n"/>
-      <c r="D46" s="62" t="n"/>
-      <c r="E46" s="62" t="n"/>
-      <c r="F46" s="62" t="n"/>
-      <c r="G46" s="62" t="n"/>
-      <c r="H46" s="62" t="n"/>
-      <c r="I46" s="63" t="n"/>
+      <c r="B46" s="48" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="40" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="90" t="n"/>
+      <c r="I46" s="53" t="n"/>
       <c r="J46" s="43" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="26.4" customHeight="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="43" t="n"/>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
-      <c r="F47" s="43" t="n"/>
-      <c r="G47" s="43" t="n"/>
-      <c r="H47" s="43" t="n"/>
-      <c r="I47" s="43" t="n"/>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="91" t="n"/>
+      <c r="I47" s="54" t="n"/>
       <c r="J47" s="43" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="26.4" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="47" t="n"/>
-      <c r="C48" s="47" t="n"/>
-      <c r="D48" s="47" t="n"/>
-      <c r="E48" s="47" t="n"/>
-      <c r="F48" s="47" t="n"/>
-      <c r="G48" s="47" t="n"/>
-      <c r="H48" s="47" t="n"/>
-      <c r="I48" s="47" t="n"/>
+      <c r="B48" s="48" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="90" t="n"/>
+      <c r="I48" s="53" t="n"/>
       <c r="J48" s="43" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="26.4" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="43" t="n"/>
-      <c r="C49" s="43" t="n"/>
-      <c r="D49" s="43" t="n"/>
-      <c r="E49" s="43" t="n"/>
-      <c r="F49" s="43" t="n"/>
-      <c r="G49" s="43" t="n"/>
-      <c r="H49" s="43" t="n"/>
-      <c r="I49" s="43" t="n"/>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="89" t="n"/>
+      <c r="H49" s="91" t="n"/>
+      <c r="I49" s="54" t="n"/>
       <c r="J49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="26.4" customHeight="1">
+      <c r="B50" s="48" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="40" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="89" t="n"/>
+      <c r="H50" s="90" t="n"/>
+      <c r="I50" s="53" t="n"/>
+    </row>
+    <row r="51" ht="26.4" customHeight="1">
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="89" t="n"/>
+      <c r="H51" s="91" t="n"/>
+      <c r="I51" s="54" t="n"/>
+    </row>
+    <row r="52" ht="26.4" customHeight="1">
+      <c r="B52" s="48" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="40" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="89" t="n"/>
+      <c r="H52" s="90" t="n"/>
+      <c r="I52" s="53" t="n"/>
+    </row>
+    <row r="53" ht="26.4" customHeight="1">
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="30" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="89" t="n"/>
+      <c r="H53" s="91" t="n"/>
+      <c r="I53" s="54" t="n"/>
+    </row>
+    <row r="54" ht="26.4" customHeight="1">
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="89" t="n"/>
+      <c r="H54" s="90" t="n"/>
+      <c r="I54" s="53" t="n"/>
+    </row>
+    <row r="55" ht="26.4" customHeight="1">
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="30" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="89" t="n"/>
+      <c r="H55" s="91" t="n"/>
+      <c r="I55" s="54" t="n"/>
+    </row>
+    <row r="56" ht="26.4" customHeight="1">
+      <c r="B56" s="48" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="40" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="89" t="n"/>
+      <c r="H56" s="90" t="n"/>
+      <c r="I56" s="53" t="n"/>
+    </row>
+    <row r="57" ht="26.4" customHeight="1">
+      <c r="B57" s="49" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="89" t="n"/>
+      <c r="H57" s="91" t="n"/>
+      <c r="I57" s="54" t="n"/>
+    </row>
+    <row r="58" ht="26.4" customHeight="1">
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="40" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="89" t="n"/>
+      <c r="H58" s="90" t="n"/>
+      <c r="I58" s="53" t="n"/>
+    </row>
+    <row r="59" ht="26.4" customHeight="1">
+      <c r="B59" s="49" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="89" t="n"/>
+      <c r="H59" s="91" t="n"/>
+      <c r="I59" s="54" t="n"/>
+    </row>
+    <row r="60" ht="26.4" customHeight="1">
+      <c r="B60" s="48" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="89" t="n"/>
+      <c r="H60" s="90" t="n"/>
+      <c r="I60" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G41">
+  <conditionalFormatting sqref="G8:G60">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -3786,7 +3844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -3958,7 +4016,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.192</v>
+        <v>1.193</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>12725.72</v>
@@ -4034,7 +4092,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.833</v>
+        <v>0.839</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>77721.12</v>
@@ -4072,7 +4130,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>77190.64999999999</v>
@@ -4110,7 +4168,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.477</v>
+        <v>0.471</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>44725.83</v>
@@ -4148,7 +4206,7 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="H13" s="91" t="n">
         <v>26566.73</v>
@@ -4186,7 +4244,7 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="H14" s="90" t="n">
         <v>86617.14</v>
@@ -4205,12 +4263,12 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Globe Life Inc.</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
@@ -4220,18 +4278,18 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="H15" s="91" t="n">
-        <v>12644.53</v>
+        <v>96186.41</v>
       </c>
       <c r="I15" s="54" t="inlineStr">
         <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J15" s="28" t="n"/>
@@ -4243,12 +4301,12 @@
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>Globe Life Inc.</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
@@ -4258,18 +4316,18 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.351</v>
+        <v>0.356</v>
       </c>
       <c r="H16" s="90" t="n">
-        <v>96186.41</v>
+        <v>12644.53</v>
       </c>
       <c r="I16" s="53" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
       <c r="J16" s="36" t="n"/>
@@ -4300,7 +4358,7 @@
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="H17" s="91" t="n">
         <v>148209.56</v>
@@ -4319,33 +4377,33 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc.</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="H18" s="90" t="n">
-        <v>64533.41</v>
+        <v>125211.85</v>
       </c>
       <c r="I18" s="53" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J18" s="36" t="n"/>
@@ -4357,33 +4415,33 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>The Travelers Companies Inc.</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="H19" s="91" t="n">
-        <v>125211.85</v>
+        <v>64533.41</v>
       </c>
       <c r="I19" s="54" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J19" s="28" t="n"/>
@@ -4452,7 +4510,7 @@
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.3</v>
+        <v>0.307</v>
       </c>
       <c r="H21" s="91" t="n">
         <v>16078.79</v>
@@ -4471,33 +4529,33 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Archer-Daniels-Midland Company</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.298</v>
+        <v>0.295</v>
       </c>
       <c r="H22" s="90" t="n">
-        <v>158667.48</v>
+        <v>39380.19</v>
       </c>
       <c r="I22" s="53" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
       <c r="J22" s="36" t="n"/>
@@ -4509,33 +4567,33 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>W.W. Grainger Inc.</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.295</v>
+        <v>0.292</v>
       </c>
       <c r="H23" s="91" t="n">
-        <v>39380.19</v>
+        <v>62147.38</v>
       </c>
       <c r="I23" s="54" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
@@ -4547,33 +4605,33 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>W.W. Grainger Inc.</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.294</v>
+        <v>0.291</v>
       </c>
       <c r="H24" s="90" t="n">
-        <v>62147.38</v>
+        <v>14353.95</v>
       </c>
       <c r="I24" s="53" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
       <c r="J24" s="36" t="n"/>
@@ -4585,33 +4643,33 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.29</v>
+        <v>0.289</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>14353.95</v>
+        <v>158667.48</v>
       </c>
       <c r="I25" s="54" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J25" s="28" t="n"/>
@@ -4642,7 +4700,7 @@
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="H26" s="90" t="n">
         <v>30713.22</v>
@@ -4680,7 +4738,7 @@
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.248</v>
+        <v>0.25</v>
       </c>
       <c r="H27" s="91" t="n">
         <v>55851.6</v>
@@ -4718,7 +4776,7 @@
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="H28" s="90" t="n">
         <v>23624.19</v>
@@ -4756,7 +4814,7 @@
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="H29" s="91" t="n">
         <v>40474.89</v>
@@ -4794,7 +4852,7 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="H30" s="90" t="n">
         <v>388502.86</v>
@@ -4832,7 +4890,7 @@
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.19</v>
+        <v>0.193</v>
       </c>
       <c r="H31" s="91" t="n">
         <v>308648.81</v>
@@ -4870,7 +4928,7 @@
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="H32" s="90" t="n">
         <v>13320.91</v>
@@ -4889,33 +4947,33 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Citizens Financial Group Inc.</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.159</v>
+        <v>0.166</v>
       </c>
       <c r="H33" s="91" t="n">
-        <v>89144.46000000001</v>
+        <v>27585.86</v>
       </c>
       <c r="I33" s="54" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
       <c r="J33" s="28" t="n"/>
@@ -4927,12 +4985,12 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc.</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
@@ -4946,14 +5004,14 @@
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.158</v>
+        <v>0.155</v>
       </c>
       <c r="H34" s="90" t="n">
-        <v>27585.86</v>
+        <v>47955.66</v>
       </c>
       <c r="I34" s="53" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
       <c r="J34" s="36" t="n"/>
@@ -4965,33 +5023,33 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G35" s="89" t="n">
         <v>0.152</v>
       </c>
       <c r="H35" s="91" t="n">
-        <v>47955.66</v>
+        <v>89144.46000000001</v>
       </c>
       <c r="I35" s="54" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
       <c r="J35" s="28" t="n"/>
@@ -5003,33 +5061,33 @@
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="D36" s="39" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Prudential Financial Inc.</t>
         </is>
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="H36" s="90" t="n">
-        <v>21453.67</v>
+        <v>36717.82</v>
       </c>
       <c r="I36" s="53" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
       <c r="J36" s="36" t="n"/>
@@ -5041,33 +5099,33 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D37" s="31" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="H37" s="91" t="n">
-        <v>36717.82</v>
+        <v>21453.67</v>
       </c>
       <c r="I37" s="54" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J37" s="28" t="n"/>
@@ -5098,7 +5156,7 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="H38" s="90" t="n">
         <v>612046.08</v>
@@ -5136,7 +5194,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>36258.68</v>
@@ -5198,108 +5256,218 @@
       <c r="I41" s="54" t="n"/>
       <c r="J41" s="28" t="n"/>
     </row>
-    <row r="42" ht="24.6" customHeight="1" thickBot="1">
+    <row r="42" ht="24" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="76" t="n"/>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="78" t="n"/>
-      <c r="E42" s="79" t="n"/>
-      <c r="F42" s="79" t="n"/>
-      <c r="G42" s="92" t="n"/>
-      <c r="H42" s="96" t="n"/>
-      <c r="I42" s="81" t="n"/>
+      <c r="B42" s="48" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="90" t="n"/>
+      <c r="I42" s="53" t="n"/>
       <c r="J42" s="75" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="91" t="n"/>
+      <c r="I43" s="54" t="n"/>
       <c r="J43" s="43" t="n"/>
     </row>
-    <row r="44" ht="15.6" customHeight="1" thickBot="1">
+    <row r="44" ht="24" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="43" t="n"/>
-      <c r="E44" s="43" t="n"/>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="43" t="n"/>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="43" t="n"/>
+      <c r="B44" s="48" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="40" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="89" t="n"/>
+      <c r="H44" s="90" t="n"/>
+      <c r="I44" s="53" t="n"/>
       <c r="J44" s="43" t="n"/>
     </row>
-    <row r="45" ht="10.2" customHeight="1">
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="58" t="n"/>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
-      <c r="G45" s="59" t="n"/>
-      <c r="H45" s="59" t="n"/>
-      <c r="I45" s="60" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="89" t="n"/>
+      <c r="H45" s="91" t="n"/>
+      <c r="I45" s="54" t="n"/>
       <c r="J45" s="43" t="n"/>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="24" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="67" t="n"/>
-      <c r="C46" s="64" t="n"/>
-      <c r="D46" s="64" t="n"/>
-      <c r="E46" s="64" t="n"/>
-      <c r="F46" s="64" t="n"/>
-      <c r="G46" s="64" t="n"/>
-      <c r="H46" s="64" t="n"/>
-      <c r="I46" s="65" t="n"/>
+      <c r="B46" s="48" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="40" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="90" t="n"/>
+      <c r="I46" s="53" t="n"/>
       <c r="J46" s="43" t="n"/>
     </row>
-    <row r="47" ht="10.8" customHeight="1" thickBot="1">
+    <row r="47" ht="24" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="62" t="n"/>
-      <c r="D47" s="62" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="62" t="n"/>
-      <c r="G47" s="62" t="n"/>
-      <c r="H47" s="62" t="n"/>
-      <c r="I47" s="63" t="n"/>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="91" t="n"/>
+      <c r="I47" s="54" t="n"/>
       <c r="J47" s="43" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="24" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="43" t="n"/>
-      <c r="E48" s="43" t="n"/>
-      <c r="F48" s="43" t="n"/>
-      <c r="G48" s="43" t="n"/>
-      <c r="H48" s="43" t="n"/>
-      <c r="I48" s="43" t="n"/>
+      <c r="B48" s="48" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="90" t="n"/>
+      <c r="I48" s="53" t="n"/>
       <c r="J48" s="43" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="24" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="47" t="n"/>
-      <c r="C49" s="47" t="n"/>
-      <c r="D49" s="47" t="n"/>
-      <c r="E49" s="47" t="n"/>
-      <c r="F49" s="47" t="n"/>
-      <c r="G49" s="47" t="n"/>
-      <c r="H49" s="47" t="n"/>
-      <c r="I49" s="47" t="n"/>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="89" t="n"/>
+      <c r="H49" s="91" t="n"/>
+      <c r="I49" s="54" t="n"/>
       <c r="J49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="B50" s="48" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="40" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="89" t="n"/>
+      <c r="H50" s="90" t="n"/>
+      <c r="I50" s="53" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="89" t="n"/>
+      <c r="H51" s="91" t="n"/>
+      <c r="I51" s="54" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" s="48" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="40" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="89" t="n"/>
+      <c r="H52" s="90" t="n"/>
+      <c r="I52" s="53" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="30" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="89" t="n"/>
+      <c r="H53" s="91" t="n"/>
+      <c r="I53" s="54" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="89" t="n"/>
+      <c r="H54" s="90" t="n"/>
+      <c r="I54" s="53" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="30" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="89" t="n"/>
+      <c r="H55" s="91" t="n"/>
+      <c r="I55" s="54" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="48" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="40" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="89" t="n"/>
+      <c r="H56" s="90" t="n"/>
+      <c r="I56" s="53" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="B57" s="49" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="89" t="n"/>
+      <c r="H57" s="91" t="n"/>
+      <c r="I57" s="54" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="40" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="89" t="n"/>
+      <c r="H58" s="90" t="n"/>
+      <c r="I58" s="53" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="B59" s="49" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="89" t="n"/>
+      <c r="H59" s="91" t="n"/>
+      <c r="I59" s="54" t="n"/>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="B60" s="48" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="89" t="n"/>
+      <c r="H60" s="90" t="n"/>
+      <c r="I60" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G42">
+  <conditionalFormatting sqref="G8:G60">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30720" yWindow="0" windowWidth="21600" windowHeight="11235" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$K$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$K$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -214,8 +214,18 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC67A29"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -298,8 +308,18 @@
         <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -453,11 +473,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC67A29"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC67A29"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC67A29"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC67A29"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1DCE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -686,25 +736,78 @@
     <xf numFmtId="164" fontId="20" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1260,7 +1363,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.8272040635</v>
+        <v>46224.85673662008</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1282,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -1292,10 +1395,10 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="14" customWidth="1" style="14" min="8" max="8"/>
-    <col width="56" customWidth="1" style="11" min="9" max="9"/>
-    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
-    <col width="8.88671875" customWidth="1" style="11" min="11" max="11"/>
+    <col width="10" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="11" min="9" max="9"/>
+    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
     <col width="8.88671875" customWidth="1" style="11" min="14" max="14"/>
@@ -1321,9 +1424,8 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84">
-        <f>Date!B2</f>
-        <v/>
+      <c r="H2" s="84" t="n">
+        <v>46224.85673662008</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -1418,15 +1520,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
-      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -1454,17 +1561,22 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.631</v>
-      </c>
-      <c r="H8" s="90" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I8" s="91" t="n">
         <v>2358.79</v>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="J8" s="53" t="inlineStr">
         <is>
           <t>Bird Construction Inc provides construction services in Canada</t>
         </is>
       </c>
-      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="26.4" customHeight="1">
       <c r="A9" s="28" t="n"/>
@@ -1492,17 +1604,22 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="H9" s="91" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I9" s="93" t="n">
         <v>555.83</v>
       </c>
-      <c r="I9" s="54" t="inlineStr">
+      <c r="J9" s="54" t="inlineStr">
         <is>
           <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
-      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="20.4" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -1530,17 +1647,22 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>1.153</v>
-      </c>
-      <c r="H10" s="90" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
         <v>284.57</v>
       </c>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="J10" s="53" t="inlineStr">
         <is>
           <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
         </is>
       </c>
-      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="20.4" customHeight="1">
       <c r="A11" s="28" t="n"/>
@@ -1568,17 +1690,22 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H11" s="91" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
         <v>2258.51</v>
       </c>
-      <c r="I11" s="54" t="inlineStr">
+      <c r="J11" s="54" t="inlineStr">
         <is>
           <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
         </is>
       </c>
-      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
     </row>
     <row r="12" ht="20.4" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -1608,15 +1735,20 @@
       <c r="G12" s="89" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="H12" s="90" t="n">
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
         <v>1565.38</v>
       </c>
-      <c r="I12" s="53" t="inlineStr">
+      <c r="J12" s="53" t="inlineStr">
         <is>
           <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
-      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="28" t="n"/>
@@ -1644,17 +1776,22 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="H13" s="91" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
         <v>1892.54</v>
       </c>
-      <c r="I13" s="54" t="inlineStr">
+      <c r="J13" s="54" t="inlineStr">
         <is>
           <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
         </is>
       </c>
-      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="28" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="36" t="n"/>
@@ -1682,17 +1819,22 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="H14" s="90" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
         <v>53011.04</v>
       </c>
-      <c r="I14" s="53" t="inlineStr">
+      <c r="J14" s="53" t="inlineStr">
         <is>
           <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
         </is>
       </c>
-      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="28" t="n"/>
@@ -1722,15 +1864,20 @@
       <c r="G15" s="89" t="n">
         <v>0.443</v>
       </c>
-      <c r="H15" s="91" t="n">
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
         <v>2385.76</v>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="J15" s="54" t="inlineStr">
         <is>
           <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
     </row>
     <row r="16" ht="20.4" customHeight="1">
       <c r="A16" s="28" t="n"/>
@@ -1758,17 +1905,22 @@
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="H16" s="90" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
         <v>390.27</v>
       </c>
-      <c r="I16" s="53" t="inlineStr">
+      <c r="J16" s="53" t="inlineStr">
         <is>
           <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
     </row>
     <row r="17" ht="40.8" customHeight="1">
       <c r="A17" s="36" t="n"/>
@@ -1798,15 +1950,20 @@
       <c r="G17" s="89" t="n">
         <v>0.36</v>
       </c>
-      <c r="H17" s="91" t="n">
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
         <v>116001.23</v>
       </c>
-      <c r="I17" s="54" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
         </is>
       </c>
-      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="28" t="n"/>
@@ -1815,36 +1972,41 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>Power Corporation of Canada</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
         <v>0.34</v>
       </c>
-      <c r="H18" s="90" t="n">
-        <v>681.6799999999999</v>
-      </c>
-      <c r="I18" s="53" t="inlineStr">
-        <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="n"/>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
+        <v>38174.66</v>
+      </c>
+      <c r="J18" s="53" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="n"/>
     </row>
     <row r="19" ht="30.6" customHeight="1">
       <c r="A19" s="36" t="n"/>
@@ -1853,36 +2015,41 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
         <v>0.339</v>
       </c>
-      <c r="H19" s="91" t="n">
-        <v>38174.66</v>
-      </c>
-      <c r="I19" s="54" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
-        </is>
-      </c>
-      <c r="J19" s="36" t="n"/>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
+        <v>681.6799999999999</v>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+        </is>
+      </c>
+      <c r="K19" s="36" t="n"/>
     </row>
     <row r="20" ht="30.6" customHeight="1">
       <c r="A20" s="28" t="n"/>
@@ -1910,17 +2077,22 @@
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="H20" s="90" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
         <v>41467.31</v>
       </c>
-      <c r="I20" s="53" t="inlineStr">
+      <c r="J20" s="53" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
-      <c r="J20" s="28" t="n"/>
+      <c r="K20" s="28" t="n"/>
     </row>
     <row r="21" ht="30.6" customHeight="1">
       <c r="A21" s="36" t="n"/>
@@ -1948,17 +2120,22 @@
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="H21" s="91" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
         <v>72839.50999999999</v>
       </c>
-      <c r="I21" s="54" t="inlineStr">
+      <c r="J21" s="54" t="inlineStr">
         <is>
           <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
-      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="28" t="n"/>
@@ -1988,15 +2165,20 @@
       <c r="G22" s="89" t="n">
         <v>0.324</v>
       </c>
-      <c r="H22" s="90" t="n">
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="n">
         <v>101497.85</v>
       </c>
-      <c r="I22" s="53" t="inlineStr">
+      <c r="J22" s="53" t="inlineStr">
         <is>
           <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
-      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="28" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="28" t="n"/>
@@ -2024,17 +2206,22 @@
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H23" s="91" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
         <v>189567.97</v>
       </c>
-      <c r="I23" s="54" t="inlineStr">
+      <c r="J23" s="54" t="inlineStr">
         <is>
           <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
         </is>
       </c>
-      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="28" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -2064,15 +2251,20 @@
       <c r="G24" s="89" t="n">
         <v>0.317</v>
       </c>
-      <c r="H24" s="90" t="n">
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
         <v>3018.47</v>
       </c>
-      <c r="I24" s="53" t="inlineStr">
+      <c r="J24" s="53" t="inlineStr">
         <is>
           <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
         </is>
       </c>
-      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="28" t="n"/>
@@ -2102,15 +2294,20 @@
       <c r="G25" s="89" t="n">
         <v>0.31</v>
       </c>
-      <c r="H25" s="91" t="n">
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I25" s="93" t="n">
         <v>28518.97</v>
       </c>
-      <c r="I25" s="54" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
-      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="20.4" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -2138,17 +2335,22 @@
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="H26" s="90" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H26" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="n">
         <v>13303.41</v>
       </c>
-      <c r="I26" s="53" t="inlineStr">
+      <c r="J26" s="53" t="inlineStr">
         <is>
           <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
         </is>
       </c>
-      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="36" t="n"/>
@@ -2176,17 +2378,22 @@
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="H27" s="91" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
         <v>275998.42</v>
       </c>
-      <c r="I27" s="54" t="inlineStr">
+      <c r="J27" s="54" t="inlineStr">
         <is>
           <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
-      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
     </row>
     <row r="28" ht="20.4" customHeight="1">
       <c r="A28" s="28" t="n"/>
@@ -2214,17 +2421,22 @@
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="H28" s="90" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
         <v>79823.21000000001</v>
       </c>
-      <c r="I28" s="53" t="inlineStr">
+      <c r="J28" s="53" t="inlineStr">
         <is>
           <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
-      <c r="J28" s="28" t="n"/>
+      <c r="K28" s="28" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="36" t="n"/>
@@ -2233,36 +2445,41 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Canadian Utilities Limited</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
         <v>0.266</v>
       </c>
-      <c r="H29" s="91" t="n">
-        <v>976.67</v>
-      </c>
-      <c r="I29" s="54" t="inlineStr">
-        <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
-        </is>
-      </c>
-      <c r="J29" s="36" t="n"/>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
+        <v>10045.65</v>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+        </is>
+      </c>
+      <c r="K29" s="36" t="n"/>
     </row>
     <row r="30" ht="30.6" customHeight="1">
       <c r="A30" s="36" t="n"/>
@@ -2271,36 +2488,41 @@
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
         <v>0.265</v>
       </c>
-      <c r="H30" s="90" t="n">
-        <v>10045.65</v>
-      </c>
-      <c r="I30" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
-        </is>
-      </c>
-      <c r="J30" s="36" t="n"/>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
+        <v>976.67</v>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="30.6" customHeight="1">
       <c r="A31" s="28" t="n"/>
@@ -2328,17 +2550,22 @@
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="H31" s="91" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="H31" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I31" s="93" t="n">
         <v>2215.94</v>
       </c>
-      <c r="I31" s="54" t="inlineStr">
+      <c r="J31" s="54" t="inlineStr">
         <is>
           <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
       </c>
-      <c r="J31" s="28" t="n"/>
+      <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -2366,17 +2593,22 @@
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="H32" s="90" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="H32" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I32" s="91" t="n">
         <v>11282.66</v>
       </c>
-      <c r="I32" s="53" t="inlineStr">
+      <c r="J32" s="53" t="inlineStr">
         <is>
           <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
-      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
@@ -2404,17 +2636,22 @@
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="H33" s="91" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H33" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I33" s="93" t="n">
         <v>576.85</v>
       </c>
-      <c r="I33" s="54" t="inlineStr">
+      <c r="J33" s="54" t="inlineStr">
         <is>
           <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
-      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="30.6" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -2444,15 +2681,20 @@
       <c r="G34" s="89" t="n">
         <v>0.227</v>
       </c>
-      <c r="H34" s="90" t="n">
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
         <v>100391.39</v>
       </c>
-      <c r="I34" s="53" t="inlineStr">
+      <c r="J34" s="53" t="inlineStr">
         <is>
           <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
-      <c r="J34" s="36" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="30.6" customHeight="1">
       <c r="A35" s="28" t="n"/>
@@ -2480,17 +2722,22 @@
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="H35" s="91" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
         <v>927.72</v>
       </c>
-      <c r="I35" s="54" t="inlineStr">
+      <c r="J35" s="54" t="inlineStr">
         <is>
           <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
-      <c r="J35" s="28" t="n"/>
+      <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="40.8" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -2518,17 +2765,22 @@
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="H36" s="90" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
         <v>65572.44</v>
       </c>
-      <c r="I36" s="53" t="inlineStr">
+      <c r="J36" s="53" t="inlineStr">
         <is>
           <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
-      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="28" t="n"/>
@@ -2556,17 +2808,22 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="H37" s="91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
         <v>501.72</v>
       </c>
-      <c r="I37" s="54" t="inlineStr">
+      <c r="J37" s="54" t="inlineStr">
         <is>
           <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
-      <c r="J37" s="28" t="n"/>
+      <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -2596,15 +2853,20 @@
       <c r="G38" s="89" t="n">
         <v>0.174</v>
       </c>
-      <c r="H38" s="90" t="n">
+      <c r="H38" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="n">
         <v>1330.28</v>
       </c>
-      <c r="I38" s="53" t="inlineStr">
+      <c r="J38" s="53" t="inlineStr">
         <is>
           <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
-      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
@@ -2632,280 +2894,199 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="H39" s="91" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="H39" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I39" s="93" t="n">
         <v>676.4400000000001</v>
       </c>
-      <c r="I39" s="54" t="inlineStr">
+      <c r="J39" s="54" t="inlineStr">
         <is>
           <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
         </is>
       </c>
-      <c r="J39" s="28" t="n"/>
+      <c r="K39" s="28" t="n"/>
     </row>
     <row r="40" ht="20.4" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n">
+      <c r="B40" s="106" t="n">
         <v>33</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="107" t="inlineStr">
         <is>
           <t>DFY</t>
         </is>
       </c>
-      <c r="D40" s="39" t="inlineStr">
+      <c r="D40" s="108" t="inlineStr">
         <is>
           <t>Definity Financial Corporation</t>
         </is>
       </c>
-      <c r="E40" s="40" t="inlineStr">
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G40" s="89" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H40" s="90" t="n">
+      <c r="G40" s="110" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H40" s="111" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I40" s="112" t="n">
         <v>6226.62</v>
       </c>
-      <c r="I40" s="53" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
         </is>
       </c>
-      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="91" t="n"/>
-      <c r="I41" s="54" t="n"/>
-      <c r="J41" s="68" t="n"/>
-    </row>
-    <row r="42" ht="26.4" customHeight="1">
+      <c r="B41" s="69" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="71" t="n"/>
+      <c r="E41" s="72" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="94" t="n"/>
+      <c r="H41" s="95" t="n"/>
+      <c r="I41" s="96" t="n"/>
+      <c r="J41" s="74" t="n"/>
+      <c r="K41" s="68" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="48" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="40" t="n"/>
-      <c r="F42" s="40" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="90" t="n"/>
-      <c r="I42" s="53" t="n"/>
-      <c r="J42" s="43" t="n"/>
-    </row>
-    <row r="43" ht="26.4" customHeight="1" thickBot="1">
+      <c r="B42" s="114" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="n"/>
+      <c r="D42" s="115" t="n"/>
+      <c r="E42" s="115" t="n"/>
+      <c r="F42" s="115" t="n"/>
+      <c r="G42" s="115" t="n"/>
+      <c r="H42" s="115" t="n"/>
+      <c r="I42" s="115" t="n"/>
+      <c r="J42" s="115" t="n"/>
+      <c r="K42" s="43" t="n"/>
+    </row>
+    <row r="43" ht="28" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="31" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="91" t="n"/>
-      <c r="I43" s="54" t="n"/>
-      <c r="J43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="26.4" customHeight="1">
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="n"/>
+      <c r="D43" s="117" t="n"/>
+      <c r="E43" s="117" t="n"/>
+      <c r="F43" s="117" t="n"/>
+      <c r="G43" s="117" t="n"/>
+      <c r="H43" s="117" t="n"/>
+      <c r="I43" s="117" t="n"/>
+      <c r="J43" s="117" t="n"/>
+      <c r="K43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="12" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="48" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="90" t="n"/>
-      <c r="I44" s="53" t="n"/>
-      <c r="J44" s="43" t="n"/>
-    </row>
-    <row r="45" ht="26.4" customHeight="1">
+      <c r="B44" s="58" t="n"/>
+      <c r="C44" s="59" t="n"/>
+      <c r="D44" s="59" t="n"/>
+      <c r="E44" s="59" t="n"/>
+      <c r="F44" s="59" t="n"/>
+      <c r="G44" s="59" t="n"/>
+      <c r="H44" s="98" t="n"/>
+      <c r="I44" s="59" t="n"/>
+      <c r="J44" s="60" t="n"/>
+      <c r="K44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="15.6" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="89" t="n"/>
-      <c r="H45" s="91" t="n"/>
-      <c r="I45" s="54" t="n"/>
-      <c r="J45" s="43" t="n"/>
-    </row>
-    <row r="46" ht="26.4" customHeight="1" thickBot="1">
+      <c r="B45" s="67" t="n"/>
+      <c r="C45" s="64" t="n"/>
+      <c r="D45" s="66" t="n"/>
+      <c r="E45" s="64" t="n"/>
+      <c r="F45" s="64" t="n"/>
+      <c r="G45" s="64" t="n"/>
+      <c r="H45" s="99" t="n"/>
+      <c r="I45" s="64" t="n"/>
+      <c r="J45" s="65" t="n"/>
+      <c r="K45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="9.6" customHeight="1" thickBot="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="40" t="n"/>
-      <c r="F46" s="40" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="43" t="n"/>
-    </row>
-    <row r="47" ht="26.4" customHeight="1">
+      <c r="B46" s="61" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="100" t="n"/>
+      <c r="I46" s="62" t="n"/>
+      <c r="J46" s="63" t="n"/>
+      <c r="K46" s="43" t="n"/>
+    </row>
+    <row r="47">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="49" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="89" t="n"/>
-      <c r="H47" s="91" t="n"/>
-      <c r="I47" s="54" t="n"/>
+      <c r="B47" s="43" t="n"/>
+      <c r="C47" s="43" t="n"/>
+      <c r="D47" s="43" t="n"/>
+      <c r="E47" s="43" t="n"/>
+      <c r="F47" s="43" t="n"/>
+      <c r="G47" s="43" t="n"/>
+      <c r="H47" s="97" t="n"/>
+      <c r="I47" s="43" t="n"/>
       <c r="J47" s="43" t="n"/>
-    </row>
-    <row r="48" ht="26.4" customHeight="1">
+      <c r="K47" s="43" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="40" t="n"/>
-      <c r="F48" s="40" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="90" t="n"/>
-      <c r="I48" s="53" t="n"/>
-      <c r="J48" s="43" t="n"/>
-    </row>
-    <row r="49" ht="26.4" customHeight="1">
+      <c r="B48" s="47" t="n"/>
+      <c r="C48" s="47" t="n"/>
+      <c r="D48" s="47" t="n"/>
+      <c r="E48" s="47" t="n"/>
+      <c r="F48" s="47" t="n"/>
+      <c r="G48" s="47" t="n"/>
+      <c r="H48" s="101" t="n"/>
+      <c r="I48" s="47" t="n"/>
+      <c r="J48" s="47" t="n"/>
+      <c r="K48" s="43" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="49" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="89" t="n"/>
-      <c r="H49" s="91" t="n"/>
-      <c r="I49" s="54" t="n"/>
+      <c r="B49" s="43" t="n"/>
+      <c r="C49" s="43" t="n"/>
+      <c r="D49" s="43" t="n"/>
+      <c r="E49" s="43" t="n"/>
+      <c r="F49" s="43" t="n"/>
+      <c r="G49" s="43" t="n"/>
+      <c r="H49" s="97" t="n"/>
+      <c r="I49" s="43" t="n"/>
       <c r="J49" s="43" t="n"/>
-    </row>
-    <row r="50" ht="26.4" customHeight="1">
-      <c r="B50" s="48" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="40" t="n"/>
-      <c r="F50" s="40" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="90" t="n"/>
-      <c r="I50" s="53" t="n"/>
-    </row>
-    <row r="51" ht="26.4" customHeight="1">
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="89" t="n"/>
-      <c r="H51" s="91" t="n"/>
-      <c r="I51" s="54" t="n"/>
-    </row>
-    <row r="52" ht="26.4" customHeight="1">
-      <c r="B52" s="48" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="40" t="n"/>
-      <c r="F52" s="40" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="90" t="n"/>
-      <c r="I52" s="53" t="n"/>
-    </row>
-    <row r="53" ht="26.4" customHeight="1">
-      <c r="B53" s="49" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="89" t="n"/>
-      <c r="H53" s="91" t="n"/>
-      <c r="I53" s="54" t="n"/>
-    </row>
-    <row r="54" ht="26.4" customHeight="1">
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="89" t="n"/>
-      <c r="H54" s="90" t="n"/>
-      <c r="I54" s="53" t="n"/>
-    </row>
-    <row r="55" ht="26.4" customHeight="1">
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="89" t="n"/>
-      <c r="H55" s="91" t="n"/>
-      <c r="I55" s="54" t="n"/>
-    </row>
-    <row r="56" ht="26.4" customHeight="1">
-      <c r="B56" s="48" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="40" t="n"/>
-      <c r="F56" s="40" t="n"/>
-      <c r="G56" s="89" t="n"/>
-      <c r="H56" s="90" t="n"/>
-      <c r="I56" s="53" t="n"/>
-    </row>
-    <row r="57" ht="26.4" customHeight="1">
-      <c r="B57" s="49" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="89" t="n"/>
-      <c r="H57" s="91" t="n"/>
-      <c r="I57" s="54" t="n"/>
-    </row>
-    <row r="58" ht="26.4" customHeight="1">
-      <c r="B58" s="48" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
-      <c r="G58" s="89" t="n"/>
-      <c r="H58" s="90" t="n"/>
-      <c r="I58" s="53" t="n"/>
-    </row>
-    <row r="59" ht="26.4" customHeight="1">
-      <c r="B59" s="49" t="n"/>
-      <c r="C59" s="30" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="32" t="n"/>
-      <c r="F59" s="32" t="n"/>
-      <c r="G59" s="89" t="n"/>
-      <c r="H59" s="91" t="n"/>
-      <c r="I59" s="54" t="n"/>
-    </row>
-    <row r="60" ht="26.4" customHeight="1">
-      <c r="B60" s="48" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="40" t="n"/>
-      <c r="F60" s="40" t="n"/>
-      <c r="G60" s="89" t="n"/>
-      <c r="H60" s="90" t="n"/>
-      <c r="I60" s="53" t="n"/>
+      <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B42:J42"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G60">
+  <conditionalFormatting sqref="G8:G40">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -3032,14 +3213,14 @@
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="94" t="n"/>
-      <c r="C11" s="94" t="n"/>
-      <c r="D11" s="94" t="n"/>
-      <c r="E11" s="94" t="n"/>
-      <c r="F11" s="94" t="n"/>
-      <c r="G11" s="94" t="n"/>
-      <c r="H11" s="94" t="n"/>
-      <c r="I11" s="94" t="n"/>
+      <c r="B11" s="102" t="n"/>
+      <c r="C11" s="102" t="n"/>
+      <c r="D11" s="102" t="n"/>
+      <c r="E11" s="102" t="n"/>
+      <c r="F11" s="102" t="n"/>
+      <c r="G11" s="102" t="n"/>
+      <c r="H11" s="102" t="n"/>
+      <c r="I11" s="102" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="M11" s="19" t="inlineStr">
         <is>
@@ -3115,7 +3296,7 @@
     <row r="13" ht="15.6" customHeight="1" thickBot="1">
       <c r="A13" s="36" t="n"/>
       <c r="B13" s="48" t="n"/>
-      <c r="C13" s="95" t="n"/>
+      <c r="C13" s="103" t="n"/>
       <c r="D13" s="38" t="n"/>
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="40" t="n"/>
@@ -3844,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -3854,10 +4035,10 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="14" customWidth="1" style="14" min="8" max="8"/>
-    <col width="56" customWidth="1" style="11" min="9" max="9"/>
-    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
-    <col width="8.88671875" customWidth="1" style="11" min="11" max="11"/>
+    <col width="10" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="11" min="9" max="9"/>
+    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
     <col width="8.88671875" customWidth="1" style="11" min="14" max="14"/>
@@ -3883,9 +4064,8 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84">
-        <f>Date!B2</f>
-        <v/>
+      <c r="H2" s="84" t="n">
+        <v>46224.85673662008</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -3980,15 +4160,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
-      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -4016,17 +4201,22 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.193</v>
-      </c>
-      <c r="H8" s="90" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I8" s="91" t="n">
         <v>12725.72</v>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="J8" s="53" t="inlineStr">
         <is>
           <t>DaVita Inc provides kidney dialysis services for patients suffering from chronic kidney failure in the United States</t>
         </is>
       </c>
-      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="28" t="n"/>
@@ -4056,15 +4246,20 @@
       <c r="G9" s="89" t="n">
         <v>0.899</v>
       </c>
-      <c r="H9" s="91" t="n">
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I9" s="93" t="n">
         <v>213908.98</v>
       </c>
-      <c r="I9" s="54" t="inlineStr">
+      <c r="J9" s="54" t="inlineStr">
         <is>
           <t>Palo Alto Networks Inc provides cybersecurity solutions in the Americas Europe the Middle East Africa the Asia Pacific and Japan</t>
         </is>
       </c>
-      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="20.4" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -4094,15 +4289,20 @@
       <c r="G10" s="89" t="n">
         <v>0.839</v>
       </c>
-      <c r="H10" s="90" t="n">
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
         <v>77721.12</v>
       </c>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="J10" s="53" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
-      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="28" t="n"/>
@@ -4132,15 +4332,20 @@
       <c r="G11" s="89" t="n">
         <v>0.701</v>
       </c>
-      <c r="H11" s="91" t="n">
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
         <v>77190.64999999999</v>
       </c>
-      <c r="I11" s="54" t="inlineStr">
+      <c r="J11" s="54" t="inlineStr">
         <is>
           <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
-      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -4170,15 +4375,20 @@
       <c r="G12" s="89" t="n">
         <v>0.471</v>
       </c>
-      <c r="H12" s="90" t="n">
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
         <v>44725.83</v>
       </c>
-      <c r="I12" s="53" t="inlineStr">
+      <c r="J12" s="53" t="inlineStr">
         <is>
           <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
-      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="20.4" customHeight="1">
       <c r="A13" s="28" t="n"/>
@@ -4208,15 +4418,20 @@
       <c r="G13" s="89" t="n">
         <v>0.424</v>
       </c>
-      <c r="H13" s="91" t="n">
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
         <v>26566.73</v>
       </c>
-      <c r="I13" s="54" t="inlineStr">
+      <c r="J13" s="54" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="28" t="n"/>
     </row>
     <row r="14" ht="40.8" customHeight="1">
       <c r="A14" s="36" t="n"/>
@@ -4246,15 +4461,20 @@
       <c r="G14" s="89" t="n">
         <v>0.37</v>
       </c>
-      <c r="H14" s="90" t="n">
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
         <v>86617.14</v>
       </c>
-      <c r="I14" s="53" t="inlineStr">
+      <c r="J14" s="53" t="inlineStr">
         <is>
           <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
-      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="30.6" customHeight="1">
       <c r="A15" s="28" t="n"/>
@@ -4284,15 +4504,20 @@
       <c r="G15" s="89" t="n">
         <v>0.356</v>
       </c>
-      <c r="H15" s="91" t="n">
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
         <v>96186.41</v>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="J15" s="54" t="inlineStr">
         <is>
           <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="36" t="n"/>
@@ -4322,15 +4547,20 @@
       <c r="G16" s="89" t="n">
         <v>0.356</v>
       </c>
-      <c r="H16" s="90" t="n">
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
         <v>12644.53</v>
       </c>
-      <c r="I16" s="53" t="inlineStr">
+      <c r="J16" s="53" t="inlineStr">
         <is>
           <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
-      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
     </row>
     <row r="17" ht="30.6" customHeight="1">
       <c r="A17" s="28" t="n"/>
@@ -4360,15 +4590,20 @@
       <c r="G17" s="89" t="n">
         <v>0.351</v>
       </c>
-      <c r="H17" s="91" t="n">
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
         <v>148209.56</v>
       </c>
-      <c r="I17" s="54" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
-      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
     </row>
     <row r="18" ht="20.4" customHeight="1">
       <c r="A18" s="36" t="n"/>
@@ -4396,17 +4631,22 @@
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="H18" s="90" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
         <v>125211.85</v>
       </c>
-      <c r="I18" s="53" t="inlineStr">
+      <c r="J18" s="53" t="inlineStr">
         <is>
           <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
-      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
     </row>
     <row r="19" ht="20.4" customHeight="1">
       <c r="A19" s="28" t="n"/>
@@ -4436,15 +4676,20 @@
       <c r="G19" s="89" t="n">
         <v>0.341</v>
       </c>
-      <c r="H19" s="91" t="n">
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
         <v>64533.41</v>
       </c>
-      <c r="I19" s="54" t="inlineStr">
+      <c r="J19" s="54" t="inlineStr">
         <is>
           <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
-      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="28" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="36" t="n"/>
@@ -4474,15 +4719,20 @@
       <c r="G20" s="89" t="n">
         <v>0.324</v>
       </c>
-      <c r="H20" s="90" t="n">
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
         <v>4309578.68</v>
       </c>
-      <c r="I20" s="53" t="inlineStr">
+      <c r="J20" s="53" t="inlineStr">
         <is>
           <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
         </is>
       </c>
-      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
     </row>
     <row r="21" ht="20.4" customHeight="1">
       <c r="A21" s="28" t="n"/>
@@ -4510,17 +4760,22 @@
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.307</v>
-      </c>
-      <c r="H21" s="91" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
         <v>16078.79</v>
       </c>
-      <c r="I21" s="54" t="inlineStr">
+      <c r="J21" s="54" t="inlineStr">
         <is>
           <t>Best Buy Co</t>
         </is>
       </c>
-      <c r="J21" s="28" t="n"/>
+      <c r="K21" s="28" t="n"/>
     </row>
     <row r="22" ht="30.6" customHeight="1">
       <c r="A22" s="36" t="n"/>
@@ -4550,15 +4805,20 @@
       <c r="G22" s="89" t="n">
         <v>0.295</v>
       </c>
-      <c r="H22" s="90" t="n">
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="n">
         <v>39380.19</v>
       </c>
-      <c r="I22" s="53" t="inlineStr">
+      <c r="J22" s="53" t="inlineStr">
         <is>
           <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
-      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
     </row>
     <row r="23" ht="20.4" customHeight="1">
       <c r="A23" s="28" t="n"/>
@@ -4588,15 +4848,20 @@
       <c r="G23" s="89" t="n">
         <v>0.292</v>
       </c>
-      <c r="H23" s="91" t="n">
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
         <v>62147.38</v>
       </c>
-      <c r="I23" s="54" t="inlineStr">
+      <c r="J23" s="54" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="28" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -4624,17 +4889,22 @@
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="H24" s="90" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
         <v>14353.95</v>
       </c>
-      <c r="I24" s="53" t="inlineStr">
+      <c r="J24" s="53" t="inlineStr">
         <is>
           <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
-      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="30.6" customHeight="1">
       <c r="A25" s="28" t="n"/>
@@ -4662,17 +4932,22 @@
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="H25" s="91" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I25" s="93" t="n">
         <v>158667.48</v>
       </c>
-      <c r="I25" s="54" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
-      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="30.6" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -4702,15 +4977,20 @@
       <c r="G26" s="89" t="n">
         <v>0.258</v>
       </c>
-      <c r="H26" s="90" t="n">
+      <c r="H26" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="n">
         <v>30713.22</v>
       </c>
-      <c r="I26" s="53" t="inlineStr">
+      <c r="J26" s="53" t="inlineStr">
         <is>
           <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
         </is>
       </c>
-      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="30.6" customHeight="1">
       <c r="A27" s="28" t="n"/>
@@ -4740,15 +5020,20 @@
       <c r="G27" s="89" t="n">
         <v>0.25</v>
       </c>
-      <c r="H27" s="91" t="n">
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
         <v>55851.6</v>
       </c>
-      <c r="I27" s="54" t="inlineStr">
+      <c r="J27" s="54" t="inlineStr">
         <is>
           <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
-      <c r="J27" s="28" t="n"/>
+      <c r="K27" s="28" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="36" t="n"/>
@@ -4778,15 +5063,20 @@
       <c r="G28" s="89" t="n">
         <v>0.222</v>
       </c>
-      <c r="H28" s="90" t="n">
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
         <v>23624.19</v>
       </c>
-      <c r="I28" s="53" t="inlineStr">
+      <c r="J28" s="53" t="inlineStr">
         <is>
           <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
-      <c r="J28" s="36" t="n"/>
+      <c r="K28" s="36" t="n"/>
     </row>
     <row r="29" ht="20.4" customHeight="1">
       <c r="A29" s="28" t="n"/>
@@ -4816,15 +5106,20 @@
       <c r="G29" s="89" t="n">
         <v>0.203</v>
       </c>
-      <c r="H29" s="91" t="n">
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
         <v>40474.89</v>
       </c>
-      <c r="I29" s="54" t="inlineStr">
+      <c r="J29" s="54" t="inlineStr">
         <is>
           <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
         </is>
       </c>
-      <c r="J29" s="28" t="n"/>
+      <c r="K29" s="28" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="36" t="n"/>
@@ -4852,17 +5147,22 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="H30" s="90" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
         <v>388502.86</v>
       </c>
-      <c r="I30" s="53" t="inlineStr">
+      <c r="J30" s="53" t="inlineStr">
         <is>
           <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
-      <c r="J30" s="36" t="n"/>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="28" t="n"/>
@@ -4892,15 +5192,20 @@
       <c r="G31" s="89" t="n">
         <v>0.193</v>
       </c>
-      <c r="H31" s="91" t="n">
+      <c r="H31" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I31" s="93" t="n">
         <v>308648.81</v>
       </c>
-      <c r="I31" s="54" t="inlineStr">
+      <c r="J31" s="54" t="inlineStr">
         <is>
           <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
         </is>
       </c>
-      <c r="J31" s="28" t="n"/>
+      <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -4930,15 +5235,20 @@
       <c r="G32" s="89" t="n">
         <v>0.18</v>
       </c>
-      <c r="H32" s="90" t="n">
+      <c r="H32" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I32" s="91" t="n">
         <v>13320.91</v>
       </c>
-      <c r="I32" s="53" t="inlineStr">
+      <c r="J32" s="53" t="inlineStr">
         <is>
           <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
-      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
@@ -4968,15 +5278,20 @@
       <c r="G33" s="89" t="n">
         <v>0.166</v>
       </c>
-      <c r="H33" s="91" t="n">
+      <c r="H33" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I33" s="93" t="n">
         <v>27585.86</v>
       </c>
-      <c r="I33" s="54" t="inlineStr">
+      <c r="J33" s="54" t="inlineStr">
         <is>
           <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
-      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -5006,15 +5321,20 @@
       <c r="G34" s="89" t="n">
         <v>0.155</v>
       </c>
-      <c r="H34" s="90" t="n">
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
         <v>47955.66</v>
       </c>
-      <c r="I34" s="53" t="inlineStr">
+      <c r="J34" s="53" t="inlineStr">
         <is>
           <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
-      <c r="J34" s="36" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="20.4" customHeight="1">
       <c r="A35" s="28" t="n"/>
@@ -5044,15 +5364,20 @@
       <c r="G35" s="89" t="n">
         <v>0.152</v>
       </c>
-      <c r="H35" s="91" t="n">
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
         <v>89144.46000000001</v>
       </c>
-      <c r="I35" s="54" t="inlineStr">
+      <c r="J35" s="54" t="inlineStr">
         <is>
           <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
-      <c r="J35" s="28" t="n"/>
+      <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="30.6" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -5082,15 +5407,20 @@
       <c r="G36" s="89" t="n">
         <v>0.131</v>
       </c>
-      <c r="H36" s="90" t="n">
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
         <v>36717.82</v>
       </c>
-      <c r="I36" s="53" t="inlineStr">
+      <c r="J36" s="53" t="inlineStr">
         <is>
           <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
-      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="30.6" customHeight="1">
       <c r="A37" s="28" t="n"/>
@@ -5120,15 +5450,20 @@
       <c r="G37" s="89" t="n">
         <v>0.127</v>
       </c>
-      <c r="H37" s="91" t="n">
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
         <v>21453.67</v>
       </c>
-      <c r="I37" s="54" t="inlineStr">
+      <c r="J37" s="54" t="inlineStr">
         <is>
           <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
-      <c r="J37" s="28" t="n"/>
+      <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -5156,17 +5491,22 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="H38" s="90" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H38" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="n">
         <v>612046.08</v>
       </c>
-      <c r="I38" s="53" t="inlineStr">
+      <c r="J38" s="53" t="inlineStr">
         <is>
           <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
-      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
@@ -5196,53 +5536,63 @@
       <c r="G39" s="89" t="n">
         <v>0.075</v>
       </c>
-      <c r="H39" s="91" t="n">
+      <c r="H39" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I39" s="93" t="n">
         <v>36258.68</v>
       </c>
-      <c r="I39" s="54" t="inlineStr">
+      <c r="J39" s="54" t="inlineStr">
         <is>
           <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
         </is>
       </c>
-      <c r="J39" s="28" t="n"/>
+      <c r="K39" s="28" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n">
+      <c r="B40" s="106" t="n">
         <v>33</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="107" t="inlineStr">
         <is>
           <t>BXP</t>
         </is>
       </c>
-      <c r="D40" s="39" t="inlineStr">
+      <c r="D40" s="108" t="inlineStr">
         <is>
           <t>BXP Inc.</t>
         </is>
       </c>
-      <c r="E40" s="40" t="inlineStr">
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Office REITs</t>
         </is>
       </c>
-      <c r="G40" s="89" t="n">
+      <c r="G40" s="110" t="n">
         <v>0.068</v>
       </c>
-      <c r="H40" s="90" t="n">
+      <c r="H40" s="111" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I40" s="112" t="n">
         <v>11826.25</v>
       </c>
-      <c r="I40" s="53" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
         </is>
       </c>
-      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="30.6" customHeight="1">
       <c r="A41" s="28" t="n"/>
@@ -5252,222 +5602,131 @@
       <c r="E41" s="32" t="n"/>
       <c r="F41" s="32" t="n"/>
       <c r="G41" s="89" t="n"/>
-      <c r="H41" s="91" t="n"/>
-      <c r="I41" s="54" t="n"/>
-      <c r="J41" s="28" t="n"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" thickBot="1">
+      <c r="H41" s="92" t="n"/>
+      <c r="I41" s="93" t="n"/>
+      <c r="J41" s="54" t="n"/>
+      <c r="K41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="48" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="40" t="n"/>
-      <c r="F42" s="40" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="90" t="n"/>
-      <c r="I42" s="53" t="n"/>
-      <c r="J42" s="75" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1">
+      <c r="B42" s="114" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="n"/>
+      <c r="D42" s="115" t="n"/>
+      <c r="E42" s="115" t="n"/>
+      <c r="F42" s="115" t="n"/>
+      <c r="G42" s="115" t="n"/>
+      <c r="H42" s="115" t="n"/>
+      <c r="I42" s="115" t="n"/>
+      <c r="J42" s="115" t="n"/>
+      <c r="K42" s="75" t="n"/>
+    </row>
+    <row r="43" ht="28" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="31" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="91" t="n"/>
-      <c r="I43" s="54" t="n"/>
-      <c r="J43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" thickBot="1">
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="n"/>
+      <c r="D43" s="117" t="n"/>
+      <c r="E43" s="117" t="n"/>
+      <c r="F43" s="117" t="n"/>
+      <c r="G43" s="117" t="n"/>
+      <c r="H43" s="117" t="n"/>
+      <c r="I43" s="117" t="n"/>
+      <c r="J43" s="117" t="n"/>
+      <c r="K43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="15.6" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="48" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="90" t="n"/>
-      <c r="I44" s="53" t="n"/>
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="43" t="n"/>
+      <c r="D44" s="43" t="n"/>
+      <c r="E44" s="43" t="n"/>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="n"/>
+      <c r="H44" s="97" t="n"/>
+      <c r="I44" s="43" t="n"/>
       <c r="J44" s="43" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
+      <c r="K44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="10.2" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="89" t="n"/>
-      <c r="H45" s="91" t="n"/>
-      <c r="I45" s="54" t="n"/>
-      <c r="J45" s="43" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="B45" s="58" t="n"/>
+      <c r="C45" s="59" t="n"/>
+      <c r="D45" s="59" t="n"/>
+      <c r="E45" s="59" t="n"/>
+      <c r="F45" s="59" t="n"/>
+      <c r="G45" s="59" t="n"/>
+      <c r="H45" s="98" t="n"/>
+      <c r="I45" s="59" t="n"/>
+      <c r="J45" s="60" t="n"/>
+      <c r="K45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="15.6" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="40" t="n"/>
-      <c r="F46" s="40" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="43" t="n"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" thickBot="1">
+      <c r="B46" s="67" t="n"/>
+      <c r="C46" s="64" t="n"/>
+      <c r="D46" s="64" t="n"/>
+      <c r="E46" s="64" t="n"/>
+      <c r="F46" s="64" t="n"/>
+      <c r="G46" s="64" t="n"/>
+      <c r="H46" s="99" t="n"/>
+      <c r="I46" s="64" t="n"/>
+      <c r="J46" s="65" t="n"/>
+      <c r="K46" s="43" t="n"/>
+    </row>
+    <row r="47" ht="10.8" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="49" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="89" t="n"/>
-      <c r="H47" s="91" t="n"/>
-      <c r="I47" s="54" t="n"/>
-      <c r="J47" s="43" t="n"/>
-    </row>
-    <row r="48" ht="24" customHeight="1">
+      <c r="B47" s="61" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="100" t="n"/>
+      <c r="I47" s="62" t="n"/>
+      <c r="J47" s="63" t="n"/>
+      <c r="K47" s="43" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="40" t="n"/>
-      <c r="F48" s="40" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="90" t="n"/>
-      <c r="I48" s="53" t="n"/>
+      <c r="B48" s="43" t="n"/>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="43" t="n"/>
+      <c r="E48" s="43" t="n"/>
+      <c r="F48" s="43" t="n"/>
+      <c r="G48" s="43" t="n"/>
+      <c r="H48" s="97" t="n"/>
+      <c r="I48" s="43" t="n"/>
       <c r="J48" s="43" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
+      <c r="K48" s="43" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="49" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="89" t="n"/>
-      <c r="H49" s="91" t="n"/>
-      <c r="I49" s="54" t="n"/>
-      <c r="J49" s="43" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="B50" s="48" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="40" t="n"/>
-      <c r="F50" s="40" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="90" t="n"/>
-      <c r="I50" s="53" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="89" t="n"/>
-      <c r="H51" s="91" t="n"/>
-      <c r="I51" s="54" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="B52" s="48" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="40" t="n"/>
-      <c r="F52" s="40" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="90" t="n"/>
-      <c r="I52" s="53" t="n"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="49" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="89" t="n"/>
-      <c r="H53" s="91" t="n"/>
-      <c r="I53" s="54" t="n"/>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="89" t="n"/>
-      <c r="H54" s="90" t="n"/>
-      <c r="I54" s="53" t="n"/>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="89" t="n"/>
-      <c r="H55" s="91" t="n"/>
-      <c r="I55" s="54" t="n"/>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="B56" s="48" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="40" t="n"/>
-      <c r="F56" s="40" t="n"/>
-      <c r="G56" s="89" t="n"/>
-      <c r="H56" s="90" t="n"/>
-      <c r="I56" s="53" t="n"/>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="B57" s="49" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="89" t="n"/>
-      <c r="H57" s="91" t="n"/>
-      <c r="I57" s="54" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="B58" s="48" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
-      <c r="G58" s="89" t="n"/>
-      <c r="H58" s="90" t="n"/>
-      <c r="I58" s="53" t="n"/>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="B59" s="49" t="n"/>
-      <c r="C59" s="30" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="32" t="n"/>
-      <c r="F59" s="32" t="n"/>
-      <c r="G59" s="89" t="n"/>
-      <c r="H59" s="91" t="n"/>
-      <c r="I59" s="54" t="n"/>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="B60" s="48" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="40" t="n"/>
-      <c r="F60" s="40" t="n"/>
-      <c r="G60" s="89" t="n"/>
-      <c r="H60" s="90" t="n"/>
-      <c r="I60" s="53" t="n"/>
+      <c r="B49" s="47" t="n"/>
+      <c r="C49" s="47" t="n"/>
+      <c r="D49" s="47" t="n"/>
+      <c r="E49" s="47" t="n"/>
+      <c r="F49" s="47" t="n"/>
+      <c r="G49" s="47" t="n"/>
+      <c r="H49" s="101" t="n"/>
+      <c r="I49" s="47" t="n"/>
+      <c r="J49" s="47" t="n"/>
+      <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B42:J42"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G60">
+  <conditionalFormatting sqref="G8:G40">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>
@@ -5594,14 +5853,14 @@
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="94" t="n"/>
-      <c r="C11" s="94" t="n"/>
-      <c r="D11" s="94" t="n"/>
-      <c r="E11" s="94" t="n"/>
-      <c r="F11" s="94" t="n"/>
-      <c r="G11" s="94" t="n"/>
-      <c r="H11" s="94" t="n"/>
-      <c r="I11" s="94" t="n"/>
+      <c r="B11" s="102" t="n"/>
+      <c r="C11" s="102" t="n"/>
+      <c r="D11" s="102" t="n"/>
+      <c r="E11" s="102" t="n"/>
+      <c r="F11" s="102" t="n"/>
+      <c r="G11" s="102" t="n"/>
+      <c r="H11" s="102" t="n"/>
+      <c r="I11" s="102" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="M11" s="19" t="inlineStr">
         <is>
@@ -5677,7 +5936,7 @@
     <row r="13" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="36" t="n"/>
       <c r="B13" s="48" t="n"/>
-      <c r="C13" s="95" t="n"/>
+      <c r="C13" s="103" t="n"/>
       <c r="D13" s="38" t="n"/>
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="40" t="n"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -1363,7 +1363,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.85673662008</v>
+        <v>46224.86266495839</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46224.85673662008</v>
+        <v>46224.86266495839</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46224.85673662008</v>
+        <v>46224.86266495839</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -479,6 +479,7 @@
       <top/>
       <bottom style="medium"/>
     </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFC67A29"/>
@@ -493,7 +494,6 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
-    <border/>
     <border>
       <left/>
       <right/>
@@ -507,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -800,14 +800,38 @@
     <xf numFmtId="0" fontId="22" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1363,7 +1387,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.86266495839</v>
+        <v>46224.87725170761</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1424,10 +1448,10 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84" t="n">
-        <v>46224.86266495839</v>
-      </c>
-      <c r="J2" s="83" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="84" t="n">
+        <v>46224.87725170761</v>
+      </c>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="45" t="n"/>
@@ -1478,21 +1502,17 @@
       <c r="F6" s="24" t="n"/>
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="24" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="B7" s="27" t="inlineStr"/>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -1535,784 +1555,822 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="n">
-        <v>1</v>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
-          <t>BDT</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
-          <t>Bird Construction Inc.</t>
+          <t>Extendicare Inc.</t>
         </is>
       </c>
       <c r="E8" s="40" t="inlineStr">
         <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G8" s="89" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I8" s="91" t="n">
+        <v>2258.51</v>
+      </c>
+      <c r="J8" s="53" t="inlineStr">
+        <is>
+          <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
+        </is>
+      </c>
+      <c r="K8" s="36" t="n"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="28" t="n"/>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Mullen Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G9" s="89" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I9" s="93" t="n">
+        <v>1565.38</v>
+      </c>
+      <c r="J9" s="54" t="inlineStr">
+        <is>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K9" s="28" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>GWO</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>Great-West Lifeco Inc.</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
+        <v>53011.04</v>
+      </c>
+      <c r="J10" s="53" t="inlineStr">
+        <is>
+          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
+        </is>
+      </c>
+      <c r="K10" s="36" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>POW</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G11" s="89" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
+        <v>38174.66</v>
+      </c>
+      <c r="J11" s="54" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
+        <v>189567.97</v>
+      </c>
+      <c r="J12" s="53" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>EQB</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>EQB Inc.</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G13" s="89" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
+        <v>3018.47</v>
+      </c>
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="n"/>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>PPL</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Pembina Pipeline Corporation</t>
+        </is>
+      </c>
+      <c r="E14" s="40" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G14" s="89" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
+        <v>28518.97</v>
+      </c>
+      <c r="J14" s="53" t="inlineStr">
+        <is>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+        </is>
+      </c>
+      <c r="K14" s="36" t="n"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G15" s="89" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
+        <v>79823.21000000001</v>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="28" t="n"/>
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>CU</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>Multi-Utilities</t>
+        </is>
+      </c>
+      <c r="G16" s="89" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
+        <v>10045.65</v>
+      </c>
+      <c r="J16" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+        </is>
+      </c>
+      <c r="K16" s="28" t="n"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Canaccord Genuity Group Inc.</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G17" s="89" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
+        <v>976.67</v>
+      </c>
+      <c r="J17" s="54" t="inlineStr">
+        <is>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+        </is>
+      </c>
+      <c r="K17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="28" t="n"/>
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>BDGI</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>Badger Infrastructure Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>Construction and Engineering</t>
         </is>
       </c>
-      <c r="G8" s="89" t="n">
-        <v>1.627</v>
-      </c>
-      <c r="H8" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I8" s="91" t="n">
-        <v>2358.79</v>
-      </c>
-      <c r="J8" s="53" t="inlineStr">
-        <is>
-          <t>Bird Construction Inc provides construction services in Canada</t>
-        </is>
-      </c>
-      <c r="K8" s="36" t="n"/>
-    </row>
-    <row r="9" ht="26.4" customHeight="1">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="G18" s="89" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
+        <v>2215.94</v>
+      </c>
+      <c r="J18" s="53" t="inlineStr">
+        <is>
+          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>BDI</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Black Diamond Group Limited</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G19" s="89" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
+        <v>927.72</v>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+        </is>
+      </c>
+      <c r="K19" s="36" t="n"/>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G20" s="89" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
+        <v>65572.44</v>
+      </c>
+      <c r="J20" s="53" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+        </is>
+      </c>
+      <c r="K20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>DBM</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Doman Building Materials Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
+        <v>676.4400000000001</v>
+      </c>
+      <c r="J21" s="54" t="inlineStr">
+        <is>
+          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
+        </is>
+      </c>
+      <c r="K21" s="36" t="n"/>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>MATR</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D22" s="39" t="inlineStr">
         <is>
           <t>Mattr Corp.</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>Energy Equipment and Services</t>
         </is>
       </c>
-      <c r="G9" s="89" t="n">
+      <c r="G22" s="89" t="n">
         <v>1.172</v>
       </c>
-      <c r="H9" s="92" t="inlineStr">
+      <c r="H22" s="90" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I9" s="93" t="n">
+      <c r="I22" s="91" t="n">
         <v>555.83</v>
       </c>
-      <c r="J9" s="54" t="inlineStr">
+      <c r="J22" s="53" t="inlineStr">
         <is>
           <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
-      <c r="K9" s="28" t="n"/>
-    </row>
-    <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>DRX</t>
-        </is>
-      </c>
-      <c r="D10" s="39" t="inlineStr">
-        <is>
-          <t>ADF Group Inc.</t>
-        </is>
-      </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="K22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>NFI</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>NFI Group Inc.</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="G23" s="89" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
+        <v>1892.54</v>
+      </c>
+      <c r="J23" s="54" t="inlineStr">
+        <is>
+          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>Russel Metals Inc.</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G24" s="89" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
+        <v>2385.76</v>
+      </c>
+      <c r="J24" s="53" t="inlineStr">
+        <is>
+          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Amerigo Resources Ltd.</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>Metals and Mining</t>
         </is>
       </c>
-      <c r="G10" s="89" t="n">
-        <v>1.162</v>
-      </c>
-      <c r="H10" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I10" s="91" t="n">
-        <v>284.57</v>
-      </c>
-      <c r="J10" s="53" t="inlineStr">
-        <is>
-          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K10" s="36" t="n"/>
-    </row>
-    <row r="11" ht="20.4" customHeight="1">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>EXE</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>Extendicare Inc.</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G11" s="89" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="H11" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I11" s="93" t="n">
-        <v>2258.51</v>
-      </c>
-      <c r="J11" s="54" t="inlineStr">
-        <is>
-          <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
-        </is>
-      </c>
-      <c r="K11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="20.4" customHeight="1">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>MTL</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>Mullen Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E12" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F12" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G12" s="89" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="H12" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I12" s="91" t="n">
-        <v>1565.38</v>
-      </c>
-      <c r="J12" s="53" t="inlineStr">
-        <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K12" s="36" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>NFI</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>NFI Group Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>Machinery</t>
-        </is>
-      </c>
-      <c r="G13" s="89" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H13" s="92" t="inlineStr">
+      <c r="G25" s="89" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H25" s="92" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I13" s="93" t="n">
-        <v>1892.54</v>
-      </c>
-      <c r="J13" s="54" t="inlineStr">
-        <is>
-          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>GWO</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>Great-West Lifeco Inc.</t>
-        </is>
-      </c>
-      <c r="E14" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F14" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G14" s="89" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="H14" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I14" s="91" t="n">
-        <v>53011.04</v>
-      </c>
-      <c r="J14" s="53" t="inlineStr">
-        <is>
-          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
-        </is>
-      </c>
-      <c r="K14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>Russel Metals Inc.</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G15" s="89" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="H15" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="n">
-        <v>2385.76</v>
-      </c>
-      <c r="J15" s="54" t="inlineStr">
-        <is>
-          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="20.4" customHeight="1">
-      <c r="A16" s="28" t="n"/>
-      <c r="B16" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>KBL</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc.</t>
-        </is>
-      </c>
-      <c r="E16" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F16" s="40" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G16" s="89" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H16" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I16" s="91" t="n">
-        <v>390.27</v>
-      </c>
-      <c r="J16" s="53" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
-        </is>
-      </c>
-      <c r="K16" s="28" t="n"/>
-    </row>
-    <row r="17" ht="40.8" customHeight="1">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>BMO</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>Bank of Montreal</t>
-        </is>
-      </c>
-      <c r="E17" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G17" s="89" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H17" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I17" s="93" t="n">
-        <v>116001.23</v>
-      </c>
-      <c r="J17" s="54" t="inlineStr">
-        <is>
-          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
-        </is>
-      </c>
-      <c r="K17" s="36" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="28" t="n"/>
-      <c r="B18" s="48" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>POW</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="n">
-        <v>38174.66</v>
-      </c>
-      <c r="J18" s="53" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
-        </is>
-      </c>
-      <c r="K18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="30.6" customHeight="1">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="49" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>Amerigo Resources Ltd.</t>
-        </is>
-      </c>
-      <c r="E19" s="32" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G19" s="89" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="H19" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I19" s="93" t="n">
+      <c r="I25" s="93" t="n">
         <v>681.6799999999999</v>
       </c>
-      <c r="J19" s="54" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
-      <c r="K19" s="36" t="n"/>
-    </row>
-    <row r="20" ht="30.6" customHeight="1">
-      <c r="A20" s="28" t="n"/>
-      <c r="B20" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F20" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I20" s="91" t="n">
-        <v>41467.31</v>
-      </c>
-      <c r="J20" s="53" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
-        </is>
-      </c>
-      <c r="K20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="30.6" customHeight="1">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="49" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>CNR</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G21" s="89" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="H21" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I21" s="93" t="n">
-        <v>72839.50999999999</v>
-      </c>
-      <c r="J21" s="54" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K21" s="36" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Imperial Bank of Commerce</t>
-        </is>
-      </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F22" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H22" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I22" s="91" t="n">
-        <v>101497.85</v>
-      </c>
-      <c r="J22" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="n">
-        <v>16</v>
-      </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F23" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="H23" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I23" s="93" t="n">
-        <v>189567.97</v>
-      </c>
-      <c r="J23" s="54" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>EQB</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>EQB Inc.</t>
-        </is>
-      </c>
-      <c r="E24" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F24" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G24" s="89" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="H24" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I24" s="91" t="n">
-        <v>3018.47</v>
-      </c>
-      <c r="J24" s="53" t="inlineStr">
-        <is>
-          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
-        </is>
-      </c>
-      <c r="K24" s="36" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="n">
-        <v>18</v>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>PPL</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>Pembina Pipeline Corporation</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F25" s="32" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G25" s="89" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I25" s="93" t="n">
-        <v>28518.97</v>
-      </c>
-      <c r="J25" s="54" t="inlineStr">
-        <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
-        </is>
-      </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="20.4" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="n">
-        <v>19</v>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
@@ -2352,653 +2410,681 @@
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="49" t="n">
-        <v>20</v>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
+          <t>DXT</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Dexterra Group Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G27" s="89" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
+        <v>576.85</v>
+      </c>
+      <c r="J27" s="54" t="inlineStr">
+        <is>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+        </is>
+      </c>
+      <c r="K27" s="36" t="n"/>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>BNS</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>The Bank of Nova Scotia</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G28" s="89" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
+        <v>100391.39</v>
+      </c>
+      <c r="J28" s="53" t="inlineStr">
+        <is>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+        </is>
+      </c>
+      <c r="K28" s="28" t="n"/>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="36" t="n"/>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>TOY</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Spin Master Corp.</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Leisure Products</t>
+        </is>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
+        <v>1330.28</v>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+        </is>
+      </c>
+      <c r="K29" s="36" t="n"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="36" t="n"/>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>DFY</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>Definity Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G30" s="89" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
+        <v>6226.62</v>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Bird Construction Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>Construction and Engineering</t>
+        </is>
+      </c>
+      <c r="G31" s="89" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="H31" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I31" s="93" t="n">
+        <v>2358.79</v>
+      </c>
+      <c r="J31" s="54" t="inlineStr">
+        <is>
+          <t>Bird Construction Inc provides construction services in Canada</t>
+        </is>
+      </c>
+      <c r="K31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="36" t="n"/>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>DRX</t>
+        </is>
+      </c>
+      <c r="D32" s="39" t="inlineStr">
+        <is>
+          <t>ADF Group Inc.</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>Metals and Mining</t>
+        </is>
+      </c>
+      <c r="G32" s="89" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="H32" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I32" s="91" t="n">
+        <v>284.57</v>
+      </c>
+      <c r="J32" s="53" t="inlineStr">
+        <is>
+          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K32" s="36" t="n"/>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>KBL</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>K-Bro Linen Inc.</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G33" s="89" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H33" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I33" s="93" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="J33" s="54" t="inlineStr">
+        <is>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+        </is>
+      </c>
+      <c r="K33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="36" t="n"/>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>BMO</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>Bank of Montreal</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G34" s="89" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
+        <v>116001.23</v>
+      </c>
+      <c r="J34" s="53" t="inlineStr">
+        <is>
+          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
+        </is>
+      </c>
+      <c r="K34" s="36" t="n"/>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>SLF</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Sun Life Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F35" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G35" s="89" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
+        <v>41467.31</v>
+      </c>
+      <c r="J35" s="54" t="inlineStr">
+        <is>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
+        </is>
+      </c>
+      <c r="K35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="36" t="n"/>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>CNR</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>Canadian National Railway Company</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G36" s="89" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
+        <v>72839.50999999999</v>
+      </c>
+      <c r="J36" s="53" t="inlineStr">
+        <is>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce</t>
+        </is>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G37" s="89" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
+        <v>101497.85</v>
+      </c>
+      <c r="J37" s="54" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="36" t="n"/>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="inlineStr">
+        <is>
           <t>RY</t>
         </is>
       </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="D38" s="39" t="inlineStr">
         <is>
           <t>Royal Bank of Canada</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E38" s="40" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="G27" s="89" t="n">
+      <c r="G38" s="89" t="n">
         <v>0.297</v>
       </c>
-      <c r="H27" s="92" t="inlineStr">
+      <c r="H38" s="90" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I27" s="93" t="n">
+      <c r="I38" s="91" t="n">
         <v>275998.42</v>
       </c>
-      <c r="J27" s="54" t="inlineStr">
+      <c r="J38" s="53" t="inlineStr">
         <is>
           <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
-      <c r="K27" s="36" t="n"/>
-    </row>
-    <row r="28" ht="20.4" customHeight="1">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="48" t="n">
-        <v>21</v>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G28" s="89" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H28" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I28" s="91" t="n">
-        <v>79823.21000000001</v>
-      </c>
-      <c r="J28" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
-        </is>
-      </c>
-      <c r="K28" s="28" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="36" t="n"/>
-      <c r="B29" s="49" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>CU</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>Multi-Utilities</t>
-        </is>
-      </c>
-      <c r="G29" s="89" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I29" s="93" t="n">
-        <v>10045.65</v>
-      </c>
-      <c r="J29" s="54" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
-        </is>
-      </c>
-      <c r="K29" s="36" t="n"/>
-    </row>
-    <row r="30" ht="30.6" customHeight="1">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="n">
-        <v>23</v>
-      </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>Canaccord Genuity Group Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
+      <c r="K38" s="36" t="n"/>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>IAG</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>iA Financial Corporation Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G30" s="89" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="H30" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I30" s="91" t="n">
-        <v>976.67</v>
-      </c>
-      <c r="J30" s="53" t="inlineStr">
-        <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
-        </is>
-      </c>
-      <c r="K30" s="36" t="n"/>
-    </row>
-    <row r="31" ht="30.6" customHeight="1">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="n">
-        <v>24</v>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>BDGI</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>Badger Infrastructure Solutions Ltd.</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>Construction and Engineering</t>
-        </is>
-      </c>
-      <c r="G31" s="89" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I31" s="93" t="n">
-        <v>2215.94</v>
-      </c>
-      <c r="J31" s="54" t="inlineStr">
-        <is>
-          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n">
-        <v>25</v>
-      </c>
-      <c r="C32" s="38" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="D32" s="39" t="inlineStr">
-        <is>
-          <t>iA Financial Corporation Inc.</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G32" s="89" t="n">
+      <c r="G39" s="89" t="n">
         <v>0.238</v>
       </c>
-      <c r="H32" s="90" t="inlineStr">
+      <c r="H39" s="92" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I32" s="91" t="n">
+      <c r="I39" s="93" t="n">
         <v>11282.66</v>
       </c>
-      <c r="J32" s="53" t="inlineStr">
+      <c r="J39" s="54" t="inlineStr">
         <is>
           <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
-      <c r="K32" s="36" t="n"/>
-    </row>
-    <row r="33" ht="20.4" customHeight="1">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n">
-        <v>26</v>
-      </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>DXT</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>Dexterra Group Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G33" s="89" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="H33" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I33" s="93" t="n">
-        <v>576.85</v>
-      </c>
-      <c r="J33" s="54" t="inlineStr">
-        <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="30.6" customHeight="1">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" s="38" t="inlineStr">
-        <is>
-          <t>BNS</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>The Bank of Nova Scotia</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G34" s="89" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="H34" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I34" s="91" t="n">
-        <v>100391.39</v>
-      </c>
-      <c r="J34" s="53" t="inlineStr">
-        <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
-        </is>
-      </c>
-      <c r="K34" s="36" t="n"/>
-    </row>
-    <row r="35" ht="30.6" customHeight="1">
-      <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="n">
-        <v>28</v>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>BDI</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>Black Diamond Group Limited</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G35" s="89" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H35" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I35" s="93" t="n">
-        <v>927.72</v>
-      </c>
-      <c r="J35" s="54" t="inlineStr">
-        <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="40.8" customHeight="1">
-      <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>MFC</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F36" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G36" s="89" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="H36" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I36" s="91" t="n">
-        <v>65572.44</v>
-      </c>
-      <c r="J36" s="53" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
-        </is>
-      </c>
-      <c r="K36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="K39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="36" t="n"/>
+      <c r="B40" s="106" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C40" s="107" t="inlineStr">
         <is>
           <t>IFP</t>
         </is>
       </c>
-      <c r="D37" s="31" t="inlineStr">
+      <c r="D40" s="108" t="inlineStr">
         <is>
           <t>Interfor Corporation</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Paper and Forest Products</t>
         </is>
       </c>
-      <c r="G37" s="89" t="n">
+      <c r="G40" s="110" t="n">
         <v>0.2</v>
       </c>
-      <c r="H37" s="92" t="inlineStr">
+      <c r="H40" s="111" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I37" s="93" t="n">
+      <c r="I40" s="112" t="n">
         <v>501.72</v>
       </c>
-      <c r="J37" s="54" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="20.4" customHeight="1">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n">
-        <v>31</v>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>TOY</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>Spin Master Corp.</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>Leisure Products</t>
-        </is>
-      </c>
-      <c r="G38" s="89" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="H38" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I38" s="91" t="n">
-        <v>1330.28</v>
-      </c>
-      <c r="J38" s="53" t="inlineStr">
-        <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
-        </is>
-      </c>
-      <c r="K38" s="36" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>DBM</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>Doman Building Materials Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G39" s="89" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="H39" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I39" s="93" t="n">
-        <v>676.4400000000001</v>
-      </c>
-      <c r="J39" s="54" t="inlineStr">
-        <is>
-          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="n"/>
-    </row>
-    <row r="40" ht="20.4" customHeight="1">
-      <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="n">
-        <v>33</v>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
-        <is>
-          <t>DFY</t>
-        </is>
-      </c>
-      <c r="D40" s="108" t="inlineStr">
-        <is>
-          <t>Definity Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E40" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F40" s="109" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G40" s="110" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H40" s="111" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I40" s="112" t="n">
-        <v>6226.62</v>
-      </c>
-      <c r="J40" s="113" t="inlineStr">
-        <is>
-          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
-        </is>
-      </c>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="15.6" customHeight="1" thickBot="1">
+    <row r="41" ht="8" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="69" t="n"/>
-      <c r="C41" s="70" t="n"/>
-      <c r="D41" s="71" t="n"/>
-      <c r="E41" s="72" t="n"/>
-      <c r="F41" s="72" t="n"/>
-      <c r="G41" s="94" t="n"/>
-      <c r="H41" s="95" t="n"/>
-      <c r="I41" s="96" t="n"/>
-      <c r="J41" s="74" t="n"/>
+      <c r="B41" s="114" t="n"/>
+      <c r="C41" s="115" t="n"/>
+      <c r="D41" s="116" t="n"/>
+      <c r="E41" s="117" t="n"/>
+      <c r="F41" s="117" t="n"/>
+      <c r="G41" s="118" t="n"/>
+      <c r="H41" s="119" t="n"/>
+      <c r="I41" s="120" t="n"/>
+      <c r="J41" s="121" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="114" t="inlineStr">
+      <c r="B42" s="122" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="115" t="n"/>
-      <c r="D42" s="115" t="n"/>
-      <c r="E42" s="115" t="n"/>
-      <c r="F42" s="115" t="n"/>
-      <c r="G42" s="115" t="n"/>
-      <c r="H42" s="115" t="n"/>
-      <c r="I42" s="115" t="n"/>
-      <c r="J42" s="115" t="n"/>
+      <c r="C42" s="123" t="n"/>
+      <c r="D42" s="123" t="n"/>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="123" t="n"/>
+      <c r="G42" s="123" t="n"/>
+      <c r="H42" s="123" t="n"/>
+      <c r="I42" s="123" t="n"/>
+      <c r="J42" s="123" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="116" t="inlineStr">
+      <c r="B43" s="124" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="117" t="n"/>
-      <c r="D43" s="117" t="n"/>
-      <c r="E43" s="117" t="n"/>
-      <c r="F43" s="117" t="n"/>
-      <c r="G43" s="117" t="n"/>
-      <c r="H43" s="117" t="n"/>
-      <c r="I43" s="117" t="n"/>
-      <c r="J43" s="117" t="n"/>
+      <c r="C43" s="125" t="n"/>
+      <c r="D43" s="125" t="n"/>
+      <c r="E43" s="125" t="n"/>
+      <c r="F43" s="125" t="n"/>
+      <c r="G43" s="125" t="n"/>
+      <c r="H43" s="125" t="n"/>
+      <c r="I43" s="125" t="n"/>
+      <c r="J43" s="125" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="12" customHeight="1">
@@ -3083,7 +3169,7 @@
   <mergeCells count="4">
     <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="B42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G40">
@@ -4064,10 +4150,10 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84" t="n">
-        <v>46224.86266495839</v>
-      </c>
-      <c r="J2" s="83" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="84" t="n">
+        <v>46224.87725170761</v>
+      </c>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="44" t="n"/>
@@ -4118,21 +4204,17 @@
       <c r="F6" s="24" t="n"/>
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="24" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="B7" s="27" t="inlineStr"/>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -4175,10 +4257,12 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="n">
-        <v>1</v>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
@@ -4218,10 +4302,12 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="n">
-        <v>2</v>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
@@ -4261,1384 +4347,1446 @@
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="20.4" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="n">
-        <v>3</v>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
+          <t>JBHT</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>J.B. Hunt Transport Services Inc.</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
+        <v>26566.73</v>
+      </c>
+      <c r="J10" s="53" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K10" s="36" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Globe Life Inc.</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G11" s="89" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
+        <v>12644.53</v>
+      </c>
+      <c r="J11" s="54" t="inlineStr">
+        <is>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>WELL</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>Welltower Inc.</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>Health Care REITs</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
+        <v>148209.56</v>
+      </c>
+      <c r="J12" s="53" t="inlineStr">
+        <is>
+          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+        </is>
+      </c>
+      <c r="K12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G13" s="89" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
+        <v>125211.85</v>
+      </c>
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="n"/>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>The Travelers Companies Inc.</t>
+        </is>
+      </c>
+      <c r="E14" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G14" s="89" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
+        <v>64533.41</v>
+      </c>
+      <c r="J14" s="53" t="inlineStr">
+        <is>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+        </is>
+      </c>
+      <c r="K14" s="36" t="n"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="G15" s="89" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
+        <v>39380.19</v>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Healthpeak Properties Inc.</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>Health Care REITs</t>
+        </is>
+      </c>
+      <c r="G16" s="89" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
+        <v>14353.95</v>
+      </c>
+      <c r="J16" s="53" t="inlineStr">
+        <is>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+        </is>
+      </c>
+      <c r="K16" s="36" t="n"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="28" t="n"/>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>GWW</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>W.W. Grainger Inc.</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G17" s="89" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
+        <v>62147.38</v>
+      </c>
+      <c r="J17" s="54" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="n"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G18" s="89" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
+        <v>158667.48</v>
+      </c>
+      <c r="J18" s="53" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+        </is>
+      </c>
+      <c r="K18" s="36" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="28" t="n"/>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>PFG</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Principal Financial Group Inc.</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G19" s="89" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
+        <v>23624.19</v>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="n"/>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Block Inc.</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G20" s="89" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
+        <v>40474.89</v>
+      </c>
+      <c r="J20" s="53" t="inlineStr">
+        <is>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K20" s="36" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="28" t="n"/>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
+        <v>388502.86</v>
+      </c>
+      <c r="J21" s="54" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G22" s="89" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="n">
+        <v>13320.91</v>
+      </c>
+      <c r="J22" s="53" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+        </is>
+      </c>
+      <c r="K22" s="36" t="n"/>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Citizens Financial Group Inc.</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G23" s="89" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
+        <v>27585.86</v>
+      </c>
+      <c r="J23" s="54" t="inlineStr">
+        <is>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="inlineStr">
+        <is>
+          <t>FITB</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>Fifth Third Bancorp</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G24" s="89" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
+        <v>47955.66</v>
+      </c>
+      <c r="J24" s="53" t="inlineStr">
+        <is>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+        </is>
+      </c>
+      <c r="K24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Monster Beverage Corporation</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="G25" s="89" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I25" s="93" t="n">
+        <v>89144.46000000001</v>
+      </c>
+      <c r="J25" s="54" t="inlineStr">
+        <is>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="36" t="n"/>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="inlineStr">
+        <is>
+          <t>PRU</t>
+        </is>
+      </c>
+      <c r="D26" s="39" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E26" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G26" s="89" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="H26" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="n">
+        <v>36717.82</v>
+      </c>
+      <c r="J26" s="53" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+        </is>
+      </c>
+      <c r="K26" s="36" t="n"/>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>EXPD</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Air Freight and Logistics</t>
+        </is>
+      </c>
+      <c r="G27" s="89" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
+        <v>21453.67</v>
+      </c>
+      <c r="J27" s="54" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="n"/>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="36" t="n"/>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G28" s="89" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
+        <v>612046.08</v>
+      </c>
+      <c r="J28" s="53" t="inlineStr">
+        <is>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K28" s="36" t="n"/>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Paychex Inc.</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
+        <v>36258.68</v>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
+        </is>
+      </c>
+      <c r="K29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="36" t="n"/>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>BXP</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>BXP Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Office REITs</t>
+        </is>
+      </c>
+      <c r="G30" s="89" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
+        <v>11826.25</v>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G10" s="89" t="n">
+      <c r="G31" s="89" t="n">
         <v>0.839</v>
       </c>
-      <c r="H10" s="90" t="inlineStr">
+      <c r="H31" s="92" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I10" s="91" t="n">
+      <c r="I31" s="93" t="n">
         <v>77721.12</v>
       </c>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="J31" s="54" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
-      <c r="K10" s="36" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="K31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="36" t="n"/>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>VLO</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D32" s="39" t="inlineStr">
         <is>
           <t>Valero Energy Corporation</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E32" s="40" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G11" s="89" t="n">
+      <c r="G32" s="89" t="n">
         <v>0.701</v>
       </c>
-      <c r="H11" s="92" t="inlineStr">
+      <c r="H32" s="90" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I11" s="93" t="n">
+      <c r="I32" s="91" t="n">
         <v>77190.64999999999</v>
       </c>
-      <c r="J11" s="54" t="inlineStr">
+      <c r="J32" s="53" t="inlineStr">
         <is>
           <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
-      <c r="K11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="K32" s="36" t="n"/>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>State Street Corporation</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="G12" s="89" t="n">
+      <c r="G33" s="89" t="n">
         <v>0.471</v>
       </c>
-      <c r="H12" s="90" t="inlineStr">
+      <c r="H33" s="92" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I12" s="91" t="n">
+      <c r="I33" s="93" t="n">
         <v>44725.83</v>
       </c>
-      <c r="J12" s="53" t="inlineStr">
+      <c r="J33" s="54" t="inlineStr">
         <is>
           <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
-      <c r="K12" s="36" t="n"/>
-    </row>
-    <row r="13" ht="20.4" customHeight="1">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>JBHT</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>J.B. Hunt Transport Services Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="K33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="36" t="n"/>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon Corporation</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G34" s="89" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
+        <v>96186.41</v>
+      </c>
+      <c r="J34" s="53" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K34" s="36" t="n"/>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F35" s="32" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
+        </is>
+      </c>
+      <c r="G35" s="89" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
+        <v>4309578.68</v>
+      </c>
+      <c r="J35" s="54" t="inlineStr">
+        <is>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+        </is>
+      </c>
+      <c r="K35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="36" t="n"/>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>Best Buy Co. Inc.</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G36" s="89" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
+        <v>16078.79</v>
+      </c>
+      <c r="J36" s="53" t="inlineStr">
+        <is>
+          <t>Best Buy Co</t>
+        </is>
+      </c>
+      <c r="K36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>NTRS</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Northern Trust Corporation</t>
+        </is>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G37" s="89" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
+        <v>30713.22</v>
+      </c>
+      <c r="J37" s="54" t="inlineStr">
+        <is>
+          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="36" t="n"/>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>MetLife Inc.</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G38" s="89" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H38" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="n">
+        <v>55851.6</v>
+      </c>
+      <c r="J38" s="53" t="inlineStr">
+        <is>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+        </is>
+      </c>
+      <c r="K38" s="36" t="n"/>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>The Goldman Sachs Group Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G39" s="89" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="H39" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I39" s="93" t="n">
+        <v>308648.81</v>
+      </c>
+      <c r="J39" s="54" t="inlineStr">
+        <is>
+          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
+        </is>
+      </c>
+      <c r="K39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="36" t="n"/>
+      <c r="B40" s="106" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C40" s="107" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D40" s="108" t="inlineStr">
+        <is>
+          <t>CSX Corporation</t>
+        </is>
+      </c>
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
-      <c r="G13" s="89" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="H13" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I13" s="93" t="n">
-        <v>26566.73</v>
-      </c>
-      <c r="J13" s="54" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="n"/>
-    </row>
-    <row r="14" ht="40.8" customHeight="1">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>CSX</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>CSX Corporation</t>
-        </is>
-      </c>
-      <c r="E14" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F14" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G14" s="89" t="n">
+      <c r="G40" s="110" t="n">
         <v>0.37</v>
       </c>
-      <c r="H14" s="90" t="inlineStr">
+      <c r="H40" s="111" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I14" s="91" t="n">
+      <c r="I40" s="112" t="n">
         <v>86617.14</v>
       </c>
-      <c r="J14" s="53" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
-      <c r="K14" s="36" t="n"/>
-    </row>
-    <row r="15" ht="30.6" customHeight="1">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>The Bank of New York Mellon Corporation</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G15" s="89" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="H15" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="n">
-        <v>96186.41</v>
-      </c>
-      <c r="J15" s="54" t="inlineStr">
-        <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>Globe Life Inc.</t>
-        </is>
-      </c>
-      <c r="E16" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F16" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G16" s="89" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="H16" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I16" s="91" t="n">
-        <v>12644.53</v>
-      </c>
-      <c r="J16" s="53" t="inlineStr">
-        <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
-        </is>
-      </c>
-      <c r="K16" s="36" t="n"/>
-    </row>
-    <row r="17" ht="30.6" customHeight="1">
-      <c r="A17" s="28" t="n"/>
-      <c r="B17" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>WELL</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>Welltower Inc.</t>
-        </is>
-      </c>
-      <c r="E17" s="32" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>Health Care REITs</t>
-        </is>
-      </c>
-      <c r="G17" s="89" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="H17" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I17" s="93" t="n">
-        <v>148209.56</v>
-      </c>
-      <c r="J17" s="54" t="inlineStr">
-        <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="20.4" customHeight="1">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="48" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="n">
-        <v>125211.85</v>
-      </c>
-      <c r="J18" s="53" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
-        </is>
-      </c>
-      <c r="K18" s="36" t="n"/>
-    </row>
-    <row r="19" ht="20.4" customHeight="1">
-      <c r="A19" s="28" t="n"/>
-      <c r="B19" s="49" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>The Travelers Companies Inc.</t>
-        </is>
-      </c>
-      <c r="E19" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G19" s="89" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="H19" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I19" s="93" t="n">
-        <v>64533.41</v>
-      </c>
-      <c r="J19" s="54" t="inlineStr">
-        <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
-        </is>
-      </c>
-      <c r="K19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F20" s="40" t="inlineStr">
-        <is>
-          <t>Technology Hardware Storage and Peripherals</t>
-        </is>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I20" s="91" t="n">
-        <v>4309578.68</v>
-      </c>
-      <c r="J20" s="53" t="inlineStr">
-        <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
-        </is>
-      </c>
-      <c r="K20" s="36" t="n"/>
-    </row>
-    <row r="21" ht="20.4" customHeight="1">
-      <c r="A21" s="28" t="n"/>
-      <c r="B21" s="49" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>BBY</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Best Buy Co. Inc.</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>Specialty Retail</t>
-        </is>
-      </c>
-      <c r="G21" s="89" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="H21" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I21" s="93" t="n">
-        <v>16078.79</v>
-      </c>
-      <c r="J21" s="54" t="inlineStr">
-        <is>
-          <t>Best Buy Co</t>
-        </is>
-      </c>
-      <c r="K21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="30.6" customHeight="1">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>Archer-Daniels-Midland Company</t>
-        </is>
-      </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F22" s="40" t="inlineStr">
-        <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H22" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I22" s="91" t="n">
-        <v>39380.19</v>
-      </c>
-      <c r="J22" s="53" t="inlineStr">
-        <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
-        </is>
-      </c>
-      <c r="K22" s="36" t="n"/>
-    </row>
-    <row r="23" ht="20.4" customHeight="1">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="n">
-        <v>16</v>
-      </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>GWW</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>W.W. Grainger Inc.</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F23" s="32" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="H23" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I23" s="93" t="n">
-        <v>62147.38</v>
-      </c>
-      <c r="J23" s="54" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>Healthpeak Properties Inc.</t>
-        </is>
-      </c>
-      <c r="E24" s="40" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F24" s="40" t="inlineStr">
-        <is>
-          <t>Health Care REITs</t>
-        </is>
-      </c>
-      <c r="G24" s="89" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="H24" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I24" s="91" t="n">
-        <v>14353.95</v>
-      </c>
-      <c r="J24" s="53" t="inlineStr">
-        <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
-        </is>
-      </c>
-      <c r="K24" s="36" t="n"/>
-    </row>
-    <row r="25" ht="30.6" customHeight="1">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="n">
-        <v>18</v>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F25" s="32" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G25" s="89" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I25" s="93" t="n">
-        <v>158667.48</v>
-      </c>
-      <c r="J25" s="54" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
-        </is>
-      </c>
-      <c r="K25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="30.6" customHeight="1">
-      <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="n">
-        <v>19</v>
-      </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>NTRS</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
-        <is>
-          <t>Northern Trust Corporation</t>
-        </is>
-      </c>
-      <c r="E26" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F26" s="40" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G26" s="89" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="H26" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I26" s="91" t="n">
-        <v>30713.22</v>
-      </c>
-      <c r="J26" s="53" t="inlineStr">
-        <is>
-          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
-        </is>
-      </c>
-      <c r="K26" s="36" t="n"/>
-    </row>
-    <row r="27" ht="30.6" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="C27" s="30" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>MetLife Inc.</t>
-        </is>
-      </c>
-      <c r="E27" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F27" s="32" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G27" s="89" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H27" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I27" s="93" t="n">
-        <v>55851.6</v>
-      </c>
-      <c r="J27" s="54" t="inlineStr">
-        <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
-        </is>
-      </c>
-      <c r="K27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="36" t="n"/>
-      <c r="B28" s="48" t="n">
-        <v>21</v>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>Principal Financial Group Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G28" s="89" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="H28" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I28" s="91" t="n">
-        <v>23624.19</v>
-      </c>
-      <c r="J28" s="53" t="inlineStr">
-        <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
-        </is>
-      </c>
-      <c r="K28" s="36" t="n"/>
-    </row>
-    <row r="29" ht="20.4" customHeight="1">
-      <c r="A29" s="28" t="n"/>
-      <c r="B29" s="49" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Block Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G29" s="89" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I29" s="93" t="n">
-        <v>40474.89</v>
-      </c>
-      <c r="J29" s="54" t="inlineStr">
-        <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K29" s="28" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="n">
-        <v>23</v>
-      </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F30" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G30" s="89" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="H30" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I30" s="91" t="n">
-        <v>388502.86</v>
-      </c>
-      <c r="J30" s="53" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
-        </is>
-      </c>
-      <c r="K30" s="36" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="n">
-        <v>24</v>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>The Goldman Sachs Group Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G31" s="89" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I31" s="93" t="n">
-        <v>308648.81</v>
-      </c>
-      <c r="J31" s="54" t="inlineStr">
-        <is>
-          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n">
-        <v>25</v>
-      </c>
-      <c r="C32" s="38" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D32" s="39" t="inlineStr">
-        <is>
-          <t>Everest Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F32" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G32" s="89" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H32" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I32" s="91" t="n">
-        <v>13320.91</v>
-      </c>
-      <c r="J32" s="53" t="inlineStr">
-        <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
-        </is>
-      </c>
-      <c r="K32" s="36" t="n"/>
-    </row>
-    <row r="33" ht="20.4" customHeight="1">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n">
-        <v>26</v>
-      </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>CFG</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>Citizens Financial Group Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G33" s="89" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="H33" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I33" s="93" t="n">
-        <v>27585.86</v>
-      </c>
-      <c r="J33" s="54" t="inlineStr">
-        <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" s="38" t="inlineStr">
-        <is>
-          <t>FITB</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>Fifth Third Bancorp</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G34" s="89" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H34" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I34" s="91" t="n">
-        <v>47955.66</v>
-      </c>
-      <c r="J34" s="53" t="inlineStr">
-        <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
-        </is>
-      </c>
-      <c r="K34" s="36" t="n"/>
-    </row>
-    <row r="35" ht="20.4" customHeight="1">
-      <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="n">
-        <v>28</v>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>MNST</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>Monster Beverage Corporation</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="G35" s="89" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="H35" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I35" s="93" t="n">
-        <v>89144.46000000001</v>
-      </c>
-      <c r="J35" s="54" t="inlineStr">
-        <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="30.6" customHeight="1">
-      <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>PRU</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>Prudential Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F36" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G36" s="89" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="H36" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I36" s="91" t="n">
-        <v>36717.82</v>
-      </c>
-      <c r="J36" s="53" t="inlineStr">
-        <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
-        </is>
-      </c>
-      <c r="K36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="30.6" customHeight="1">
-      <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>EXPD</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>Expeditors International of Washington Inc.</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F37" s="32" t="inlineStr">
-        <is>
-          <t>Air Freight and Logistics</t>
-        </is>
-      </c>
-      <c r="G37" s="89" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="H37" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I37" s="93" t="n">
-        <v>21453.67</v>
-      </c>
-      <c r="J37" s="54" t="inlineStr">
-        <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="20.4" customHeight="1">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n">
-        <v>31</v>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>Visa Inc.</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G38" s="89" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="H38" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I38" s="91" t="n">
-        <v>612046.08</v>
-      </c>
-      <c r="J38" s="53" t="inlineStr">
-        <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K38" s="36" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>Paychex Inc.</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>Professional Services</t>
-        </is>
-      </c>
-      <c r="G39" s="89" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H39" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I39" s="93" t="n">
-        <v>36258.68</v>
-      </c>
-      <c r="J39" s="54" t="inlineStr">
-        <is>
-          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="n">
-        <v>33</v>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
-        <is>
-          <t>BXP</t>
-        </is>
-      </c>
-      <c r="D40" s="108" t="inlineStr">
-        <is>
-          <t>BXP Inc.</t>
-        </is>
-      </c>
-      <c r="E40" s="109" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F40" s="109" t="inlineStr">
-        <is>
-          <t>Office REITs</t>
-        </is>
-      </c>
-      <c r="G40" s="110" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="H40" s="111" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I40" s="112" t="n">
-        <v>11826.25</v>
-      </c>
-      <c r="J40" s="113" t="inlineStr">
-        <is>
-          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
-        </is>
-      </c>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="30.6" customHeight="1">
+    <row r="41" ht="8" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="92" t="n"/>
-      <c r="I41" s="93" t="n"/>
-      <c r="J41" s="54" t="n"/>
+      <c r="B41" s="114" t="n"/>
+      <c r="C41" s="115" t="n"/>
+      <c r="D41" s="116" t="n"/>
+      <c r="E41" s="117" t="n"/>
+      <c r="F41" s="117" t="n"/>
+      <c r="G41" s="118" t="n"/>
+      <c r="H41" s="119" t="n"/>
+      <c r="I41" s="120" t="n"/>
+      <c r="J41" s="121" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="114" t="inlineStr">
+      <c r="B42" s="122" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="115" t="n"/>
-      <c r="D42" s="115" t="n"/>
-      <c r="E42" s="115" t="n"/>
-      <c r="F42" s="115" t="n"/>
-      <c r="G42" s="115" t="n"/>
-      <c r="H42" s="115" t="n"/>
-      <c r="I42" s="115" t="n"/>
-      <c r="J42" s="115" t="n"/>
+      <c r="C42" s="123" t="n"/>
+      <c r="D42" s="123" t="n"/>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="123" t="n"/>
+      <c r="G42" s="123" t="n"/>
+      <c r="H42" s="123" t="n"/>
+      <c r="I42" s="123" t="n"/>
+      <c r="J42" s="123" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="116" t="inlineStr">
+      <c r="B43" s="124" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="117" t="n"/>
-      <c r="D43" s="117" t="n"/>
-      <c r="E43" s="117" t="n"/>
-      <c r="F43" s="117" t="n"/>
-      <c r="G43" s="117" t="n"/>
-      <c r="H43" s="117" t="n"/>
-      <c r="I43" s="117" t="n"/>
-      <c r="J43" s="117" t="n"/>
+      <c r="C43" s="125" t="n"/>
+      <c r="D43" s="125" t="n"/>
+      <c r="E43" s="125" t="n"/>
+      <c r="F43" s="125" t="n"/>
+      <c r="G43" s="125" t="n"/>
+      <c r="H43" s="125" t="n"/>
+      <c r="I43" s="125" t="n"/>
+      <c r="J43" s="125" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1">
@@ -5723,7 +5871,7 @@
   <mergeCells count="4">
     <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="B42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G40">

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -216,6 +216,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="FFC67A29"/>
       <sz val="10"/>
     </font>
@@ -225,7 +230,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -306,6 +311,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E86DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8E44AD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0392B"/>
       </patternFill>
     </fill>
     <fill>
@@ -507,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -776,7 +796,16 @@
     <xf numFmtId="166" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -824,14 +853,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1387,7 +1416,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.87725170761</v>
+        <v>46224.90155205015</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1413,7 +1442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.44140625" customWidth="1" style="11" min="2" max="2"/>
+    <col width="8.5" customWidth="1" style="11" min="2" max="2"/>
     <col width="10" customWidth="1" style="14" min="3" max="3"/>
     <col width="26" customWidth="1" style="15" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
@@ -1450,7 +1479,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46224.87725170761</v>
+        <v>46224.90155205015</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -1555,11 +1584,11 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B8" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
@@ -1600,11 +1629,11 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B9" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -1645,11 +1674,11 @@
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="67" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B10" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
@@ -1690,11 +1719,11 @@
       </c>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B11" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -1735,11 +1764,11 @@
       </c>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="67" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B12" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C12" s="38" t="inlineStr">
@@ -1780,11 +1809,11 @@
       </c>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B13" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -1825,11 +1854,11 @@
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B14" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
@@ -1870,11 +1899,11 @@
       </c>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="67" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B15" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
@@ -1915,11 +1944,11 @@
       </c>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="67" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B16" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
@@ -1960,11 +1989,11 @@
       </c>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="67" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B17" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
@@ -2005,11 +2034,11 @@
       </c>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="67" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B18" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
@@ -2050,11 +2079,11 @@
       </c>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B19" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
@@ -2095,11 +2124,11 @@
       </c>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="67" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B20" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
@@ -2140,11 +2169,11 @@
       </c>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="67" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B21" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
@@ -2185,11 +2214,11 @@
       </c>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="84" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B22" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
@@ -2230,11 +2259,11 @@
       </c>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="50" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B23" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
@@ -2275,11 +2304,11 @@
       </c>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B24" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
@@ -2320,11 +2349,11 @@
       </c>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="50" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B25" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
@@ -2365,11 +2394,11 @@
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="45" customHeight="1">
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B26" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
@@ -2410,11 +2439,11 @@
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="50" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B27" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
@@ -2455,11 +2484,11 @@
       </c>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="67" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B28" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
@@ -2500,11 +2529,11 @@
       </c>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="45" customHeight="1">
+    <row r="29" ht="67" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B29" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
@@ -2545,11 +2574,11 @@
       </c>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="45" customHeight="1">
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B30" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
@@ -2590,11 +2619,11 @@
       </c>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B31" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
@@ -2635,11 +2664,11 @@
       </c>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32" ht="50" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B32" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C32" s="38" t="inlineStr">
@@ -2680,11 +2709,11 @@
       </c>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="67" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B33" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
@@ -2725,11 +2754,11 @@
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B34" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
@@ -2770,11 +2799,11 @@
       </c>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="101" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B35" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
@@ -2815,11 +2844,11 @@
       </c>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="67" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B36" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
@@ -2860,11 +2889,11 @@
       </c>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="84" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B37" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
@@ -2905,11 +2934,11 @@
       </c>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="45" customHeight="1">
+    <row r="38" ht="50" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B38" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C38" s="38" t="inlineStr">
@@ -2950,11 +2979,11 @@
       </c>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="50" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B39" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
@@ -2995,45 +3024,45 @@
       </c>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="67" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
+      <c r="B40" s="109" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C40" s="110" t="inlineStr">
         <is>
           <t>IFP</t>
         </is>
       </c>
-      <c r="D40" s="108" t="inlineStr">
+      <c r="D40" s="111" t="inlineStr">
         <is>
           <t>Interfor Corporation</t>
         </is>
       </c>
-      <c r="E40" s="109" t="inlineStr">
+      <c r="E40" s="112" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F40" s="109" t="inlineStr">
+      <c r="F40" s="112" t="inlineStr">
         <is>
           <t>Paper and Forest Products</t>
         </is>
       </c>
-      <c r="G40" s="110" t="n">
+      <c r="G40" s="113" t="n">
         <v>0.2</v>
       </c>
-      <c r="H40" s="111" t="inlineStr">
+      <c r="H40" s="114" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I40" s="112" t="n">
+      <c r="I40" s="115" t="n">
         <v>501.72</v>
       </c>
-      <c r="J40" s="113" t="inlineStr">
+      <c r="J40" s="116" t="inlineStr">
         <is>
           <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
@@ -3042,49 +3071,49 @@
     </row>
     <row r="41" ht="8" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="114" t="n"/>
-      <c r="C41" s="115" t="n"/>
-      <c r="D41" s="116" t="n"/>
-      <c r="E41" s="117" t="n"/>
-      <c r="F41" s="117" t="n"/>
-      <c r="G41" s="118" t="n"/>
-      <c r="H41" s="119" t="n"/>
-      <c r="I41" s="120" t="n"/>
-      <c r="J41" s="121" t="n"/>
+      <c r="B41" s="117" t="n"/>
+      <c r="C41" s="118" t="n"/>
+      <c r="D41" s="119" t="n"/>
+      <c r="E41" s="120" t="n"/>
+      <c r="F41" s="120" t="n"/>
+      <c r="G41" s="121" t="n"/>
+      <c r="H41" s="122" t="n"/>
+      <c r="I41" s="123" t="n"/>
+      <c r="J41" s="124" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="122" t="inlineStr">
+      <c r="B42" s="125" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="123" t="n"/>
-      <c r="D42" s="123" t="n"/>
-      <c r="E42" s="123" t="n"/>
-      <c r="F42" s="123" t="n"/>
-      <c r="G42" s="123" t="n"/>
-      <c r="H42" s="123" t="n"/>
-      <c r="I42" s="123" t="n"/>
-      <c r="J42" s="123" t="n"/>
+      <c r="C42" s="126" t="n"/>
+      <c r="D42" s="126" t="n"/>
+      <c r="E42" s="126" t="n"/>
+      <c r="F42" s="126" t="n"/>
+      <c r="G42" s="126" t="n"/>
+      <c r="H42" s="126" t="n"/>
+      <c r="I42" s="126" t="n"/>
+      <c r="J42" s="126" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="124" t="inlineStr">
+      <c r="B43" s="127" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="125" t="n"/>
-      <c r="D43" s="125" t="n"/>
-      <c r="E43" s="125" t="n"/>
-      <c r="F43" s="125" t="n"/>
-      <c r="G43" s="125" t="n"/>
-      <c r="H43" s="125" t="n"/>
-      <c r="I43" s="125" t="n"/>
-      <c r="J43" s="125" t="n"/>
+      <c r="C43" s="128" t="n"/>
+      <c r="D43" s="128" t="n"/>
+      <c r="E43" s="128" t="n"/>
+      <c r="F43" s="128" t="n"/>
+      <c r="G43" s="128" t="n"/>
+      <c r="H43" s="128" t="n"/>
+      <c r="I43" s="128" t="n"/>
+      <c r="J43" s="128" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="12" customHeight="1">
@@ -4115,7 +4144,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.44140625" customWidth="1" style="11" min="2" max="2"/>
+    <col width="8.5" customWidth="1" style="11" min="2" max="2"/>
     <col width="10" customWidth="1" style="14" min="3" max="3"/>
     <col width="26" customWidth="1" style="15" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
@@ -4152,7 +4181,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46224.87725170761</v>
+        <v>46224.90155205015</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -4257,11 +4286,11 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B8" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
@@ -4302,11 +4331,11 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B9" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -4347,11 +4376,11 @@
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B10" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
@@ -4392,11 +4421,11 @@
       </c>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="67" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B11" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -4437,11 +4466,11 @@
       </c>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="67" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B12" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C12" s="38" t="inlineStr">
@@ -4482,11 +4511,11 @@
       </c>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B13" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -4527,11 +4556,11 @@
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="84" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B14" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
@@ -4572,11 +4601,11 @@
       </c>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="67" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B15" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
@@ -4617,11 +4646,11 @@
       </c>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="67" customHeight="1">
       <c r="A16" s="36" t="n"/>
-      <c r="B16" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B16" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
@@ -4662,11 +4691,11 @@
       </c>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="33" customHeight="1">
       <c r="A17" s="28" t="n"/>
-      <c r="B17" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B17" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
@@ -4707,11 +4736,11 @@
       </c>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B18" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
@@ -4752,11 +4781,11 @@
       </c>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="67" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B19" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
@@ -4797,11 +4826,11 @@
       </c>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="67" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B20" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
@@ -4842,11 +4871,11 @@
       </c>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="84" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B21" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
@@ -4887,11 +4916,11 @@
       </c>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B22" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
@@ -4932,11 +4961,11 @@
       </c>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="84" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B23" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
@@ -4977,11 +5006,11 @@
       </c>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="67" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B24" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
@@ -5022,11 +5051,11 @@
       </c>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="67" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B25" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
@@ -5067,11 +5096,11 @@
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="45" customHeight="1">
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B26" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
@@ -5112,11 +5141,11 @@
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="67" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B27" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
@@ -5157,11 +5186,11 @@
       </c>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="50" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B28" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
@@ -5202,11 +5231,11 @@
       </c>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="45" customHeight="1">
+    <row r="29" ht="84" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B29" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
@@ -5247,11 +5276,11 @@
       </c>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="45" customHeight="1">
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B30" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
@@ -5292,11 +5321,11 @@
       </c>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B31" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
@@ -5337,11 +5366,11 @@
       </c>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32" ht="84" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B32" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C32" s="38" t="inlineStr">
@@ -5382,11 +5411,11 @@
       </c>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="50" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B33" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
@@ -5427,11 +5456,11 @@
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B34" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
@@ -5472,11 +5501,11 @@
       </c>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="50" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B35" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
@@ -5517,11 +5546,11 @@
       </c>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="33" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B36" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
@@ -5562,11 +5591,11 @@
       </c>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="67" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B37" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
@@ -5607,11 +5636,11 @@
       </c>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="45" customHeight="1">
+    <row r="38" ht="50" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B38" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C38" s="38" t="inlineStr">
@@ -5652,11 +5681,11 @@
       </c>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="67" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B39" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
@@ -5697,45 +5726,45 @@
       </c>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="50" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
+      <c r="B40" s="109" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C40" s="110" t="inlineStr">
         <is>
           <t>CSX</t>
         </is>
       </c>
-      <c r="D40" s="108" t="inlineStr">
+      <c r="D40" s="111" t="inlineStr">
         <is>
           <t>CSX Corporation</t>
         </is>
       </c>
-      <c r="E40" s="109" t="inlineStr">
+      <c r="E40" s="112" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F40" s="109" t="inlineStr">
+      <c r="F40" s="112" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
-      <c r="G40" s="110" t="n">
+      <c r="G40" s="113" t="n">
         <v>0.37</v>
       </c>
-      <c r="H40" s="111" t="inlineStr">
+      <c r="H40" s="114" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I40" s="112" t="n">
+      <c r="I40" s="115" t="n">
         <v>86617.14</v>
       </c>
-      <c r="J40" s="113" t="inlineStr">
+      <c r="J40" s="116" t="inlineStr">
         <is>
           <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
@@ -5744,49 +5773,49 @@
     </row>
     <row r="41" ht="8" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="114" t="n"/>
-      <c r="C41" s="115" t="n"/>
-      <c r="D41" s="116" t="n"/>
-      <c r="E41" s="117" t="n"/>
-      <c r="F41" s="117" t="n"/>
-      <c r="G41" s="118" t="n"/>
-      <c r="H41" s="119" t="n"/>
-      <c r="I41" s="120" t="n"/>
-      <c r="J41" s="121" t="n"/>
+      <c r="B41" s="117" t="n"/>
+      <c r="C41" s="118" t="n"/>
+      <c r="D41" s="119" t="n"/>
+      <c r="E41" s="120" t="n"/>
+      <c r="F41" s="120" t="n"/>
+      <c r="G41" s="121" t="n"/>
+      <c r="H41" s="122" t="n"/>
+      <c r="I41" s="123" t="n"/>
+      <c r="J41" s="124" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="122" t="inlineStr">
+      <c r="B42" s="125" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="123" t="n"/>
-      <c r="D42" s="123" t="n"/>
-      <c r="E42" s="123" t="n"/>
-      <c r="F42" s="123" t="n"/>
-      <c r="G42" s="123" t="n"/>
-      <c r="H42" s="123" t="n"/>
-      <c r="I42" s="123" t="n"/>
-      <c r="J42" s="123" t="n"/>
+      <c r="C42" s="126" t="n"/>
+      <c r="D42" s="126" t="n"/>
+      <c r="E42" s="126" t="n"/>
+      <c r="F42" s="126" t="n"/>
+      <c r="G42" s="126" t="n"/>
+      <c r="H42" s="126" t="n"/>
+      <c r="I42" s="126" t="n"/>
+      <c r="J42" s="126" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="124" t="inlineStr">
+      <c r="B43" s="127" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="125" t="n"/>
-      <c r="D43" s="125" t="n"/>
-      <c r="E43" s="125" t="n"/>
-      <c r="F43" s="125" t="n"/>
-      <c r="G43" s="125" t="n"/>
-      <c r="H43" s="125" t="n"/>
-      <c r="I43" s="125" t="n"/>
-      <c r="J43" s="125" t="n"/>
+      <c r="C43" s="128" t="n"/>
+      <c r="D43" s="128" t="n"/>
+      <c r="E43" s="128" t="n"/>
+      <c r="F43" s="128" t="n"/>
+      <c r="G43" s="128" t="n"/>
+      <c r="H43" s="128" t="n"/>
+      <c r="I43" s="128" t="n"/>
+      <c r="J43" s="128" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1">

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -1416,7 +1416,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.90155205015</v>
+        <v>46225.51627063603</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46224.90155205015</v>
+        <v>46225.51627063603</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="50" customHeight="1">
+    <row r="9" ht="67" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="106" t="inlineStr">
         <is>
@@ -1638,26 +1638,26 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>GWO</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>Great-West Lifeco Inc.</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.458</v>
       </c>
       <c r="H9" s="92" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         </is>
       </c>
       <c r="I9" s="93" t="n">
-        <v>1565.38</v>
+        <v>53011.04</v>
       </c>
       <c r="J9" s="54" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
         </is>
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="67" customHeight="1">
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="106" t="inlineStr">
         <is>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
-          <t>GWO</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="D10" s="39" t="inlineStr">
         <is>
-          <t>Great-West Lifeco Inc.</t>
+          <t>Power Corporation of Canada</t>
         </is>
       </c>
       <c r="E10" s="40" t="inlineStr">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.458</v>
+        <v>0.34</v>
       </c>
       <c r="H10" s="90" t="inlineStr">
         <is>
@@ -1710,11 +1710,11 @@
         </is>
       </c>
       <c r="I10" s="91" t="n">
-        <v>53011.04</v>
+        <v>38174.66</v>
       </c>
       <c r="J10" s="53" t="inlineStr">
         <is>
-          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
         </is>
       </c>
       <c r="K10" s="36" t="n"/>
@@ -1728,26 +1728,26 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="D11" s="31" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada</t>
+          <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="H11" s="92" t="inlineStr">
         <is>
@@ -1755,11 +1755,11 @@
         </is>
       </c>
       <c r="I11" s="93" t="n">
-        <v>38174.66</v>
+        <v>28518.97</v>
       </c>
       <c r="J11" s="54" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="K11" s="28" t="n"/>
@@ -1773,26 +1773,26 @@
       </c>
       <c r="C12" s="38" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Canadian Pacific Kansas City Limited</t>
         </is>
       </c>
       <c r="E12" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F12" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.323</v>
+        <v>0.295</v>
       </c>
       <c r="H12" s="90" t="inlineStr">
         <is>
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="I12" s="91" t="n">
-        <v>189567.97</v>
+        <v>79823.21000000001</v>
       </c>
       <c r="J12" s="53" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="50" customHeight="1">
+    <row r="13" ht="67" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="106" t="inlineStr">
         <is>
@@ -1818,26 +1818,26 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>EQB</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>EQB Inc.</t>
+          <t>Canadian Utilities Limited</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.317</v>
+        <v>0.266</v>
       </c>
       <c r="H13" s="92" t="inlineStr">
         <is>
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="I13" s="93" t="n">
-        <v>3018.47</v>
+        <v>10045.65</v>
       </c>
       <c r="J13" s="54" t="inlineStr">
         <is>
-          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
         </is>
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="50" customHeight="1">
+    <row r="14" ht="67" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="106" t="inlineStr">
         <is>
@@ -1863,26 +1863,26 @@
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>BDGI</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation</t>
+          <t>Badger Infrastructure Solutions Ltd.</t>
         </is>
       </c>
       <c r="E14" s="40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F14" s="40" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Construction and Engineering</t>
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.31</v>
+        <v>0.254</v>
       </c>
       <c r="H14" s="90" t="inlineStr">
         <is>
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="I14" s="91" t="n">
-        <v>28518.97</v>
+        <v>2215.94</v>
       </c>
       <c r="J14" s="53" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
       </c>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="67" customHeight="1">
+    <row r="15" ht="50" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="106" t="inlineStr">
         <is>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited</t>
+          <t>Black Diamond Group Limited</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.295</v>
+        <v>0.22</v>
       </c>
       <c r="H15" s="92" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
         </is>
       </c>
       <c r="I15" s="93" t="n">
-        <v>79823.21000000001</v>
+        <v>927.72</v>
       </c>
       <c r="J15" s="54" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
       <c r="K15" s="28" t="n"/>
@@ -1953,26 +1953,26 @@
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>TOY</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited</t>
+          <t>Spin Master Corp.</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.266</v>
+        <v>0.174</v>
       </c>
       <c r="H16" s="90" t="inlineStr">
         <is>
@@ -1980,11 +1980,11 @@
         </is>
       </c>
       <c r="I16" s="91" t="n">
-        <v>10045.65</v>
+        <v>1330.28</v>
       </c>
       <c r="J16" s="53" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
       <c r="K16" s="28" t="n"/>
@@ -1998,26 +1998,26 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Doman Building Materials Group Ltd.</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.265</v>
+        <v>0.146</v>
       </c>
       <c r="H17" s="92" t="inlineStr">
         <is>
@@ -2025,16 +2025,16 @@
         </is>
       </c>
       <c r="I17" s="93" t="n">
-        <v>976.67</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="J17" s="54" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
         </is>
       </c>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="67" customHeight="1">
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="106" t="inlineStr">
         <is>
@@ -2043,178 +2043,178 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>BDGI</t>
+          <t>DFY</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Badger Infrastructure Solutions Ltd.</t>
+          <t>Definity Financial Corporation</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G18" s="89" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
+        <v>6226.62</v>
+      </c>
+      <c r="J18" s="53" t="inlineStr">
+        <is>
+          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="n"/>
+    </row>
+    <row r="19" ht="84" customHeight="1">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>MATR</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Mattr Corp.</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Energy Equipment and Services</t>
+        </is>
+      </c>
+      <c r="G19" s="89" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
+        <v>555.83</v>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+        </is>
+      </c>
+      <c r="K19" s="36" t="n"/>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Mullen Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>Construction and Engineering</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="n">
-        <v>2215.94</v>
-      </c>
-      <c r="J18" s="53" t="inlineStr">
-        <is>
-          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>BDI</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>Black Diamond Group Limited</t>
-        </is>
-      </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G20" s="89" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
+        <v>1565.38</v>
+      </c>
+      <c r="J20" s="53" t="inlineStr">
+        <is>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="50" customHeight="1">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>NFI</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>NFI Group Inc.</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G19" s="89" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H19" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I19" s="93" t="n">
-        <v>927.72</v>
-      </c>
-      <c r="J19" s="54" t="inlineStr">
-        <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
-        </is>
-      </c>
-      <c r="K19" s="36" t="n"/>
-    </row>
-    <row r="20" ht="67" customHeight="1">
-      <c r="A20" s="28" t="n"/>
-      <c r="B20" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>MFC</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F20" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I20" s="91" t="n">
-        <v>65572.44</v>
-      </c>
-      <c r="J20" s="53" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
-        </is>
-      </c>
-      <c r="K20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="67" customHeight="1">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>DBM</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Doman Building Materials Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.146</v>
+        <v>0.545</v>
       </c>
       <c r="H21" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I21" s="93" t="n">
-        <v>676.4400000000001</v>
+        <v>1892.54</v>
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
+          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="84" customHeight="1">
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="107" t="inlineStr">
         <is>
@@ -2223,26 +2223,26 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Mattr Corp.</t>
+          <t>Russel Metals Inc.</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>1.172</v>
+        <v>0.443</v>
       </c>
       <c r="H22" s="90" t="inlineStr">
         <is>
@@ -2250,11 +2250,11 @@
         </is>
       </c>
       <c r="I22" s="91" t="n">
-        <v>555.83</v>
+        <v>2385.76</v>
       </c>
       <c r="J22" s="53" t="inlineStr">
         <is>
-          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
         </is>
       </c>
       <c r="K22" s="28" t="n"/>
@@ -2268,26 +2268,26 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>NFI</t>
+          <t>BMO</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>NFI Group Inc.</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.545</v>
+        <v>0.36</v>
       </c>
       <c r="H23" s="92" t="inlineStr">
         <is>
@@ -2295,11 +2295,11 @@
         </is>
       </c>
       <c r="I23" s="93" t="n">
-        <v>1892.54</v>
+        <v>116001.23</v>
       </c>
       <c r="J23" s="54" t="inlineStr">
         <is>
-          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
+          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
         </is>
       </c>
       <c r="K23" s="28" t="n"/>
@@ -2313,26 +2313,26 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Russel Metals Inc.</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.443</v>
+        <v>0.339</v>
       </c>
       <c r="H24" s="90" t="inlineStr">
         <is>
@@ -2340,16 +2340,16 @@
         </is>
       </c>
       <c r="I24" s="91" t="n">
-        <v>2385.76</v>
+        <v>681.6799999999999</v>
       </c>
       <c r="J24" s="53" t="inlineStr">
         <is>
-          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="50" customHeight="1">
+    <row r="25" ht="84" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="107" t="inlineStr">
         <is>
@@ -2358,26 +2358,26 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>Canadian Imperial Bank of Commerce</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.339</v>
+        <v>0.324</v>
       </c>
       <c r="H25" s="92" t="inlineStr">
         <is>
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="I25" s="93" t="n">
-        <v>681.6799999999999</v>
+        <v>101497.85</v>
       </c>
       <c r="J25" s="54" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="50" customHeight="1">
+    <row r="26" ht="67" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="107" t="inlineStr">
         <is>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>IGM</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>IGM Financial Inc.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
@@ -2418,11 +2418,11 @@
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.308</v>
+        <v>0.323</v>
       </c>
       <c r="H26" s="90" t="inlineStr">
         <is>
@@ -2430,11 +2430,11 @@
         </is>
       </c>
       <c r="I26" s="91" t="n">
-        <v>13303.41</v>
+        <v>189567.97</v>
       </c>
       <c r="J26" s="53" t="inlineStr">
         <is>
-          <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
+          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="K26" s="36" t="n"/>
@@ -2448,26 +2448,26 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>IGM</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>IGM Financial Inc.</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.234</v>
+        <v>0.308</v>
       </c>
       <c r="H27" s="92" t="inlineStr">
         <is>
@@ -2475,16 +2475,16 @@
         </is>
       </c>
       <c r="I27" s="93" t="n">
-        <v>576.85</v>
+        <v>13303.41</v>
       </c>
       <c r="J27" s="54" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
         </is>
       </c>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="67" customHeight="1">
+    <row r="28" ht="50" customHeight="1">
       <c r="A28" s="28" t="n"/>
       <c r="B28" s="107" t="inlineStr">
         <is>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E28" s="40" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.227</v>
+        <v>0.297</v>
       </c>
       <c r="H28" s="90" t="inlineStr">
         <is>
@@ -2520,11 +2520,11 @@
         </is>
       </c>
       <c r="I28" s="91" t="n">
-        <v>100391.39</v>
+        <v>275998.42</v>
       </c>
       <c r="J28" s="53" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
       <c r="K28" s="28" t="n"/>
@@ -2538,26 +2538,26 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>TOY</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Spin Master Corp.</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.174</v>
+        <v>0.265</v>
       </c>
       <c r="H29" s="92" t="inlineStr">
         <is>
@@ -2565,11 +2565,11 @@
         </is>
       </c>
       <c r="I29" s="93" t="n">
-        <v>1330.28</v>
+        <v>976.67</v>
       </c>
       <c r="J29" s="54" t="inlineStr">
         <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
         </is>
       </c>
       <c r="K29" s="36" t="n"/>
@@ -2583,83 +2583,83 @@
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>DFY</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>Definity Financial Corporation</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
         <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G30" s="89" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
+        <v>576.85</v>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="67" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>BNS</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>The Bank of Nova Scotia</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G30" s="89" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H30" s="90" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G31" s="89" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="H31" s="92" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I30" s="91" t="n">
-        <v>6226.62</v>
-      </c>
-      <c r="J30" s="53" t="inlineStr">
-        <is>
-          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
-        </is>
-      </c>
-      <c r="K30" s="36" t="n"/>
-    </row>
-    <row r="31" ht="50" customHeight="1">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="108" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>BDT</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>Bird Construction Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>Construction and Engineering</t>
-        </is>
-      </c>
-      <c r="G31" s="89" t="n">
-        <v>1.627</v>
-      </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
       <c r="I31" s="93" t="n">
-        <v>2358.79</v>
+        <v>100391.39</v>
       </c>
       <c r="J31" s="54" t="inlineStr">
         <is>
-          <t>Bird Construction Inc provides construction services in Canada</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="K31" s="28" t="n"/>
@@ -2673,26 +2673,26 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>BDT</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>ADF Group Inc.</t>
+          <t>Bird Construction Inc.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Construction and Engineering</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>1.162</v>
+        <v>1.627</v>
       </c>
       <c r="H32" s="90" t="inlineStr">
         <is>
@@ -2700,16 +2700,16 @@
         </is>
       </c>
       <c r="I32" s="91" t="n">
-        <v>284.57</v>
+        <v>2358.79</v>
       </c>
       <c r="J32" s="53" t="inlineStr">
         <is>
-          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
+          <t>Bird Construction Inc provides construction services in Canada</t>
         </is>
       </c>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="67" customHeight="1">
+    <row r="33" ht="50" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="108" t="inlineStr">
         <is>
@@ -2718,26 +2718,26 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc.</t>
+          <t>ADF Group Inc.</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.38</v>
+        <v>1.162</v>
       </c>
       <c r="H33" s="92" t="inlineStr">
         <is>
@@ -2745,16 +2745,16 @@
         </is>
       </c>
       <c r="I33" s="93" t="n">
-        <v>390.27</v>
+        <v>284.57</v>
       </c>
       <c r="J33" s="54" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
         </is>
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="50" customHeight="1">
+    <row r="34" ht="67" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="108" t="inlineStr">
         <is>
@@ -2763,26 +2763,26 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>BMO</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>K-Bro Linen Inc.</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H34" s="90" t="inlineStr">
         <is>
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="I34" s="91" t="n">
-        <v>116001.23</v>
+        <v>390.27</v>
       </c>
       <c r="J34" s="53" t="inlineStr">
         <is>
-          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
       <c r="K34" s="36" t="n"/>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="84" customHeight="1">
+    <row r="37" ht="50" customHeight="1">
       <c r="A37" s="28" t="n"/>
       <c r="B37" s="108" t="inlineStr">
         <is>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>EQB</t>
         </is>
       </c>
       <c r="D37" s="31" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce</t>
+          <t>EQB Inc.</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.324</v>
+        <v>0.317</v>
       </c>
       <c r="H37" s="92" t="inlineStr">
         <is>
@@ -2925,11 +2925,11 @@
         </is>
       </c>
       <c r="I37" s="93" t="n">
-        <v>101497.85</v>
+        <v>3018.47</v>
       </c>
       <c r="J37" s="54" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
+          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
         </is>
       </c>
       <c r="K37" s="28" t="n"/>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="C38" s="38" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D38" s="39" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E38" s="40" t="inlineStr">
@@ -2958,11 +2958,11 @@
       </c>
       <c r="F38" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.297</v>
+        <v>0.238</v>
       </c>
       <c r="H38" s="90" t="inlineStr">
         <is>
@@ -2970,16 +2970,16 @@
         </is>
       </c>
       <c r="I38" s="91" t="n">
-        <v>275998.42</v>
+        <v>11282.66</v>
       </c>
       <c r="J38" s="53" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="50" customHeight="1">
+    <row r="39" ht="67" customHeight="1">
       <c r="A39" s="28" t="n"/>
       <c r="B39" s="108" t="inlineStr">
         <is>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E39" s="32" t="inlineStr">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.238</v>
+        <v>0.216</v>
       </c>
       <c r="H39" s="92" t="inlineStr">
         <is>
@@ -3015,11 +3015,11 @@
         </is>
       </c>
       <c r="I39" s="93" t="n">
-        <v>11282.66</v>
+        <v>65572.44</v>
       </c>
       <c r="J39" s="54" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="K39" s="28" t="n"/>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46224.90155205015</v>
+        <v>46225.51627063603</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="67" customHeight="1">
+    <row r="20" ht="50" customHeight="1">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="106" t="inlineStr">
         <is>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>Block Inc.</t>
+          <t>Everest Group Ltd.</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
@@ -4850,11 +4850,11 @@
       </c>
       <c r="F20" s="40" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.203</v>
+        <v>0.18</v>
       </c>
       <c r="H20" s="90" t="inlineStr">
         <is>
@@ -4862,11 +4862,11 @@
         </is>
       </c>
       <c r="I20" s="91" t="n">
-        <v>40474.89</v>
+        <v>13320.91</v>
       </c>
       <c r="J20" s="53" t="inlineStr">
         <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="K20" s="36" t="n"/>
@@ -4880,12 +4880,12 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Citizens Financial Group Inc.</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.197</v>
+        <v>0.166</v>
       </c>
       <c r="H21" s="92" t="inlineStr">
         <is>
@@ -4907,16 +4907,16 @@
         </is>
       </c>
       <c r="I21" s="93" t="n">
-        <v>388502.86</v>
+        <v>27585.86</v>
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="50" customHeight="1">
+    <row r="22" ht="67" customHeight="1">
       <c r="A22" s="36" t="n"/>
       <c r="B22" s="106" t="inlineStr">
         <is>
@@ -4925,12 +4925,12 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Everest Group Ltd.</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.18</v>
+        <v>0.155</v>
       </c>
       <c r="H22" s="90" t="inlineStr">
         <is>
@@ -4952,16 +4952,16 @@
         </is>
       </c>
       <c r="I22" s="91" t="n">
-        <v>13320.91</v>
+        <v>47955.66</v>
       </c>
       <c r="J22" s="53" t="inlineStr">
         <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="84" customHeight="1">
+    <row r="23" ht="67" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="106" t="inlineStr">
         <is>
@@ -4970,26 +4970,26 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc.</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.166</v>
+        <v>0.152</v>
       </c>
       <c r="H23" s="92" t="inlineStr">
         <is>
@@ -4997,16 +4997,16 @@
         </is>
       </c>
       <c r="I23" s="93" t="n">
-        <v>27585.86</v>
+        <v>89144.46000000001</v>
       </c>
       <c r="J23" s="54" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="67" customHeight="1">
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="106" t="inlineStr">
         <is>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Prudential Financial Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
@@ -5030,11 +5030,11 @@
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.155</v>
+        <v>0.131</v>
       </c>
       <c r="H24" s="90" t="inlineStr">
         <is>
@@ -5042,11 +5042,11 @@
         </is>
       </c>
       <c r="I24" s="91" t="n">
-        <v>47955.66</v>
+        <v>36717.82</v>
       </c>
       <c r="J24" s="53" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
       <c r="K24" s="36" t="n"/>
@@ -5060,26 +5060,26 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.152</v>
+        <v>0.127</v>
       </c>
       <c r="H25" s="92" t="inlineStr">
         <is>
@@ -5087,11 +5087,11 @@
         </is>
       </c>
       <c r="I25" s="93" t="n">
-        <v>89144.46000000001</v>
+        <v>21453.67</v>
       </c>
       <c r="J25" s="54" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="K25" s="28" t="n"/>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
@@ -5120,11 +5120,11 @@
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.131</v>
+        <v>0.095</v>
       </c>
       <c r="H26" s="90" t="inlineStr">
         <is>
@@ -5132,16 +5132,16 @@
         </is>
       </c>
       <c r="I26" s="91" t="n">
-        <v>36717.82</v>
+        <v>612046.08</v>
       </c>
       <c r="J26" s="53" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="67" customHeight="1">
+    <row r="27" ht="84" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="106" t="inlineStr">
         <is>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Paychex Inc.</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
@@ -5165,11 +5165,11 @@
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.127</v>
+        <v>0.075</v>
       </c>
       <c r="H27" s="92" t="inlineStr">
         <is>
@@ -5177,11 +5177,11 @@
         </is>
       </c>
       <c r="I27" s="93" t="n">
-        <v>21453.67</v>
+        <v>36258.68</v>
       </c>
       <c r="J27" s="54" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
         </is>
       </c>
       <c r="K27" s="28" t="n"/>
@@ -5195,26 +5195,26 @@
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>BXP Inc.</t>
         </is>
       </c>
       <c r="E28" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Office REITs</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.095</v>
+        <v>0.068</v>
       </c>
       <c r="H28" s="90" t="inlineStr">
         <is>
@@ -5222,101 +5222,101 @@
         </is>
       </c>
       <c r="I28" s="91" t="n">
-        <v>612046.08</v>
+        <v>11826.25</v>
       </c>
       <c r="J28" s="53" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
         </is>
       </c>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="84" customHeight="1">
+    <row r="29" ht="50" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B29" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Paychex Inc.</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.075</v>
+        <v>0.839</v>
       </c>
       <c r="H29" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I29" s="93" t="n">
-        <v>36258.68</v>
+        <v>77721.12</v>
       </c>
       <c r="J29" s="54" t="inlineStr">
         <is>
-          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="50" customHeight="1">
+    <row r="30" ht="84" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B30" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>BXP Inc.</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Office REITs</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.068</v>
+        <v>0.701</v>
       </c>
       <c r="H30" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I30" s="91" t="n">
-        <v>11826.25</v>
+        <v>77190.64999999999</v>
       </c>
       <c r="J30" s="53" t="inlineStr">
         <is>
-          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="K30" s="36" t="n"/>
@@ -5330,26 +5330,26 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.839</v>
+        <v>0.471</v>
       </c>
       <c r="H31" s="92" t="inlineStr">
         <is>
@@ -5357,16 +5357,16 @@
         </is>
       </c>
       <c r="I31" s="93" t="n">
-        <v>77721.12</v>
+        <v>44725.83</v>
       </c>
       <c r="J31" s="54" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="84" customHeight="1">
+    <row r="32" ht="50" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="107" t="inlineStr">
         <is>
@@ -5375,26 +5375,26 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.701</v>
+        <v>0.356</v>
       </c>
       <c r="H32" s="90" t="inlineStr">
         <is>
@@ -5402,11 +5402,11 @@
         </is>
       </c>
       <c r="I32" s="91" t="n">
-        <v>77190.64999999999</v>
+        <v>96186.41</v>
       </c>
       <c r="J32" s="53" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="K32" s="36" t="n"/>
@@ -5420,26 +5420,26 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.471</v>
+        <v>0.324</v>
       </c>
       <c r="H33" s="92" t="inlineStr">
         <is>
@@ -5447,16 +5447,16 @@
         </is>
       </c>
       <c r="I33" s="93" t="n">
-        <v>44725.83</v>
+        <v>4309578.68</v>
       </c>
       <c r="J33" s="54" t="inlineStr">
         <is>
-          <t>State Street Corporation provides various financial products and services to institutional investors</t>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
         </is>
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="50" customHeight="1">
+    <row r="34" ht="33" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="107" t="inlineStr">
         <is>
@@ -5465,26 +5465,26 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.356</v>
+        <v>0.308</v>
       </c>
       <c r="H34" s="90" t="inlineStr">
         <is>
@@ -5492,16 +5492,16 @@
         </is>
       </c>
       <c r="I34" s="91" t="n">
-        <v>96186.41</v>
+        <v>16078.79</v>
       </c>
       <c r="J34" s="53" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="50" customHeight="1">
+    <row r="35" ht="67" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="107" t="inlineStr">
         <is>
@@ -5510,26 +5510,26 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Northern Trust Corporation</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.324</v>
+        <v>0.258</v>
       </c>
       <c r="H35" s="92" t="inlineStr">
         <is>
@@ -5537,16 +5537,16 @@
         </is>
       </c>
       <c r="I35" s="93" t="n">
-        <v>4309578.68</v>
+        <v>30713.22</v>
       </c>
       <c r="J35" s="54" t="inlineStr">
         <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
         </is>
       </c>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="33" customHeight="1">
+    <row r="36" ht="50" customHeight="1">
       <c r="A36" s="36" t="n"/>
       <c r="B36" s="107" t="inlineStr">
         <is>
@@ -5555,26 +5555,26 @@
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D36" s="39" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.308</v>
+        <v>0.25</v>
       </c>
       <c r="H36" s="90" t="inlineStr">
         <is>
@@ -5582,11 +5582,11 @@
         </is>
       </c>
       <c r="I36" s="91" t="n">
-        <v>16078.79</v>
+        <v>55851.6</v>
       </c>
       <c r="J36" s="53" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="K36" s="36" t="n"/>
@@ -5600,12 +5600,12 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="D37" s="31" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation</t>
+          <t>Block Inc.</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
@@ -5615,11 +5615,11 @@
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.258</v>
+        <v>0.203</v>
       </c>
       <c r="H37" s="92" t="inlineStr">
         <is>
@@ -5627,16 +5627,16 @@
         </is>
       </c>
       <c r="I37" s="93" t="n">
-        <v>30713.22</v>
+        <v>40474.89</v>
       </c>
       <c r="J37" s="54" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="50" customHeight="1">
+    <row r="38" ht="84" customHeight="1">
       <c r="A38" s="36" t="n"/>
       <c r="B38" s="107" t="inlineStr">
         <is>
@@ -5645,12 +5645,12 @@
       </c>
       <c r="C38" s="38" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D38" s="39" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E38" s="40" t="inlineStr">
@@ -5660,11 +5660,11 @@
       </c>
       <c r="F38" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.25</v>
+        <v>0.197</v>
       </c>
       <c r="H38" s="90" t="inlineStr">
         <is>
@@ -5672,11 +5672,11 @@
         </is>
       </c>
       <c r="I38" s="91" t="n">
-        <v>55851.6</v>
+        <v>388502.86</v>
       </c>
       <c r="J38" s="53" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
       <c r="K38" s="36" t="n"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$K$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$K$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$K$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$K$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -339,7 +339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -513,15 +513,6 @@
       <bottom style="thin">
         <color rgb="FFC67A29"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD1DCE8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -1416,7 +1407,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46225.51627063603</v>
+        <v>46226.51410952971</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1479,7 +1470,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46225.51627063603</v>
+        <v>46226.51410952971</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -1612,7 +1603,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>0.735</v>
+        <v>0.656</v>
       </c>
       <c r="H8" s="90" t="inlineStr">
         <is>
@@ -1629,7 +1620,7 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="67" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="106" t="inlineStr">
         <is>
@@ -1638,26 +1629,26 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>GWO</t>
+          <t>SOBO</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>Great-West Lifeco Inc.</t>
+          <t>South Bow Corporation</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.458</v>
+        <v>0.473</v>
       </c>
       <c r="H9" s="92" t="inlineStr">
         <is>
@@ -1665,11 +1656,11 @@
         </is>
       </c>
       <c r="I9" s="93" t="n">
-        <v>53011.04</v>
+        <v>7850.04</v>
       </c>
       <c r="J9" s="54" t="inlineStr">
         <is>
-          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
+          <t>South Bow Corporation operates as an energy infrastructure company</t>
         </is>
       </c>
       <c r="K9" s="28" t="n"/>
@@ -1702,7 +1693,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="H10" s="90" t="inlineStr">
         <is>
@@ -1719,7 +1710,7 @@
       </c>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="50" customHeight="1">
+    <row r="11" ht="67" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="106" t="inlineStr">
         <is>
@@ -1728,26 +1719,26 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="D11" s="31" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation</t>
+          <t>Canadian Utilities Limited</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.31</v>
+        <v>0.278</v>
       </c>
       <c r="H11" s="92" t="inlineStr">
         <is>
@@ -1755,11 +1746,11 @@
         </is>
       </c>
       <c r="I11" s="93" t="n">
-        <v>28518.97</v>
+        <v>10045.65</v>
       </c>
       <c r="J11" s="54" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
         </is>
       </c>
       <c r="K11" s="28" t="n"/>
@@ -1773,12 +1764,12 @@
       </c>
       <c r="C12" s="38" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>BDGI</t>
         </is>
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited</t>
+          <t>Badger Infrastructure Solutions Ltd.</t>
         </is>
       </c>
       <c r="E12" s="40" t="inlineStr">
@@ -1788,11 +1779,11 @@
       </c>
       <c r="F12" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Construction and Engineering</t>
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.295</v>
+        <v>0.236</v>
       </c>
       <c r="H12" s="90" t="inlineStr">
         <is>
@@ -1800,16 +1791,16 @@
         </is>
       </c>
       <c r="I12" s="91" t="n">
-        <v>79823.21000000001</v>
+        <v>2215.94</v>
       </c>
       <c r="J12" s="53" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
       </c>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="67" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="106" t="inlineStr">
         <is>
@@ -1818,26 +1809,26 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>DFY</t>
         </is>
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited</t>
+          <t>Definity Financial Corporation</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.266</v>
+        <v>0.105</v>
       </c>
       <c r="H13" s="92" t="inlineStr">
         <is>
@@ -1845,75 +1836,75 @@
         </is>
       </c>
       <c r="I13" s="93" t="n">
-        <v>10045.65</v>
+        <v>6226.62</v>
       </c>
       <c r="J13" s="54" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
         </is>
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="67" customHeight="1">
+    <row r="14" ht="84" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B14" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>BDGI</t>
+          <t>MATR</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>Badger Infrastructure Solutions Ltd.</t>
+          <t>Mattr Corp.</t>
         </is>
       </c>
       <c r="E14" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="40" t="inlineStr">
         <is>
-          <t>Construction and Engineering</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.254</v>
+        <v>1.156</v>
       </c>
       <c r="H14" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I14" s="91" t="n">
-        <v>2215.94</v>
+        <v>555.83</v>
       </c>
       <c r="J14" s="53" t="inlineStr">
         <is>
-          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
+          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="50" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B15" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited</t>
+          <t>Mullen Group Ltd.</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
@@ -1923,87 +1914,87 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.22</v>
+        <v>0.578</v>
       </c>
       <c r="H15" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I15" s="93" t="n">
-        <v>927.72</v>
+        <v>1565.38</v>
       </c>
       <c r="J15" s="54" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="67" customHeight="1">
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B16" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>TOY</t>
+          <t>NFI</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>Spin Master Corp.</t>
+          <t>NFI Group Inc.</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.174</v>
+        <v>0.527</v>
       </c>
       <c r="H16" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I16" s="91" t="n">
-        <v>1330.28</v>
+        <v>1892.54</v>
       </c>
       <c r="J16" s="53" t="inlineStr">
         <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="67" customHeight="1">
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B17" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Doman Building Materials Group Ltd.</t>
+          <t>Russel Metals Inc.</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
@@ -2017,64 +2008,64 @@
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.146</v>
+        <v>0.468</v>
       </c>
       <c r="H17" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I17" s="93" t="n">
-        <v>676.4400000000001</v>
+        <v>2385.76</v>
       </c>
       <c r="J17" s="54" t="inlineStr">
         <is>
-          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
+          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
         </is>
       </c>
       <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="50" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>DFY</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Definity Financial Corporation</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.08</v>
+        <v>0.374</v>
       </c>
       <c r="H18" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I18" s="91" t="n">
-        <v>6226.62</v>
+        <v>681.6799999999999</v>
       </c>
       <c r="J18" s="53" t="inlineStr">
         <is>
-          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
       <c r="K18" s="28" t="n"/>
@@ -2088,26 +2079,26 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Mattr Corp.</t>
+          <t>Canadian Imperial Bank of Commerce</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>1.172</v>
+        <v>0.342</v>
       </c>
       <c r="H19" s="92" t="inlineStr">
         <is>
@@ -2115,11 +2106,11 @@
         </is>
       </c>
       <c r="I19" s="93" t="n">
-        <v>555.83</v>
+        <v>101497.85</v>
       </c>
       <c r="J19" s="54" t="inlineStr">
         <is>
-          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="K19" s="36" t="n"/>
@@ -2133,26 +2124,26 @@
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F20" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.316</v>
       </c>
       <c r="H20" s="90" t="inlineStr">
         <is>
@@ -2160,16 +2151,16 @@
         </is>
       </c>
       <c r="I20" s="91" t="n">
-        <v>1565.38</v>
+        <v>28518.97</v>
       </c>
       <c r="J20" s="53" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="50" customHeight="1">
+    <row r="21" ht="67" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="107" t="inlineStr">
         <is>
@@ -2178,12 +2169,12 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>NFI</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>NFI Group Inc.</t>
+          <t>Canadian Pacific Kansas City Limited</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -2193,11 +2184,11 @@
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.545</v>
+        <v>0.298</v>
       </c>
       <c r="H21" s="92" t="inlineStr">
         <is>
@@ -2205,16 +2196,16 @@
         </is>
       </c>
       <c r="I21" s="93" t="n">
-        <v>1892.54</v>
+        <v>79823.21000000001</v>
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="50" customHeight="1">
+    <row r="22" ht="67" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="107" t="inlineStr">
         <is>
@@ -2223,26 +2214,26 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Russel Metals Inc.</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.443</v>
+        <v>0.252</v>
       </c>
       <c r="H22" s="90" t="inlineStr">
         <is>
@@ -2250,11 +2241,11 @@
         </is>
       </c>
       <c r="I22" s="91" t="n">
-        <v>2385.76</v>
+        <v>976.67</v>
       </c>
       <c r="J22" s="53" t="inlineStr">
         <is>
-          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
         </is>
       </c>
       <c r="K22" s="28" t="n"/>
@@ -2268,26 +2259,26 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>BMO</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.36</v>
+        <v>0.229</v>
       </c>
       <c r="H23" s="92" t="inlineStr">
         <is>
@@ -2295,16 +2286,16 @@
         </is>
       </c>
       <c r="I23" s="93" t="n">
-        <v>116001.23</v>
+        <v>576.85</v>
       </c>
       <c r="J23" s="54" t="inlineStr">
         <is>
-          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="50" customHeight="1">
+    <row r="24" ht="67" customHeight="1">
       <c r="A24" s="36" t="n"/>
       <c r="B24" s="107" t="inlineStr">
         <is>
@@ -2313,26 +2304,26 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>TOY</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>Spin Master Corp.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.339</v>
+        <v>0.196</v>
       </c>
       <c r="H24" s="90" t="inlineStr">
         <is>
@@ -2340,16 +2331,16 @@
         </is>
       </c>
       <c r="I24" s="91" t="n">
-        <v>681.6799999999999</v>
+        <v>1330.28</v>
       </c>
       <c r="J24" s="53" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="84" customHeight="1">
+    <row r="25" ht="67" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="107" t="inlineStr">
         <is>
@@ -2358,26 +2349,26 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce</t>
+          <t>Doman Building Materials Group Ltd.</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.324</v>
+        <v>0.192</v>
       </c>
       <c r="H25" s="92" t="inlineStr">
         <is>
@@ -2385,16 +2376,16 @@
         </is>
       </c>
       <c r="I25" s="93" t="n">
-        <v>101497.85</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="J25" s="54" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
+          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
         </is>
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="67" customHeight="1">
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="107" t="inlineStr">
         <is>
@@ -2403,26 +2394,26 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Black Diamond Group Limited</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.323</v>
+        <v>0.178</v>
       </c>
       <c r="H26" s="90" t="inlineStr">
         <is>
@@ -2430,236 +2421,236 @@
         </is>
       </c>
       <c r="I26" s="91" t="n">
-        <v>189567.97</v>
+        <v>927.72</v>
       </c>
       <c r="J26" s="53" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="50" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B27" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>IGM</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>IGM Financial Inc.</t>
+          <t>ADF Group Inc.</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Metals and Mining</t>
+        </is>
+      </c>
+      <c r="G27" s="89" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
+        <v>284.57</v>
+      </c>
+      <c r="J27" s="54" t="inlineStr">
+        <is>
+          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K27" s="36" t="n"/>
+    </row>
+    <row r="28" ht="67" customHeight="1">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>GWO</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>Great-West Lifeco Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G27" s="89" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="H27" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I27" s="93" t="n">
-        <v>13303.41</v>
-      </c>
-      <c r="J27" s="54" t="inlineStr">
-        <is>
-          <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
-        </is>
-      </c>
-      <c r="K27" s="36" t="n"/>
-    </row>
-    <row r="28" ht="50" customHeight="1">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>RY</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>Royal Bank of Canada</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.297</v>
+        <v>0.458</v>
       </c>
       <c r="H28" s="90" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>Streak</t>
         </is>
       </c>
       <c r="I28" s="91" t="n">
-        <v>275998.42</v>
+        <v>53011.04</v>
       </c>
       <c r="J28" s="53" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
+          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
         </is>
       </c>
       <c r="K28" s="28" t="n"/>
     </row>
     <row r="29" ht="67" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B29" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>K-Bro Linen Inc.</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+        </is>
+      </c>
+      <c r="K29" s="36" t="n"/>
+    </row>
+    <row r="30" ht="101" customHeight="1">
+      <c r="A30" s="36" t="n"/>
+      <c r="B30" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>SLF</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>Sun Life Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G29" s="89" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I29" s="93" t="n">
-        <v>976.67</v>
-      </c>
-      <c r="J29" s="54" t="inlineStr">
-        <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
-        </is>
-      </c>
-      <c r="K29" s="36" t="n"/>
-    </row>
-    <row r="30" ht="50" customHeight="1">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>DXT</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>Dexterra Group Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.234</v>
+        <v>0.35</v>
       </c>
       <c r="H30" s="90" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>Streak</t>
         </is>
       </c>
       <c r="I30" s="91" t="n">
-        <v>576.85</v>
+        <v>41467.31</v>
       </c>
       <c r="J30" s="53" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
       <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="67" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B31" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Canadian National Railway Company</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.227</v>
+        <v>0.331</v>
       </c>
       <c r="H31" s="92" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>Streak</t>
         </is>
       </c>
       <c r="I31" s="93" t="n">
-        <v>100391.39</v>
+        <v>72839.50999999999</v>
       </c>
       <c r="J31" s="54" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
       <c r="K31" s="28" t="n"/>
@@ -2673,26 +2664,26 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>BDT</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>Bird Construction Inc.</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Construction and Engineering</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>1.627</v>
+        <v>0.24</v>
       </c>
       <c r="H32" s="90" t="inlineStr">
         <is>
@@ -2700,16 +2691,16 @@
         </is>
       </c>
       <c r="I32" s="91" t="n">
-        <v>2358.79</v>
+        <v>11282.66</v>
       </c>
       <c r="J32" s="53" t="inlineStr">
         <is>
-          <t>Bird Construction Inc provides construction services in Canada</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="50" customHeight="1">
+    <row r="33" ht="67" customHeight="1">
       <c r="A33" s="28" t="n"/>
       <c r="B33" s="108" t="inlineStr">
         <is>
@@ -2718,26 +2709,26 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>ADF Group Inc.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>1.162</v>
+        <v>0.215</v>
       </c>
       <c r="H33" s="92" t="inlineStr">
         <is>
@@ -2745,375 +2736,183 @@
         </is>
       </c>
       <c r="I33" s="93" t="n">
-        <v>284.57</v>
+        <v>65572.44</v>
       </c>
       <c r="J33" s="54" t="inlineStr">
         <is>
-          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="67" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="108" t="inlineStr">
+      <c r="B34" s="109" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C34" s="38" t="inlineStr">
-        <is>
-          <t>KBL</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc.</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G34" s="89" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H34" s="90" t="inlineStr">
+      <c r="C34" s="110" t="inlineStr">
+        <is>
+          <t>IFP</t>
+        </is>
+      </c>
+      <c r="D34" s="111" t="inlineStr">
+        <is>
+          <t>Interfor Corporation</t>
+        </is>
+      </c>
+      <c r="E34" s="112" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F34" s="112" t="inlineStr">
+        <is>
+          <t>Paper and Forest Products</t>
+        </is>
+      </c>
+      <c r="G34" s="113" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="H34" s="114" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I34" s="91" t="n">
-        <v>390.27</v>
-      </c>
-      <c r="J34" s="53" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+      <c r="I34" s="115" t="n">
+        <v>501.72</v>
+      </c>
+      <c r="J34" s="116" t="inlineStr">
+        <is>
+          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="101" customHeight="1">
+    <row r="35" ht="8" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="108" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G35" s="89" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="H35" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I35" s="93" t="n">
-        <v>41467.31</v>
-      </c>
-      <c r="J35" s="54" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
-        </is>
-      </c>
+      <c r="B35" s="117" t="n"/>
+      <c r="C35" s="118" t="n"/>
+      <c r="D35" s="119" t="n"/>
+      <c r="E35" s="120" t="n"/>
+      <c r="F35" s="120" t="n"/>
+      <c r="G35" s="121" t="n"/>
+      <c r="H35" s="122" t="n"/>
+      <c r="I35" s="123" t="n"/>
+      <c r="J35" s="124" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="67" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="108" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>CNR</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F36" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G36" s="89" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="H36" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I36" s="91" t="n">
-        <v>72839.50999999999</v>
-      </c>
-      <c r="J36" s="53" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
-        </is>
-      </c>
+      <c r="B36" s="125" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C36" s="126" t="n"/>
+      <c r="D36" s="126" t="n"/>
+      <c r="E36" s="126" t="n"/>
+      <c r="F36" s="126" t="n"/>
+      <c r="G36" s="126" t="n"/>
+      <c r="H36" s="126" t="n"/>
+      <c r="I36" s="126" t="n"/>
+      <c r="J36" s="126" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="50" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="108" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>EQB</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>EQB Inc.</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F37" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G37" s="89" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="H37" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I37" s="93" t="n">
-        <v>3018.47</v>
-      </c>
-      <c r="J37" s="54" t="inlineStr">
-        <is>
-          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
-        </is>
-      </c>
+      <c r="B37" s="127" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C37" s="128" t="n"/>
+      <c r="D37" s="128" t="n"/>
+      <c r="E37" s="128" t="n"/>
+      <c r="F37" s="128" t="n"/>
+      <c r="G37" s="128" t="n"/>
+      <c r="H37" s="128" t="n"/>
+      <c r="I37" s="128" t="n"/>
+      <c r="J37" s="128" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="50" customHeight="1">
+    <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="108" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>iA Financial Corporation Inc.</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G38" s="89" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="H38" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I38" s="91" t="n">
-        <v>11282.66</v>
-      </c>
-      <c r="J38" s="53" t="inlineStr">
-        <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
-        </is>
-      </c>
+      <c r="B38" s="48" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="40" t="n"/>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="89" t="n"/>
+      <c r="H38" s="90" t="n"/>
+      <c r="I38" s="91" t="n"/>
+      <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="67" customHeight="1">
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="108" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>MFC</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G39" s="89" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="H39" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I39" s="93" t="n">
-        <v>65572.44</v>
-      </c>
-      <c r="J39" s="54" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
-        </is>
-      </c>
+      <c r="B39" s="49" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="89" t="n"/>
+      <c r="H39" s="92" t="n"/>
+      <c r="I39" s="93" t="n"/>
+      <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="67" customHeight="1">
+    <row r="40" ht="20.4" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="109" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C40" s="110" t="inlineStr">
-        <is>
-          <t>IFP</t>
-        </is>
-      </c>
-      <c r="D40" s="111" t="inlineStr">
-        <is>
-          <t>Interfor Corporation</t>
-        </is>
-      </c>
-      <c r="E40" s="112" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F40" s="112" t="inlineStr">
-        <is>
-          <t>Paper and Forest Products</t>
-        </is>
-      </c>
-      <c r="G40" s="113" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H40" s="114" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I40" s="115" t="n">
-        <v>501.72</v>
-      </c>
-      <c r="J40" s="116" t="inlineStr">
-        <is>
-          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
-        </is>
-      </c>
+      <c r="B40" s="48" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="89" t="n"/>
+      <c r="H40" s="90" t="n"/>
+      <c r="I40" s="91" t="n"/>
+      <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="8" customHeight="1" thickBot="1">
+    <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="117" t="n"/>
-      <c r="C41" s="118" t="n"/>
-      <c r="D41" s="119" t="n"/>
-      <c r="E41" s="120" t="n"/>
-      <c r="F41" s="120" t="n"/>
-      <c r="G41" s="121" t="n"/>
-      <c r="H41" s="122" t="n"/>
-      <c r="I41" s="123" t="n"/>
-      <c r="J41" s="124" t="n"/>
+      <c r="B41" s="69" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="71" t="n"/>
+      <c r="E41" s="72" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="94" t="n"/>
+      <c r="H41" s="95" t="n"/>
+      <c r="I41" s="96" t="n"/>
+      <c r="J41" s="74" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
-    <row r="42" ht="34" customHeight="1">
+    <row r="42">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="125" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C42" s="126" t="n"/>
-      <c r="D42" s="126" t="n"/>
-      <c r="E42" s="126" t="n"/>
-      <c r="F42" s="126" t="n"/>
-      <c r="G42" s="126" t="n"/>
-      <c r="H42" s="126" t="n"/>
-      <c r="I42" s="126" t="n"/>
-      <c r="J42" s="126" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="43" t="n"/>
+      <c r="E42" s="43" t="n"/>
+      <c r="F42" s="43" t="n"/>
+      <c r="G42" s="43" t="n"/>
+      <c r="H42" s="97" t="n"/>
+      <c r="I42" s="43" t="n"/>
+      <c r="J42" s="43" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
-    <row r="43" ht="28" customHeight="1" thickBot="1">
+    <row r="43" ht="15.6" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="127" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C43" s="128" t="n"/>
-      <c r="D43" s="128" t="n"/>
-      <c r="E43" s="128" t="n"/>
-      <c r="F43" s="128" t="n"/>
-      <c r="G43" s="128" t="n"/>
-      <c r="H43" s="128" t="n"/>
-      <c r="I43" s="128" t="n"/>
-      <c r="J43" s="128" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="97" t="n"/>
+      <c r="I43" s="43" t="n"/>
+      <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="12" customHeight="1">
@@ -3196,12 +2995,12 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B36:J36"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B37:J37"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G40">
+  <conditionalFormatting sqref="G8:G34">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4181,7 +3980,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46225.51627063603</v>
+        <v>46226.51410952971</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -4314,7 +4113,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.195</v>
+        <v>1.159</v>
       </c>
       <c r="H8" s="90" t="inlineStr">
         <is>
@@ -4359,7 +4158,7 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.899</v>
+        <v>0.82</v>
       </c>
       <c r="H9" s="92" t="inlineStr">
         <is>
@@ -4376,7 +4175,7 @@
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="50" customHeight="1">
+    <row r="10" ht="84" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="106" t="inlineStr">
         <is>
@@ -4385,26 +4184,26 @@
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="D10" s="39" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Services Inc.</t>
+          <t>The Travelers Companies Inc.</t>
         </is>
       </c>
       <c r="E10" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.424</v>
+        <v>0.331</v>
       </c>
       <c r="H10" s="90" t="inlineStr">
         <is>
@@ -4412,11 +4211,11 @@
         </is>
       </c>
       <c r="I10" s="91" t="n">
-        <v>26566.73</v>
+        <v>64533.41</v>
       </c>
       <c r="J10" s="53" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="K10" s="36" t="n"/>
@@ -4430,26 +4229,26 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="D11" s="31" t="inlineStr">
         <is>
-          <t>Globe Life Inc.</t>
+          <t>Archer-Daniels-Midland Company</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.356</v>
+        <v>0.315</v>
       </c>
       <c r="H11" s="92" t="inlineStr">
         <is>
@@ -4457,16 +4256,16 @@
         </is>
       </c>
       <c r="I11" s="93" t="n">
-        <v>12644.53</v>
+        <v>39380.19</v>
       </c>
       <c r="J11" s="54" t="inlineStr">
         <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="67" customHeight="1">
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="106" t="inlineStr">
         <is>
@@ -4475,26 +4274,26 @@
       </c>
       <c r="C12" s="38" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E12" s="40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F12" s="40" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.351</v>
+        <v>0.3</v>
       </c>
       <c r="H12" s="90" t="inlineStr">
         <is>
@@ -4502,16 +4301,16 @@
         </is>
       </c>
       <c r="I12" s="91" t="n">
-        <v>148209.56</v>
+        <v>125211.85</v>
       </c>
       <c r="J12" s="53" t="inlineStr">
         <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="50" customHeight="1">
+    <row r="13" ht="33" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="106" t="inlineStr">
         <is>
@@ -4520,26 +4319,26 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>W.W. Grainger Inc.</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.344</v>
+        <v>0.295</v>
       </c>
       <c r="H13" s="92" t="inlineStr">
         <is>
@@ -4547,16 +4346,16 @@
         </is>
       </c>
       <c r="I13" s="93" t="n">
-        <v>125211.85</v>
+        <v>62147.38</v>
       </c>
       <c r="J13" s="54" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="84" customHeight="1">
+    <row r="14" ht="67" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="106" t="inlineStr">
         <is>
@@ -4565,12 +4364,12 @@
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc.</t>
+          <t>Principal Financial Group Inc.</t>
         </is>
       </c>
       <c r="E14" s="40" t="inlineStr">
@@ -4584,7 +4383,7 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.341</v>
+        <v>0.184</v>
       </c>
       <c r="H14" s="90" t="inlineStr">
         <is>
@@ -4592,16 +4391,16 @@
         </is>
       </c>
       <c r="I14" s="91" t="n">
-        <v>64533.41</v>
+        <v>23624.19</v>
       </c>
       <c r="J14" s="53" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="67" customHeight="1">
+    <row r="15" ht="33" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="106" t="inlineStr">
         <is>
@@ -4610,26 +4409,26 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.295</v>
+        <v>0.168</v>
       </c>
       <c r="H15" s="92" t="inlineStr">
         <is>
@@ -4637,16 +4436,16 @@
         </is>
       </c>
       <c r="I15" s="93" t="n">
-        <v>39380.19</v>
+        <v>834204.25</v>
       </c>
       <c r="J15" s="54" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="67" customHeight="1">
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="106" t="inlineStr">
         <is>
@@ -4655,26 +4454,26 @@
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>Everest Group Ltd.</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.292</v>
+        <v>0.155</v>
       </c>
       <c r="H16" s="90" t="inlineStr">
         <is>
@@ -4682,120 +4481,120 @@
         </is>
       </c>
       <c r="I16" s="91" t="n">
-        <v>14353.95</v>
+        <v>13320.91</v>
       </c>
       <c r="J16" s="53" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="33" customHeight="1">
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="28" t="n"/>
-      <c r="B17" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B17" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>W.W. Grainger Inc.</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.292</v>
+        <v>0.847</v>
       </c>
       <c r="H17" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I17" s="93" t="n">
-        <v>62147.38</v>
+        <v>77721.12</v>
       </c>
       <c r="J17" s="54" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="50" customHeight="1">
+    <row r="18" ht="84" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B18" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.29</v>
+        <v>0.715</v>
       </c>
       <c r="H18" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I18" s="91" t="n">
-        <v>158667.48</v>
+        <v>77190.64999999999</v>
       </c>
       <c r="J18" s="53" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="67" customHeight="1">
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B19" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc.</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
@@ -4805,267 +4604,267 @@
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.222</v>
+        <v>0.469</v>
       </c>
       <c r="H19" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I19" s="93" t="n">
-        <v>23624.19</v>
+        <v>44725.83</v>
       </c>
       <c r="J19" s="54" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+          <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
       <c r="K19" s="28" t="n"/>
     </row>
     <row r="20" ht="50" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B20" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>Everest Group Ltd.</t>
+          <t>J.B. Hunt Transport Services Inc.</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="H20" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I20" s="91" t="n">
-        <v>13320.91</v>
+        <v>26566.73</v>
       </c>
       <c r="J20" s="53" t="inlineStr">
         <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+          <t>J</t>
         </is>
       </c>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="84" customHeight="1">
+    <row r="21" ht="67" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B21" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc.</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.166</v>
+        <v>0.344</v>
       </c>
       <c r="H21" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I21" s="93" t="n">
-        <v>27585.86</v>
+        <v>148209.56</v>
       </c>
       <c r="J21" s="54" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="67" customHeight="1">
+    <row r="22" ht="33" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B22" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.155</v>
+        <v>0.343</v>
       </c>
       <c r="H22" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I22" s="91" t="n">
-        <v>47955.66</v>
+        <v>16078.79</v>
       </c>
       <c r="J22" s="53" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="K22" s="36" t="n"/>
     </row>
     <row r="23" ht="67" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B23" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Globe Life Inc.</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.152</v>
+        <v>0.338</v>
       </c>
       <c r="H23" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I23" s="93" t="n">
-        <v>89144.46000000001</v>
+        <v>12644.53</v>
       </c>
       <c r="J23" s="54" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="50" customHeight="1">
+    <row r="24" ht="67" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B24" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc.</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.131</v>
+        <v>0.291</v>
       </c>
       <c r="H24" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I24" s="91" t="n">
-        <v>36717.82</v>
+        <v>14353.95</v>
       </c>
       <c r="J24" s="53" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="67" customHeight="1">
+    <row r="25" ht="50" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B25" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
@@ -5075,163 +4874,163 @@
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.127</v>
+        <v>0.28</v>
       </c>
       <c r="H25" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I25" s="93" t="n">
-        <v>21453.67</v>
+        <v>158667.48</v>
       </c>
       <c r="J25" s="54" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="50" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B26" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.095</v>
+        <v>0.278</v>
       </c>
       <c r="H26" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I26" s="91" t="n">
-        <v>612046.08</v>
+        <v>4309578.68</v>
       </c>
       <c r="J26" s="53" t="inlineStr">
         <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
         </is>
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="84" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B27" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Paychex Inc.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.075</v>
+        <v>0.197</v>
       </c>
       <c r="H27" s="92" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I27" s="93" t="n">
-        <v>36258.68</v>
+        <v>388502.86</v>
       </c>
       <c r="J27" s="54" t="inlineStr">
         <is>
-          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="50" customHeight="1">
+    <row r="28" ht="67" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B28" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>BXP Inc.</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E28" s="40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>Office REITs</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.068</v>
+        <v>0.179</v>
       </c>
       <c r="H28" s="90" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="I28" s="91" t="n">
-        <v>11826.25</v>
+        <v>89144.46000000001</v>
       </c>
       <c r="J28" s="53" t="inlineStr">
         <is>
-          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="50" customHeight="1">
+    <row r="29" ht="67" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="107" t="inlineStr">
         <is>
@@ -5240,26 +5039,26 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Block Inc.</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.839</v>
+        <v>0.175</v>
       </c>
       <c r="H29" s="92" t="inlineStr">
         <is>
@@ -5267,11 +5066,11 @@
         </is>
       </c>
       <c r="I29" s="93" t="n">
-        <v>77721.12</v>
+        <v>40474.89</v>
       </c>
       <c r="J29" s="54" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="K29" s="28" t="n"/>
@@ -5285,26 +5084,26 @@
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Citizens Financial Group Inc.</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.701</v>
+        <v>0.175</v>
       </c>
       <c r="H30" s="90" t="inlineStr">
         <is>
@@ -5312,16 +5111,16 @@
         </is>
       </c>
       <c r="I30" s="91" t="n">
-        <v>77190.64999999999</v>
+        <v>27585.86</v>
       </c>
       <c r="J30" s="53" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="50" customHeight="1">
+    <row r="31" ht="67" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="107" t="inlineStr">
         <is>
@@ -5330,12 +5129,12 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
@@ -5345,11 +5144,11 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.471</v>
+        <v>0.161</v>
       </c>
       <c r="H31" s="92" t="inlineStr">
         <is>
@@ -5357,16 +5156,16 @@
         </is>
       </c>
       <c r="I31" s="93" t="n">
-        <v>44725.83</v>
+        <v>47955.66</v>
       </c>
       <c r="J31" s="54" t="inlineStr">
         <is>
-          <t>State Street Corporation provides various financial products and services to institutional investors</t>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="50" customHeight="1">
+    <row r="32" ht="67" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="107" t="inlineStr">
         <is>
@@ -5375,26 +5174,26 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.356</v>
+        <v>0.123</v>
       </c>
       <c r="H32" s="90" t="inlineStr">
         <is>
@@ -5402,11 +5201,11 @@
         </is>
       </c>
       <c r="I32" s="91" t="n">
-        <v>96186.41</v>
+        <v>21453.67</v>
       </c>
       <c r="J32" s="53" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="K32" s="36" t="n"/>
@@ -5420,26 +5219,26 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Prudential Financial Inc.</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.324</v>
+        <v>0.12</v>
       </c>
       <c r="H33" s="92" t="inlineStr">
         <is>
@@ -5447,16 +5246,16 @@
         </is>
       </c>
       <c r="I33" s="93" t="n">
-        <v>4309578.68</v>
+        <v>36717.82</v>
       </c>
       <c r="J33" s="54" t="inlineStr">
         <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="33" customHeight="1">
+    <row r="34" ht="84" customHeight="1">
       <c r="A34" s="36" t="n"/>
       <c r="B34" s="107" t="inlineStr">
         <is>
@@ -5465,26 +5264,26 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>Paychex Inc.</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.308</v>
+        <v>0.067</v>
       </c>
       <c r="H34" s="90" t="inlineStr">
         <is>
@@ -5492,16 +5291,16 @@
         </is>
       </c>
       <c r="I34" s="91" t="n">
-        <v>16078.79</v>
+        <v>36258.68</v>
       </c>
       <c r="J34" s="53" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
         </is>
       </c>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="67" customHeight="1">
+    <row r="35" ht="50" customHeight="1">
       <c r="A35" s="28" t="n"/>
       <c r="B35" s="107" t="inlineStr">
         <is>
@@ -5510,26 +5309,26 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation</t>
+          <t>BXP Inc.</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Office REITs</t>
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.258</v>
+        <v>0.066</v>
       </c>
       <c r="H35" s="92" t="inlineStr">
         <is>
@@ -5537,285 +5336,221 @@
         </is>
       </c>
       <c r="I35" s="93" t="n">
-        <v>30713.22</v>
+        <v>11826.25</v>
       </c>
       <c r="J35" s="54" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
+          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
         </is>
       </c>
       <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="50" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B36" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>CSX Corporation</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G36" s="89" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
+        <v>86617.14</v>
+      </c>
+      <c r="J36" s="53" t="inlineStr">
+        <is>
+          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+        </is>
+      </c>
+      <c r="K36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="50" customHeight="1">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
           <t>MET</t>
         </is>
       </c>
-      <c r="D36" s="39" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>MetLife Inc.</t>
         </is>
       </c>
-      <c r="E36" s="40" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G36" s="89" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H36" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I36" s="91" t="n">
+      <c r="G37" s="89" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
         <v>55851.6</v>
       </c>
-      <c r="J36" s="53" t="inlineStr">
+      <c r="J37" s="54" t="inlineStr">
         <is>
           <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
-      <c r="K36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="67" customHeight="1">
-      <c r="A37" s="28" t="n"/>
-      <c r="B37" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>Block Inc.</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="50" customHeight="1">
+      <c r="A38" s="36" t="n"/>
+      <c r="B38" s="109" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C38" s="110" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D38" s="111" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E38" s="112" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F38" s="112" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="G37" s="89" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="H37" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I37" s="93" t="n">
-        <v>40474.89</v>
-      </c>
-      <c r="J37" s="54" t="inlineStr">
-        <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="84" customHeight="1">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G38" s="89" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="H38" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I38" s="91" t="n">
-        <v>388502.86</v>
-      </c>
-      <c r="J38" s="53" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+      <c r="G38" s="113" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H38" s="114" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I38" s="115" t="n">
+        <v>612046.08</v>
+      </c>
+      <c r="J38" s="116" t="inlineStr">
+        <is>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="67" customHeight="1">
+    <row r="39" ht="8" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>The Goldman Sachs Group Inc.</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G39" s="89" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="H39" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I39" s="93" t="n">
-        <v>308648.81</v>
-      </c>
-      <c r="J39" s="54" t="inlineStr">
-        <is>
-          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
-        </is>
-      </c>
+      <c r="B39" s="117" t="n"/>
+      <c r="C39" s="118" t="n"/>
+      <c r="D39" s="119" t="n"/>
+      <c r="E39" s="120" t="n"/>
+      <c r="F39" s="120" t="n"/>
+      <c r="G39" s="121" t="n"/>
+      <c r="H39" s="122" t="n"/>
+      <c r="I39" s="123" t="n"/>
+      <c r="J39" s="124" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="50" customHeight="1">
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="109" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C40" s="110" t="inlineStr">
-        <is>
-          <t>CSX</t>
-        </is>
-      </c>
-      <c r="D40" s="111" t="inlineStr">
-        <is>
-          <t>CSX Corporation</t>
-        </is>
-      </c>
-      <c r="E40" s="112" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F40" s="112" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G40" s="113" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H40" s="114" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I40" s="115" t="n">
-        <v>86617.14</v>
-      </c>
-      <c r="J40" s="116" t="inlineStr">
-        <is>
-          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
-        </is>
-      </c>
+      <c r="B40" s="125" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C40" s="126" t="n"/>
+      <c r="D40" s="126" t="n"/>
+      <c r="E40" s="126" t="n"/>
+      <c r="F40" s="126" t="n"/>
+      <c r="G40" s="126" t="n"/>
+      <c r="H40" s="126" t="n"/>
+      <c r="I40" s="126" t="n"/>
+      <c r="J40" s="126" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="8" customHeight="1">
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="117" t="n"/>
-      <c r="C41" s="118" t="n"/>
-      <c r="D41" s="119" t="n"/>
-      <c r="E41" s="120" t="n"/>
-      <c r="F41" s="120" t="n"/>
-      <c r="G41" s="121" t="n"/>
-      <c r="H41" s="122" t="n"/>
-      <c r="I41" s="123" t="n"/>
-      <c r="J41" s="124" t="n"/>
+      <c r="B41" s="127" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C41" s="128" t="n"/>
+      <c r="D41" s="128" t="n"/>
+      <c r="E41" s="128" t="n"/>
+      <c r="F41" s="128" t="n"/>
+      <c r="G41" s="128" t="n"/>
+      <c r="H41" s="128" t="n"/>
+      <c r="I41" s="128" t="n"/>
+      <c r="J41" s="128" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="34" customHeight="1" thickBot="1">
+    <row r="42" ht="24.6" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="125" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C42" s="126" t="n"/>
-      <c r="D42" s="126" t="n"/>
-      <c r="E42" s="126" t="n"/>
-      <c r="F42" s="126" t="n"/>
-      <c r="G42" s="126" t="n"/>
-      <c r="H42" s="126" t="n"/>
-      <c r="I42" s="126" t="n"/>
-      <c r="J42" s="126" t="n"/>
+      <c r="B42" s="76" t="n"/>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="78" t="n"/>
+      <c r="E42" s="79" t="n"/>
+      <c r="F42" s="79" t="n"/>
+      <c r="G42" s="94" t="n"/>
+      <c r="H42" s="104" t="n"/>
+      <c r="I42" s="105" t="n"/>
+      <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43" ht="28" customHeight="1">
+    <row r="43">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="127" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C43" s="128" t="n"/>
-      <c r="D43" s="128" t="n"/>
-      <c r="E43" s="128" t="n"/>
-      <c r="F43" s="128" t="n"/>
-      <c r="G43" s="128" t="n"/>
-      <c r="H43" s="128" t="n"/>
-      <c r="I43" s="128" t="n"/>
-      <c r="J43" s="128" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="97" t="n"/>
+      <c r="I43" s="43" t="n"/>
+      <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1">
@@ -5898,12 +5633,12 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B41:J41"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B40:J40"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G40">
+  <conditionalFormatting sqref="G8:G38">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$K$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -213,6 +213,16 @@
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF6B7A8D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -518,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -787,16 +797,34 @@
     <xf numFmtId="166" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -805,19 +833,16 @@
     <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="26" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -836,19 +861,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1407,7 +1429,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46226.51410952971</v>
+        <v>46226.55952428059</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1439,9 +1461,9 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="10" customWidth="1" style="14" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="14" customWidth="1" style="14" min="8" max="8"/>
+    <col width="56" customWidth="1" style="11" min="9" max="9"/>
+    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
     <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
@@ -1468,9 +1490,8 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="82" t="n"/>
-      <c r="I2" s="84" t="n">
-        <v>46226.51410952971</v>
+      <c r="H2" s="84" t="n">
+        <v>46226.55952428059</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -1515,24 +1536,32 @@
     </row>
     <row r="6" ht="27.6" customHeight="1">
       <c r="A6" s="24" t="n"/>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Legend:  NEW = new this week    RPT = repeat (2–3 wks)    STRK = streak (4+ wks)</t>
+        </is>
+      </c>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="55" t="inlineStr">
+      <c r="I6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
+      <c r="J6" s="55" t="inlineStr">
+        <is>
+          <t>Chris White, CFA
+Head of Research</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr"/>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -1560,24 +1589,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
+      <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="106" t="inlineStr">
+      <c r="B8" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1592,12 +1617,12 @@
           <t>Extendicare Inc.</t>
         </is>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="106" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="106" t="inlineStr">
         <is>
           <t>Health Care Providers and Services</t>
         </is>
@@ -1605,24 +1630,20 @@
       <c r="G8" s="89" t="n">
         <v>0.656</v>
       </c>
-      <c r="H8" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I8" s="91" t="n">
+      <c r="H8" s="107" t="n">
         <v>2258.51</v>
       </c>
-      <c r="J8" s="53" t="inlineStr">
+      <c r="I8" s="108" t="inlineStr">
         <is>
           <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
         </is>
       </c>
+      <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="106" t="inlineStr">
+      <c r="B9" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1637,12 +1658,12 @@
           <t>South Bow Corporation</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="109" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="109" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
@@ -1650,24 +1671,20 @@
       <c r="G9" s="89" t="n">
         <v>0.473</v>
       </c>
-      <c r="H9" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I9" s="93" t="n">
+      <c r="H9" s="110" t="n">
         <v>7850.04</v>
       </c>
-      <c r="J9" s="54" t="inlineStr">
+      <c r="I9" s="111" t="inlineStr">
         <is>
           <t>South Bow Corporation operates as an energy infrastructure company</t>
         </is>
       </c>
+      <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="106" t="inlineStr">
+      <c r="B10" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1682,12 +1699,12 @@
           <t>Power Corporation of Canada</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E10" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F10" s="106" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
@@ -1695,24 +1712,20 @@
       <c r="G10" s="89" t="n">
         <v>0.345</v>
       </c>
-      <c r="H10" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I10" s="91" t="n">
+      <c r="H10" s="107" t="n">
         <v>38174.66</v>
       </c>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="I10" s="108" t="inlineStr">
         <is>
           <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
         </is>
       </c>
+      <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="67" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="106" t="inlineStr">
+      <c r="B11" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1727,12 +1740,12 @@
           <t>Canadian Utilities Limited</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="109" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="109" t="inlineStr">
         <is>
           <t>Multi-Utilities</t>
         </is>
@@ -1740,24 +1753,20 @@
       <c r="G11" s="89" t="n">
         <v>0.278</v>
       </c>
-      <c r="H11" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I11" s="93" t="n">
+      <c r="H11" s="110" t="n">
         <v>10045.65</v>
       </c>
-      <c r="J11" s="54" t="inlineStr">
+      <c r="I11" s="111" t="inlineStr">
         <is>
           <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
         </is>
       </c>
+      <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
     <row r="12" ht="67" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="106" t="inlineStr">
+      <c r="B12" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1772,12 +1781,12 @@
           <t>Badger Infrastructure Solutions Ltd.</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="106" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="106" t="inlineStr">
         <is>
           <t>Construction and Engineering</t>
         </is>
@@ -1785,24 +1794,20 @@
       <c r="G12" s="89" t="n">
         <v>0.236</v>
       </c>
-      <c r="H12" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I12" s="91" t="n">
+      <c r="H12" s="107" t="n">
         <v>2215.94</v>
       </c>
-      <c r="J12" s="53" t="inlineStr">
+      <c r="I12" s="108" t="inlineStr">
         <is>
           <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
       </c>
+      <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="50" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="106" t="inlineStr">
+      <c r="B13" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1817,12 +1822,12 @@
           <t>Definity Financial Corporation</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="109" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
@@ -1830,24 +1835,20 @@
       <c r="G13" s="89" t="n">
         <v>0.105</v>
       </c>
-      <c r="H13" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I13" s="93" t="n">
+      <c r="H13" s="110" t="n">
         <v>6226.62</v>
       </c>
-      <c r="J13" s="54" t="inlineStr">
+      <c r="I13" s="111" t="inlineStr">
         <is>
           <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
         </is>
       </c>
+      <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
     <row r="14" ht="84" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="107" t="inlineStr">
+      <c r="B14" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -1862,12 +1863,12 @@
           <t>Mattr Corp.</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="106" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F14" s="106" t="inlineStr">
         <is>
           <t>Energy Equipment and Services</t>
         </is>
@@ -1875,24 +1876,20 @@
       <c r="G14" s="89" t="n">
         <v>1.156</v>
       </c>
-      <c r="H14" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I14" s="91" t="n">
+      <c r="H14" s="107" t="n">
         <v>555.83</v>
       </c>
-      <c r="J14" s="53" t="inlineStr">
+      <c r="I14" s="108" t="inlineStr">
         <is>
           <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
+      <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="50" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="107" t="inlineStr">
+      <c r="B15" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -1907,12 +1904,12 @@
           <t>Mullen Group Ltd.</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="109" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
@@ -1920,24 +1917,20 @@
       <c r="G15" s="89" t="n">
         <v>0.578</v>
       </c>
-      <c r="H15" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="n">
+      <c r="H15" s="110" t="n">
         <v>1565.38</v>
       </c>
-      <c r="J15" s="54" t="inlineStr">
+      <c r="I15" s="111" t="inlineStr">
         <is>
           <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
+      <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="50" customHeight="1">
+    <row r="16" ht="67" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="107" t="inlineStr">
+      <c r="B16" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -1952,12 +1945,12 @@
           <t>NFI Group Inc.</t>
         </is>
       </c>
-      <c r="E16" s="40" t="inlineStr">
+      <c r="E16" s="106" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="106" t="inlineStr">
         <is>
           <t>Machinery</t>
         </is>
@@ -1965,24 +1958,20 @@
       <c r="G16" s="89" t="n">
         <v>0.527</v>
       </c>
-      <c r="H16" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I16" s="91" t="n">
+      <c r="H16" s="107" t="n">
         <v>1892.54</v>
       </c>
-      <c r="J16" s="53" t="inlineStr">
+      <c r="I16" s="108" t="inlineStr">
         <is>
           <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
         </is>
       </c>
+      <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
     <row r="17" ht="50" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="107" t="inlineStr">
+      <c r="B17" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -1997,12 +1986,12 @@
           <t>Russel Metals Inc.</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" s="109" t="inlineStr">
         <is>
           <t>Trading Companies and Distributors</t>
         </is>
@@ -2010,24 +1999,20 @@
       <c r="G17" s="89" t="n">
         <v>0.468</v>
       </c>
-      <c r="H17" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I17" s="93" t="n">
+      <c r="H17" s="110" t="n">
         <v>2385.76</v>
       </c>
-      <c r="J17" s="54" t="inlineStr">
+      <c r="I17" s="111" t="inlineStr">
         <is>
           <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
         </is>
       </c>
+      <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="50" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="107" t="inlineStr">
+      <c r="B18" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2042,12 +2027,12 @@
           <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="E18" s="106" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="106" t="inlineStr">
         <is>
           <t>Metals and Mining</t>
         </is>
@@ -2055,24 +2040,20 @@
       <c r="G18" s="89" t="n">
         <v>0.374</v>
       </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="n">
+      <c r="H18" s="107" t="n">
         <v>681.6799999999999</v>
       </c>
-      <c r="J18" s="53" t="inlineStr">
+      <c r="I18" s="108" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
+      <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
     <row r="19" ht="84" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="107" t="inlineStr">
+      <c r="B19" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2087,12 +2068,12 @@
           <t>Canadian Imperial Bank of Commerce</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="109" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
@@ -2100,24 +2081,20 @@
       <c r="G19" s="89" t="n">
         <v>0.342</v>
       </c>
-      <c r="H19" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I19" s="93" t="n">
+      <c r="H19" s="110" t="n">
         <v>101497.85</v>
       </c>
-      <c r="J19" s="54" t="inlineStr">
+      <c r="I19" s="111" t="inlineStr">
         <is>
           <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
+      <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
     <row r="20" ht="50" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="107" t="inlineStr">
+      <c r="B20" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2132,12 +2109,12 @@
           <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
-      <c r="E20" s="40" t="inlineStr">
+      <c r="E20" s="106" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="106" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
@@ -2145,24 +2122,20 @@
       <c r="G20" s="89" t="n">
         <v>0.316</v>
       </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I20" s="91" t="n">
+      <c r="H20" s="107" t="n">
         <v>28518.97</v>
       </c>
-      <c r="J20" s="53" t="inlineStr">
+      <c r="I20" s="108" t="inlineStr">
         <is>
           <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
+      <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
     <row r="21" ht="67" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="107" t="inlineStr">
+      <c r="B21" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2177,12 +2150,12 @@
           <t>Canadian Pacific Kansas City Limited</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="F21" s="109" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
@@ -2190,24 +2163,20 @@
       <c r="G21" s="89" t="n">
         <v>0.298</v>
       </c>
-      <c r="H21" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I21" s="93" t="n">
+      <c r="H21" s="110" t="n">
         <v>79823.21000000001</v>
       </c>
-      <c r="J21" s="54" t="inlineStr">
+      <c r="I21" s="111" t="inlineStr">
         <is>
           <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
+      <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
     <row r="22" ht="67" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="107" t="inlineStr">
+      <c r="B22" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2222,12 +2191,12 @@
           <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
-      <c r="E22" s="40" t="inlineStr">
+      <c r="E22" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="106" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
@@ -2235,24 +2204,20 @@
       <c r="G22" s="89" t="n">
         <v>0.252</v>
       </c>
-      <c r="H22" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I22" s="91" t="n">
+      <c r="H22" s="107" t="n">
         <v>976.67</v>
       </c>
-      <c r="J22" s="53" t="inlineStr">
+      <c r="I22" s="108" t="inlineStr">
         <is>
           <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
         </is>
       </c>
+      <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
     <row r="23" ht="50" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="107" t="inlineStr">
+      <c r="B23" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2267,12 +2232,12 @@
           <t>Dexterra Group Inc.</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F23" s="32" t="inlineStr">
+      <c r="F23" s="109" t="inlineStr">
         <is>
           <t>Commercial Services and Supplies</t>
         </is>
@@ -2280,24 +2245,20 @@
       <c r="G23" s="89" t="n">
         <v>0.229</v>
       </c>
-      <c r="H23" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I23" s="93" t="n">
+      <c r="H23" s="110" t="n">
         <v>576.85</v>
       </c>
-      <c r="J23" s="54" t="inlineStr">
+      <c r="I23" s="111" t="inlineStr">
         <is>
           <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
+      <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="67" customHeight="1">
+    <row r="24" ht="84" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="107" t="inlineStr">
+      <c r="B24" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2312,12 +2273,12 @@
           <t>Spin Master Corp.</t>
         </is>
       </c>
-      <c r="E24" s="40" t="inlineStr">
+      <c r="E24" s="106" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="F24" s="40" t="inlineStr">
+      <c r="F24" s="106" t="inlineStr">
         <is>
           <t>Leisure Products</t>
         </is>
@@ -2325,24 +2286,20 @@
       <c r="G24" s="89" t="n">
         <v>0.196</v>
       </c>
-      <c r="H24" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I24" s="91" t="n">
+      <c r="H24" s="107" t="n">
         <v>1330.28</v>
       </c>
-      <c r="J24" s="53" t="inlineStr">
+      <c r="I24" s="108" t="inlineStr">
         <is>
           <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
+      <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="67" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="107" t="inlineStr">
+      <c r="B25" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2357,12 +2314,12 @@
           <t>Doman Building Materials Group Ltd.</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E25" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="F25" s="109" t="inlineStr">
         <is>
           <t>Trading Companies and Distributors</t>
         </is>
@@ -2370,24 +2327,20 @@
       <c r="G25" s="89" t="n">
         <v>0.192</v>
       </c>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I25" s="93" t="n">
+      <c r="H25" s="110" t="n">
         <v>676.4400000000001</v>
       </c>
-      <c r="J25" s="54" t="inlineStr">
+      <c r="I25" s="111" t="inlineStr">
         <is>
           <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
         </is>
       </c>
+      <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="50" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="107" t="inlineStr">
+      <c r="B26" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -2402,12 +2355,12 @@
           <t>Black Diamond Group Limited</t>
         </is>
       </c>
-      <c r="E26" s="40" t="inlineStr">
+      <c r="E26" s="106" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F26" s="40" t="inlineStr">
+      <c r="F26" s="106" t="inlineStr">
         <is>
           <t>Commercial Services and Supplies</t>
         </is>
@@ -2415,24 +2368,20 @@
       <c r="G26" s="89" t="n">
         <v>0.178</v>
       </c>
-      <c r="H26" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I26" s="91" t="n">
+      <c r="H26" s="107" t="n">
         <v>927.72</v>
       </c>
-      <c r="J26" s="53" t="inlineStr">
+      <c r="I26" s="108" t="inlineStr">
         <is>
           <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
+      <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="50" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="108" t="inlineStr">
+      <c r="B27" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -2447,12 +2396,12 @@
           <t>ADF Group Inc.</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E27" s="109" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F27" s="109" t="inlineStr">
         <is>
           <t>Metals and Mining</t>
         </is>
@@ -2460,24 +2409,20 @@
       <c r="G27" s="89" t="n">
         <v>1.168</v>
       </c>
-      <c r="H27" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I27" s="93" t="n">
+      <c r="H27" s="110" t="n">
         <v>284.57</v>
       </c>
-      <c r="J27" s="54" t="inlineStr">
+      <c r="I27" s="111" t="inlineStr">
         <is>
           <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
         </is>
       </c>
+      <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
     <row r="28" ht="67" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="108" t="inlineStr">
+      <c r="B28" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -2492,12 +2437,12 @@
           <t>Great-West Lifeco Inc.</t>
         </is>
       </c>
-      <c r="E28" s="40" t="inlineStr">
+      <c r="E28" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="F28" s="106" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
@@ -2505,24 +2450,20 @@
       <c r="G28" s="89" t="n">
         <v>0.458</v>
       </c>
-      <c r="H28" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I28" s="91" t="n">
+      <c r="H28" s="107" t="n">
         <v>53011.04</v>
       </c>
-      <c r="J28" s="53" t="inlineStr">
+      <c r="I28" s="108" t="inlineStr">
         <is>
           <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
         </is>
       </c>
+      <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
     <row r="29" ht="67" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="108" t="inlineStr">
+      <c r="B29" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -2537,12 +2478,12 @@
           <t>K-Bro Linen Inc.</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
+      <c r="E29" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="F29" s="109" t="inlineStr">
         <is>
           <t>Commercial Services and Supplies</t>
         </is>
@@ -2550,24 +2491,20 @@
       <c r="G29" s="89" t="n">
         <v>0.357</v>
       </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I29" s="93" t="n">
+      <c r="H29" s="110" t="n">
         <v>390.27</v>
       </c>
-      <c r="J29" s="54" t="inlineStr">
+      <c r="I29" s="111" t="inlineStr">
         <is>
           <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
+      <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
     <row r="30" ht="101" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="108" t="inlineStr">
+      <c r="B30" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -2582,12 +2519,12 @@
           <t>Sun Life Financial Inc.</t>
         </is>
       </c>
-      <c r="E30" s="40" t="inlineStr">
+      <c r="E30" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="106" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
@@ -2595,24 +2532,20 @@
       <c r="G30" s="89" t="n">
         <v>0.35</v>
       </c>
-      <c r="H30" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I30" s="91" t="n">
+      <c r="H30" s="107" t="n">
         <v>41467.31</v>
       </c>
-      <c r="J30" s="53" t="inlineStr">
+      <c r="I30" s="108" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
+      <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="67" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="108" t="inlineStr">
+      <c r="B31" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -2627,12 +2560,12 @@
           <t>Canadian National Railway Company</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
+      <c r="E31" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="F31" s="109" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
@@ -2640,24 +2573,20 @@
       <c r="G31" s="89" t="n">
         <v>0.331</v>
       </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I31" s="93" t="n">
+      <c r="H31" s="110" t="n">
         <v>72839.50999999999</v>
       </c>
-      <c r="J31" s="54" t="inlineStr">
+      <c r="I31" s="111" t="inlineStr">
         <is>
           <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
+      <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="50" customHeight="1">
+    <row r="32" ht="67" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="108" t="inlineStr">
+      <c r="B32" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -2672,12 +2601,12 @@
           <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
-      <c r="E32" s="40" t="inlineStr">
+      <c r="E32" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="106" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
@@ -2685,24 +2614,20 @@
       <c r="G32" s="89" t="n">
         <v>0.24</v>
       </c>
-      <c r="H32" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I32" s="91" t="n">
+      <c r="H32" s="107" t="n">
         <v>11282.66</v>
       </c>
-      <c r="J32" s="53" t="inlineStr">
+      <c r="I32" s="108" t="inlineStr">
         <is>
           <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
+      <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="67" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="108" t="inlineStr">
+      <c r="B33" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -2717,12 +2642,12 @@
           <t>Manulife Financial Corporation</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E33" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="F33" s="109" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
@@ -2730,111 +2655,103 @@
       <c r="G33" s="89" t="n">
         <v>0.215</v>
       </c>
-      <c r="H33" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I33" s="93" t="n">
+      <c r="H33" s="110" t="n">
         <v>65572.44</v>
       </c>
-      <c r="J33" s="54" t="inlineStr">
+      <c r="I33" s="111" t="inlineStr">
         <is>
           <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
+      <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="67" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="109" t="inlineStr">
+      <c r="B34" s="115" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C34" s="110" t="inlineStr">
+      <c r="C34" s="116" t="inlineStr">
         <is>
           <t>IFP</t>
         </is>
       </c>
-      <c r="D34" s="111" t="inlineStr">
+      <c r="D34" s="117" t="inlineStr">
         <is>
           <t>Interfor Corporation</t>
         </is>
       </c>
-      <c r="E34" s="112" t="inlineStr">
+      <c r="E34" s="118" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F34" s="112" t="inlineStr">
+      <c r="F34" s="118" t="inlineStr">
         <is>
           <t>Paper and Forest Products</t>
         </is>
       </c>
-      <c r="G34" s="113" t="n">
+      <c r="G34" s="119" t="n">
         <v>0.202</v>
       </c>
-      <c r="H34" s="114" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I34" s="115" t="n">
+      <c r="H34" s="120" t="n">
         <v>501.72</v>
       </c>
-      <c r="J34" s="116" t="inlineStr">
+      <c r="I34" s="121" t="inlineStr">
         <is>
           <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
+      <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="8" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="117" t="n"/>
-      <c r="C35" s="118" t="n"/>
-      <c r="D35" s="119" t="n"/>
-      <c r="E35" s="120" t="n"/>
-      <c r="F35" s="120" t="n"/>
-      <c r="G35" s="121" t="n"/>
-      <c r="H35" s="122" t="n"/>
-      <c r="I35" s="123" t="n"/>
-      <c r="J35" s="124" t="n"/>
+      <c r="B35" s="122" t="n"/>
+      <c r="C35" s="123" t="n"/>
+      <c r="D35" s="124" t="n"/>
+      <c r="E35" s="125" t="n"/>
+      <c r="F35" s="125" t="n"/>
+      <c r="G35" s="126" t="n"/>
+      <c r="H35" s="127" t="n"/>
+      <c r="I35" s="128" t="n"/>
+      <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="125" t="inlineStr">
+      <c r="B36" s="129" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C36" s="126" t="n"/>
-      <c r="D36" s="126" t="n"/>
-      <c r="E36" s="126" t="n"/>
-      <c r="F36" s="126" t="n"/>
-      <c r="G36" s="126" t="n"/>
-      <c r="H36" s="126" t="n"/>
-      <c r="I36" s="126" t="n"/>
-      <c r="J36" s="126" t="n"/>
+      <c r="C36" s="130" t="n"/>
+      <c r="D36" s="130" t="n"/>
+      <c r="E36" s="130" t="n"/>
+      <c r="F36" s="130" t="n"/>
+      <c r="G36" s="130" t="n"/>
+      <c r="H36" s="130" t="n"/>
+      <c r="I36" s="130" t="n"/>
+      <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="127" t="inlineStr">
+      <c r="B37" s="131" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C37" s="128" t="n"/>
-      <c r="D37" s="128" t="n"/>
-      <c r="E37" s="128" t="n"/>
-      <c r="F37" s="128" t="n"/>
-      <c r="G37" s="128" t="n"/>
-      <c r="H37" s="128" t="n"/>
-      <c r="I37" s="128" t="n"/>
-      <c r="J37" s="128" t="n"/>
+      <c r="C37" s="132" t="n"/>
+      <c r="D37" s="132" t="n"/>
+      <c r="E37" s="132" t="n"/>
+      <c r="F37" s="132" t="n"/>
+      <c r="G37" s="132" t="n"/>
+      <c r="H37" s="132" t="n"/>
+      <c r="I37" s="132" t="n"/>
+      <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="20.4" customHeight="1">
@@ -2845,8 +2762,8 @@
       <c r="E38" s="40" t="n"/>
       <c r="F38" s="40" t="n"/>
       <c r="G38" s="89" t="n"/>
-      <c r="H38" s="90" t="n"/>
-      <c r="I38" s="91" t="n"/>
+      <c r="H38" s="91" t="n"/>
+      <c r="I38" s="53" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
@@ -2858,8 +2775,8 @@
       <c r="E39" s="32" t="n"/>
       <c r="F39" s="32" t="n"/>
       <c r="G39" s="89" t="n"/>
-      <c r="H39" s="92" t="n"/>
-      <c r="I39" s="93" t="n"/>
+      <c r="H39" s="93" t="n"/>
+      <c r="I39" s="54" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
@@ -2871,8 +2788,8 @@
       <c r="E40" s="40" t="n"/>
       <c r="F40" s="40" t="n"/>
       <c r="G40" s="89" t="n"/>
-      <c r="H40" s="90" t="n"/>
-      <c r="I40" s="91" t="n"/>
+      <c r="H40" s="91" t="n"/>
+      <c r="I40" s="53" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
@@ -2884,8 +2801,8 @@
       <c r="E41" s="72" t="n"/>
       <c r="F41" s="72" t="n"/>
       <c r="G41" s="94" t="n"/>
-      <c r="H41" s="95" t="n"/>
-      <c r="I41" s="96" t="n"/>
+      <c r="H41" s="96" t="n"/>
+      <c r="I41" s="74" t="n"/>
       <c r="J41" s="74" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
@@ -2897,7 +2814,7 @@
       <c r="E42" s="43" t="n"/>
       <c r="F42" s="43" t="n"/>
       <c r="G42" s="43" t="n"/>
-      <c r="H42" s="97" t="n"/>
+      <c r="H42" s="43" t="n"/>
       <c r="I42" s="43" t="n"/>
       <c r="J42" s="43" t="n"/>
       <c r="K42" s="43" t="n"/>
@@ -2910,7 +2827,7 @@
       <c r="E43" s="43" t="n"/>
       <c r="F43" s="43" t="n"/>
       <c r="G43" s="43" t="n"/>
-      <c r="H43" s="97" t="n"/>
+      <c r="H43" s="43" t="n"/>
       <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
@@ -2923,8 +2840,8 @@
       <c r="E44" s="59" t="n"/>
       <c r="F44" s="59" t="n"/>
       <c r="G44" s="59" t="n"/>
-      <c r="H44" s="98" t="n"/>
-      <c r="I44" s="59" t="n"/>
+      <c r="H44" s="59" t="n"/>
+      <c r="I44" s="60" t="n"/>
       <c r="J44" s="60" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
@@ -2936,8 +2853,8 @@
       <c r="E45" s="64" t="n"/>
       <c r="F45" s="64" t="n"/>
       <c r="G45" s="64" t="n"/>
-      <c r="H45" s="99" t="n"/>
-      <c r="I45" s="64" t="n"/>
+      <c r="H45" s="64" t="n"/>
+      <c r="I45" s="65" t="n"/>
       <c r="J45" s="65" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
@@ -2949,8 +2866,8 @@
       <c r="E46" s="62" t="n"/>
       <c r="F46" s="62" t="n"/>
       <c r="G46" s="62" t="n"/>
-      <c r="H46" s="100" t="n"/>
-      <c r="I46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="63" t="n"/>
       <c r="J46" s="63" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
@@ -2962,7 +2879,7 @@
       <c r="E47" s="43" t="n"/>
       <c r="F47" s="43" t="n"/>
       <c r="G47" s="43" t="n"/>
-      <c r="H47" s="97" t="n"/>
+      <c r="H47" s="43" t="n"/>
       <c r="I47" s="43" t="n"/>
       <c r="J47" s="43" t="n"/>
       <c r="K47" s="43" t="n"/>
@@ -2975,7 +2892,7 @@
       <c r="E48" s="47" t="n"/>
       <c r="F48" s="47" t="n"/>
       <c r="G48" s="47" t="n"/>
-      <c r="H48" s="101" t="n"/>
+      <c r="H48" s="47" t="n"/>
       <c r="I48" s="47" t="n"/>
       <c r="J48" s="47" t="n"/>
       <c r="K48" s="43" t="n"/>
@@ -2988,17 +2905,18 @@
       <c r="E49" s="43" t="n"/>
       <c r="F49" s="43" t="n"/>
       <c r="G49" s="43" t="n"/>
-      <c r="H49" s="97" t="n"/>
+      <c r="H49" s="43" t="n"/>
       <c r="I49" s="43" t="n"/>
       <c r="J49" s="43" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G34">
     <cfRule type="colorScale" priority="1371">
@@ -3949,9 +3867,9 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="10" customWidth="1" style="14" min="8" max="8"/>
-    <col width="14" customWidth="1" style="11" min="9" max="9"/>
-    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="14" customWidth="1" style="14" min="8" max="8"/>
+    <col width="56" customWidth="1" style="11" min="9" max="9"/>
+    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
     <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
@@ -3978,9 +3896,8 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="82" t="n"/>
-      <c r="I2" s="84" t="n">
-        <v>46226.51410952971</v>
+      <c r="H2" s="84" t="n">
+        <v>46226.55952428059</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -4025,24 +3942,32 @@
     </row>
     <row r="6" ht="27.6" customHeight="1">
       <c r="A6" s="24" t="n"/>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Legend:  NEW = new this week    RPT = repeat (2–3 wks)    STRK = streak (4+ wks)</t>
+        </is>
+      </c>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="55" t="inlineStr">
+      <c r="I6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
+      <c r="J6" s="55" t="inlineStr">
+        <is>
+          <t>Chris White, CFA
+Head of Research</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr"/>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -4070,24 +3995,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
+      <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="106" t="inlineStr">
+      <c r="B8" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4102,37 +4023,33 @@
           <t>DaVita Inc.</t>
         </is>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="106" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="106" t="inlineStr">
         <is>
           <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.159</v>
-      </c>
-      <c r="H8" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I8" s="91" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="H8" s="107" t="n">
         <v>12725.72</v>
       </c>
-      <c r="J8" s="53" t="inlineStr">
+      <c r="I8" s="108" t="inlineStr">
         <is>
           <t>DaVita Inc provides kidney dialysis services for patients suffering from chronic kidney failure in the United States</t>
         </is>
       </c>
+      <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="106" t="inlineStr">
+      <c r="B9" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4147,37 +4064,33 @@
           <t>Palo Alto Networks Inc.</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="109" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="109" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H9" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I9" s="93" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="H9" s="110" t="n">
         <v>213908.98</v>
       </c>
-      <c r="J9" s="54" t="inlineStr">
+      <c r="I9" s="111" t="inlineStr">
         <is>
           <t>Palo Alto Networks Inc provides cybersecurity solutions in the Americas Europe the Middle East Africa the Asia Pacific and Japan</t>
         </is>
       </c>
+      <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="84" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="106" t="inlineStr">
+      <c r="B10" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4192,37 +4105,33 @@
           <t>The Travelers Companies Inc.</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E10" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F10" s="106" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="H10" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I10" s="91" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H10" s="107" t="n">
         <v>64533.41</v>
       </c>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="I10" s="108" t="inlineStr">
         <is>
           <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
+      <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="67" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="106" t="inlineStr">
+      <c r="B11" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4237,127 +4146,115 @@
           <t>Archer-Daniels-Midland Company</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="109" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="109" t="inlineStr">
         <is>
           <t>Food Products</t>
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="H11" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I11" s="93" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H11" s="110" t="n">
         <v>39380.19</v>
       </c>
-      <c r="J11" s="54" t="inlineStr">
+      <c r="I11" s="111" t="inlineStr">
         <is>
           <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
+      <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="50" customHeight="1">
+    <row r="12" ht="33" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="106" t="inlineStr">
+      <c r="B12" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="C12" s="38" t="inlineStr">
         <is>
+          <t>GWW</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>W.W. Grainger Inc.</t>
+        </is>
+      </c>
+      <c r="E12" s="106" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F12" s="106" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H12" s="107" t="n">
+        <v>62147.38</v>
+      </c>
+      <c r="I12" s="108" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="53" t="n"/>
+      <c r="K12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="112" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>CVS Health Corporation</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E13" s="109" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F13" s="109" t="inlineStr">
         <is>
           <t>Health Care Providers and Services</t>
         </is>
       </c>
-      <c r="G12" s="89" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H12" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I12" s="91" t="n">
+      <c r="G13" s="89" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="H13" s="110" t="n">
         <v>125211.85</v>
       </c>
-      <c r="J12" s="53" t="inlineStr">
+      <c r="I13" s="111" t="inlineStr">
         <is>
           <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
-      <c r="K12" s="36" t="n"/>
-    </row>
-    <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="106" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>GWW</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>W.W. Grainger Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G13" s="89" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H13" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I13" s="93" t="n">
-        <v>62147.38</v>
-      </c>
-      <c r="J13" s="54" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
+      <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
     <row r="14" ht="67" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="106" t="inlineStr">
+      <c r="B14" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4372,37 +4269,33 @@
           <t>Principal Financial Group Inc.</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F14" s="106" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="H14" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I14" s="91" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H14" s="107" t="n">
         <v>23624.19</v>
       </c>
-      <c r="J14" s="53" t="inlineStr">
+      <c r="I14" s="108" t="inlineStr">
         <is>
           <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
+      <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="33" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="106" t="inlineStr">
+      <c r="B15" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4417,37 +4310,33 @@
           <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="109" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="H15" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="H15" s="110" t="n">
         <v>834204.25</v>
       </c>
-      <c r="J15" s="54" t="inlineStr">
+      <c r="I15" s="111" t="inlineStr">
         <is>
           <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
+      <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
     <row r="16" ht="50" customHeight="1">
       <c r="A16" s="36" t="n"/>
-      <c r="B16" s="106" t="inlineStr">
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4462,37 +4351,33 @@
           <t>Everest Group Ltd.</t>
         </is>
       </c>
-      <c r="E16" s="40" t="inlineStr">
+      <c r="E16" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
+      <c r="F16" s="106" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H16" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I16" s="91" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="H16" s="107" t="n">
         <v>13320.91</v>
       </c>
-      <c r="J16" s="53" t="inlineStr">
+      <c r="I16" s="108" t="inlineStr">
         <is>
           <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
+      <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
     <row r="17" ht="50" customHeight="1">
       <c r="A17" s="28" t="n"/>
-      <c r="B17" s="107" t="inlineStr">
+      <c r="B17" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -4507,37 +4392,33 @@
           <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="109" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" s="109" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="H17" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I17" s="93" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="H17" s="110" t="n">
         <v>77721.12</v>
       </c>
-      <c r="J17" s="54" t="inlineStr">
+      <c r="I17" s="111" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
+      <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
     <row r="18" ht="84" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="107" t="inlineStr">
+      <c r="B18" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -4552,37 +4433,33 @@
           <t>Valero Energy Corporation</t>
         </is>
       </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="E18" s="106" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F18" s="106" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="H18" s="107" t="n">
         <v>77190.64999999999</v>
       </c>
-      <c r="J18" s="53" t="inlineStr">
+      <c r="I18" s="108" t="inlineStr">
         <is>
           <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
+      <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
     <row r="19" ht="50" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="107" t="inlineStr">
+      <c r="B19" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -4597,37 +4474,33 @@
           <t>State Street Corporation</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="109" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="H19" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I19" s="93" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H19" s="110" t="n">
         <v>44725.83</v>
       </c>
-      <c r="J19" s="54" t="inlineStr">
+      <c r="I19" s="111" t="inlineStr">
         <is>
           <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
+      <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
     <row r="20" ht="50" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="107" t="inlineStr">
+      <c r="B20" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -4642,172 +4515,156 @@
           <t>J.B. Hunt Transport Services Inc.</t>
         </is>
       </c>
-      <c r="E20" s="40" t="inlineStr">
+      <c r="E20" s="106" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="106" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I20" s="91" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="H20" s="107" t="n">
         <v>26566.73</v>
       </c>
-      <c r="J20" s="53" t="inlineStr">
+      <c r="I20" s="108" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
+      <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="67" customHeight="1">
+    <row r="21" ht="50" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="107" t="inlineStr">
+      <c r="B21" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation</t>
+        </is>
+      </c>
+      <c r="E21" s="109" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F21" s="109" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="H21" s="110" t="n">
+        <v>158667.48</v>
+      </c>
+      <c r="I21" s="111" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+        </is>
+      </c>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="67" customHeight="1">
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="113" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
+        <is>
           <t>WELL</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D22" s="39" t="inlineStr">
         <is>
           <t>Welltower Inc.</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E22" s="106" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="F22" s="106" t="inlineStr">
         <is>
           <t>Health Care REITs</t>
         </is>
       </c>
-      <c r="G21" s="89" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="H21" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I21" s="93" t="n">
+      <c r="G22" s="89" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="H22" s="107" t="n">
         <v>148209.56</v>
       </c>
-      <c r="J21" s="54" t="inlineStr">
+      <c r="I22" s="108" t="inlineStr">
         <is>
           <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
-      <c r="K21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="33" customHeight="1">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="107" t="inlineStr">
+      <c r="J22" s="53" t="n"/>
+      <c r="K22" s="36" t="n"/>
+    </row>
+    <row r="23" ht="33" customHeight="1">
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>BBY</t>
         </is>
       </c>
-      <c r="D22" s="39" t="inlineStr">
+      <c r="D23" s="31" t="inlineStr">
         <is>
           <t>Best Buy Co. Inc.</t>
         </is>
       </c>
-      <c r="E22" s="40" t="inlineStr">
+      <c r="E23" s="109" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F23" s="109" t="inlineStr">
         <is>
           <t>Specialty Retail</t>
         </is>
       </c>
-      <c r="G22" s="89" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="H22" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I22" s="91" t="n">
+      <c r="G23" s="89" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="H23" s="110" t="n">
         <v>16078.79</v>
       </c>
-      <c r="J22" s="53" t="inlineStr">
+      <c r="I23" s="111" t="inlineStr">
         <is>
           <t>Best Buy Co</t>
         </is>
       </c>
-      <c r="K22" s="36" t="n"/>
-    </row>
-    <row r="23" ht="67" customHeight="1">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>Globe Life Inc.</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F23" s="32" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="H23" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I23" s="93" t="n">
-        <v>12644.53</v>
-      </c>
-      <c r="J23" s="54" t="inlineStr">
-        <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
-        </is>
-      </c>
+      <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
     <row r="24" ht="67" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="107" t="inlineStr">
+      <c r="B24" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -4822,127 +4679,115 @@
           <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
-      <c r="E24" s="40" t="inlineStr">
+      <c r="E24" s="106" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="F24" s="40" t="inlineStr">
+      <c r="F24" s="106" t="inlineStr">
         <is>
           <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="H24" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I24" s="91" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H24" s="107" t="n">
         <v>14353.95</v>
       </c>
-      <c r="J24" s="53" t="inlineStr">
+      <c r="I24" s="108" t="inlineStr">
         <is>
           <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
+      <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="50" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="107" t="inlineStr">
+      <c r="B25" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F25" s="32" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E25" s="109" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F25" s="109" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I25" s="93" t="n">
-        <v>158667.48</v>
-      </c>
-      <c r="J25" s="54" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
-        </is>
-      </c>
+        <v>0.261</v>
+      </c>
+      <c r="H25" s="110" t="n">
+        <v>4309578.68</v>
+      </c>
+      <c r="I25" s="111" t="inlineStr">
+        <is>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+        </is>
+      </c>
+      <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="50" customHeight="1">
+    <row r="26" ht="67" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="107" t="inlineStr">
+      <c r="B26" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="E26" s="40" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F26" s="40" t="inlineStr">
-        <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Globe Life Inc.</t>
+        </is>
+      </c>
+      <c r="E26" s="106" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F26" s="106" t="inlineStr">
+        <is>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="H26" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I26" s="91" t="n">
-        <v>4309578.68</v>
-      </c>
-      <c r="J26" s="53" t="inlineStr">
-        <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
-        </is>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="H26" s="107" t="n">
+        <v>12644.53</v>
+      </c>
+      <c r="I26" s="108" t="inlineStr">
+        <is>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+        </is>
+      </c>
+      <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="84" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="107" t="inlineStr">
+      <c r="B27" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -4957,127 +4802,115 @@
           <t>Bank of America Corporation</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E27" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F27" s="109" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="H27" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I27" s="93" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="H27" s="110" t="n">
         <v>388502.86</v>
       </c>
-      <c r="J27" s="54" t="inlineStr">
+      <c r="I27" s="111" t="inlineStr">
         <is>
           <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
+      <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
     <row r="28" ht="67" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="107" t="inlineStr">
+      <c r="B28" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="inlineStr">
-        <is>
-          <t>Beverages</t>
+          <t>Block Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="106" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F28" s="106" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="H28" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I28" s="91" t="n">
-        <v>89144.46000000001</v>
-      </c>
-      <c r="J28" s="53" t="inlineStr">
-        <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
-        </is>
-      </c>
+        <v>0.173</v>
+      </c>
+      <c r="H28" s="107" t="n">
+        <v>40474.89</v>
+      </c>
+      <c r="I28" s="108" t="inlineStr">
+        <is>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
     <row r="29" ht="67" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="107" t="inlineStr">
+      <c r="B29" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Block Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
+          <t>Monster Beverage Corporation</t>
+        </is>
+      </c>
+      <c r="E29" s="109" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F29" s="109" t="inlineStr">
+        <is>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I29" s="93" t="n">
-        <v>40474.89</v>
-      </c>
-      <c r="J29" s="54" t="inlineStr">
-        <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
-        </is>
-      </c>
+        <v>0.164</v>
+      </c>
+      <c r="H29" s="110" t="n">
+        <v>89144.46000000001</v>
+      </c>
+      <c r="I29" s="111" t="inlineStr">
+        <is>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
     <row r="30" ht="84" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="107" t="inlineStr">
+      <c r="B30" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -5092,37 +4925,33 @@
           <t>Citizens Financial Group Inc.</t>
         </is>
       </c>
-      <c r="E30" s="40" t="inlineStr">
+      <c r="E30" s="106" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="106" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="H30" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I30" s="91" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="H30" s="107" t="n">
         <v>27585.86</v>
       </c>
-      <c r="J30" s="53" t="inlineStr">
+      <c r="I30" s="108" t="inlineStr">
         <is>
           <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
+      <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="67" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="107" t="inlineStr">
+      <c r="B31" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -5137,37 +4966,33 @@
           <t>Fifth Third Bancorp</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
+      <c r="E31" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="F31" s="109" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I31" s="93" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="H31" s="110" t="n">
         <v>47955.66</v>
       </c>
-      <c r="J31" s="54" t="inlineStr">
+      <c r="I31" s="111" t="inlineStr">
         <is>
           <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
+      <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="67" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="107" t="inlineStr">
+      <c r="B32" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -5182,37 +5007,33 @@
           <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
-      <c r="E32" s="40" t="inlineStr">
+      <c r="E32" s="106" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="106" t="inlineStr">
         <is>
           <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="H32" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I32" s="91" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="H32" s="107" t="n">
         <v>21453.67</v>
       </c>
-      <c r="J32" s="53" t="inlineStr">
+      <c r="I32" s="108" t="inlineStr">
         <is>
           <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
+      <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="50" customHeight="1">
+    <row r="33" ht="67" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="107" t="inlineStr">
+      <c r="B33" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -5227,127 +5048,115 @@
           <t>Prudential Financial Inc.</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E33" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="F33" s="109" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H33" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I33" s="93" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="H33" s="110" t="n">
         <v>36717.82</v>
       </c>
-      <c r="J33" s="54" t="inlineStr">
+      <c r="I33" s="111" t="inlineStr">
         <is>
           <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
+      <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="84" customHeight="1">
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="107" t="inlineStr">
+      <c r="B34" s="113" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
+          <t>BXP</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>BXP Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="106" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F34" s="106" t="inlineStr">
+        <is>
+          <t>Office REITs</t>
+        </is>
+      </c>
+      <c r="G34" s="89" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="H34" s="107" t="n">
+        <v>11826.25</v>
+      </c>
+      <c r="I34" s="108" t="inlineStr">
+        <is>
+          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
+        </is>
+      </c>
+      <c r="J34" s="53" t="n"/>
+      <c r="K34" s="36" t="n"/>
+    </row>
+    <row r="35" ht="84" customHeight="1">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="113" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
           <t>PAYX</t>
         </is>
       </c>
-      <c r="D34" s="39" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>Paychex Inc.</t>
         </is>
       </c>
-      <c r="E34" s="40" t="inlineStr">
+      <c r="E35" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F35" s="109" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
       </c>
-      <c r="G34" s="89" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="H34" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I34" s="91" t="n">
+      <c r="G35" s="89" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="H35" s="110" t="n">
         <v>36258.68</v>
       </c>
-      <c r="J34" s="53" t="inlineStr">
+      <c r="I35" s="111" t="inlineStr">
         <is>
           <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
         </is>
       </c>
-      <c r="K34" s="36" t="n"/>
-    </row>
-    <row r="35" ht="50" customHeight="1">
-      <c r="A35" s="28" t="n"/>
-      <c r="B35" s="107" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>BXP</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>BXP Inc.</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>Office REITs</t>
-        </is>
-      </c>
-      <c r="G35" s="89" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="H35" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I35" s="93" t="n">
-        <v>11826.25</v>
-      </c>
-      <c r="J35" s="54" t="inlineStr">
-        <is>
-          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
-        </is>
-      </c>
+      <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="50" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="108" t="inlineStr">
+      <c r="B36" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -5362,37 +5171,33 @@
           <t>CSX Corporation</t>
         </is>
       </c>
-      <c r="E36" s="40" t="inlineStr">
+      <c r="E36" s="106" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="106" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="H36" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I36" s="91" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="H36" s="107" t="n">
         <v>86617.14</v>
       </c>
-      <c r="J36" s="53" t="inlineStr">
+      <c r="I36" s="108" t="inlineStr">
         <is>
           <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
+      <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="50" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="108" t="inlineStr">
+      <c r="B37" s="114" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
@@ -5407,124 +5212,116 @@
           <t>MetLife Inc.</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E37" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F37" s="109" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="H37" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I37" s="93" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H37" s="110" t="n">
         <v>55851.6</v>
       </c>
-      <c r="J37" s="54" t="inlineStr">
+      <c r="I37" s="111" t="inlineStr">
         <is>
           <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
+      <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="50" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="109" t="inlineStr">
+      <c r="B38" s="115" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C38" s="110" t="inlineStr">
+      <c r="C38" s="116" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D38" s="111" t="inlineStr">
+      <c r="D38" s="117" t="inlineStr">
         <is>
           <t>Visa Inc.</t>
         </is>
       </c>
-      <c r="E38" s="112" t="inlineStr">
+      <c r="E38" s="118" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F38" s="112" t="inlineStr">
+      <c r="F38" s="118" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="G38" s="113" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H38" s="114" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I38" s="115" t="n">
+      <c r="G38" s="119" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H38" s="120" t="n">
         <v>612046.08</v>
       </c>
-      <c r="J38" s="116" t="inlineStr">
+      <c r="I38" s="121" t="inlineStr">
         <is>
           <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
+      <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="8" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="117" t="n"/>
-      <c r="C39" s="118" t="n"/>
-      <c r="D39" s="119" t="n"/>
-      <c r="E39" s="120" t="n"/>
-      <c r="F39" s="120" t="n"/>
-      <c r="G39" s="121" t="n"/>
-      <c r="H39" s="122" t="n"/>
-      <c r="I39" s="123" t="n"/>
-      <c r="J39" s="124" t="n"/>
+      <c r="B39" s="122" t="n"/>
+      <c r="C39" s="123" t="n"/>
+      <c r="D39" s="124" t="n"/>
+      <c r="E39" s="125" t="n"/>
+      <c r="F39" s="125" t="n"/>
+      <c r="G39" s="126" t="n"/>
+      <c r="H39" s="127" t="n"/>
+      <c r="I39" s="128" t="n"/>
+      <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="125" t="inlineStr">
+      <c r="B40" s="129" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C40" s="126" t="n"/>
-      <c r="D40" s="126" t="n"/>
-      <c r="E40" s="126" t="n"/>
-      <c r="F40" s="126" t="n"/>
-      <c r="G40" s="126" t="n"/>
-      <c r="H40" s="126" t="n"/>
-      <c r="I40" s="126" t="n"/>
-      <c r="J40" s="126" t="n"/>
+      <c r="C40" s="130" t="n"/>
+      <c r="D40" s="130" t="n"/>
+      <c r="E40" s="130" t="n"/>
+      <c r="F40" s="130" t="n"/>
+      <c r="G40" s="130" t="n"/>
+      <c r="H40" s="130" t="n"/>
+      <c r="I40" s="130" t="n"/>
+      <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="127" t="inlineStr">
+      <c r="B41" s="131" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C41" s="128" t="n"/>
-      <c r="D41" s="128" t="n"/>
-      <c r="E41" s="128" t="n"/>
-      <c r="F41" s="128" t="n"/>
-      <c r="G41" s="128" t="n"/>
-      <c r="H41" s="128" t="n"/>
-      <c r="I41" s="128" t="n"/>
-      <c r="J41" s="128" t="n"/>
+      <c r="C41" s="132" t="n"/>
+      <c r="D41" s="132" t="n"/>
+      <c r="E41" s="132" t="n"/>
+      <c r="F41" s="132" t="n"/>
+      <c r="G41" s="132" t="n"/>
+      <c r="H41" s="132" t="n"/>
+      <c r="I41" s="132" t="n"/>
+      <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
     <row r="42" ht="24.6" customHeight="1" thickBot="1">
@@ -5535,8 +5332,8 @@
       <c r="E42" s="79" t="n"/>
       <c r="F42" s="79" t="n"/>
       <c r="G42" s="94" t="n"/>
-      <c r="H42" s="104" t="n"/>
-      <c r="I42" s="105" t="n"/>
+      <c r="H42" s="105" t="n"/>
+      <c r="I42" s="81" t="n"/>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
@@ -5548,7 +5345,7 @@
       <c r="E43" s="43" t="n"/>
       <c r="F43" s="43" t="n"/>
       <c r="G43" s="43" t="n"/>
-      <c r="H43" s="97" t="n"/>
+      <c r="H43" s="43" t="n"/>
       <c r="I43" s="43" t="n"/>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
@@ -5561,7 +5358,7 @@
       <c r="E44" s="43" t="n"/>
       <c r="F44" s="43" t="n"/>
       <c r="G44" s="43" t="n"/>
-      <c r="H44" s="97" t="n"/>
+      <c r="H44" s="43" t="n"/>
       <c r="I44" s="43" t="n"/>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
@@ -5574,8 +5371,8 @@
       <c r="E45" s="59" t="n"/>
       <c r="F45" s="59" t="n"/>
       <c r="G45" s="59" t="n"/>
-      <c r="H45" s="98" t="n"/>
-      <c r="I45" s="59" t="n"/>
+      <c r="H45" s="59" t="n"/>
+      <c r="I45" s="60" t="n"/>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
@@ -5587,8 +5384,8 @@
       <c r="E46" s="64" t="n"/>
       <c r="F46" s="64" t="n"/>
       <c r="G46" s="64" t="n"/>
-      <c r="H46" s="99" t="n"/>
-      <c r="I46" s="64" t="n"/>
+      <c r="H46" s="64" t="n"/>
+      <c r="I46" s="65" t="n"/>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
@@ -5600,8 +5397,8 @@
       <c r="E47" s="62" t="n"/>
       <c r="F47" s="62" t="n"/>
       <c r="G47" s="62" t="n"/>
-      <c r="H47" s="100" t="n"/>
-      <c r="I47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="63" t="n"/>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
@@ -5613,7 +5410,7 @@
       <c r="E48" s="43" t="n"/>
       <c r="F48" s="43" t="n"/>
       <c r="G48" s="43" t="n"/>
-      <c r="H48" s="97" t="n"/>
+      <c r="H48" s="43" t="n"/>
       <c r="I48" s="43" t="n"/>
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="43" t="n"/>
@@ -5626,17 +5423,18 @@
       <c r="E49" s="47" t="n"/>
       <c r="F49" s="47" t="n"/>
       <c r="G49" s="47" t="n"/>
-      <c r="H49" s="101" t="n"/>
+      <c r="H49" s="47" t="n"/>
       <c r="I49" s="47" t="n"/>
       <c r="J49" s="47" t="n"/>
       <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G38">
     <cfRule type="colorScale" priority="1351">

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -528,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -815,6 +815,7 @@
     <xf numFmtId="0" fontId="27" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1429,7 +1430,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46226.55952428059</v>
+        <v>46226.57685464746</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1491,8 +1492,9 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46226.55952428059</v>
-      </c>
+        <v>46226.57685464746</v>
+      </c>
+      <c r="J2" s="83" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="45" t="n"/>
@@ -1548,12 +1550,7 @@
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="55" t="inlineStr">
-        <is>
-          <t>Chris White, CFA
-Head of Research</t>
-        </is>
-      </c>
+      <c r="J6" s="112" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
@@ -1602,7 +1599,7 @@
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="112" t="inlineStr">
+      <c r="B8" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1628,7 +1625,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>0.656</v>
+        <v>0.638</v>
       </c>
       <c r="H8" s="107" t="n">
         <v>2258.51</v>
@@ -1643,7 +1640,7 @@
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="112" t="inlineStr">
+      <c r="B9" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1669,7 +1666,7 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.473</v>
+        <v>0.471</v>
       </c>
       <c r="H9" s="110" t="n">
         <v>7850.04</v>
@@ -1684,7 +1681,7 @@
     </row>
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="112" t="inlineStr">
+      <c r="B10" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1710,7 +1707,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.345</v>
+        <v>0.336</v>
       </c>
       <c r="H10" s="107" t="n">
         <v>38174.66</v>
@@ -1725,7 +1722,7 @@
     </row>
     <row r="11" ht="67" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="112" t="inlineStr">
+      <c r="B11" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1751,7 +1748,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.278</v>
+        <v>0.284</v>
       </c>
       <c r="H11" s="110" t="n">
         <v>10045.65</v>
@@ -1766,7 +1763,7 @@
     </row>
     <row r="12" ht="67" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="112" t="inlineStr">
+      <c r="B12" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1792,7 +1789,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.236</v>
+        <v>0.237</v>
       </c>
       <c r="H12" s="107" t="n">
         <v>2215.94</v>
@@ -1807,7 +1804,7 @@
     </row>
     <row r="13" ht="50" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="112" t="inlineStr">
+      <c r="B13" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -1833,7 +1830,7 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.105</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H13" s="110" t="n">
         <v>6226.62</v>
@@ -1846,62 +1843,62 @@
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="84" customHeight="1">
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="113" t="inlineStr">
+      <c r="B14" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>Mattr Corp.</t>
+          <t>Mullen Group Ltd.</t>
         </is>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F14" s="106" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>1.156</v>
+        <v>0.651</v>
       </c>
       <c r="H14" s="107" t="n">
-        <v>555.83</v>
+        <v>1565.38</v>
       </c>
       <c r="I14" s="108" t="inlineStr">
         <is>
-          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="50" customHeight="1">
+    <row r="15" ht="67" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="113" t="inlineStr">
+      <c r="B15" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>NFI</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd.</t>
+          <t>NFI Group Inc.</t>
         </is>
       </c>
       <c r="E15" s="109" t="inlineStr">
@@ -1911,38 +1908,38 @@
       </c>
       <c r="F15" s="109" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.578</v>
+        <v>0.536</v>
       </c>
       <c r="H15" s="110" t="n">
-        <v>1565.38</v>
+        <v>1892.54</v>
       </c>
       <c r="I15" s="111" t="inlineStr">
         <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="67" customHeight="1">
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="113" t="inlineStr">
+      <c r="B16" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>NFI</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>NFI Group Inc.</t>
+          <t>Russel Metals Inc.</t>
         </is>
       </c>
       <c r="E16" s="106" t="inlineStr">
@@ -1952,18 +1949,18 @@
       </c>
       <c r="F16" s="106" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.527</v>
+        <v>0.469</v>
       </c>
       <c r="H16" s="107" t="n">
-        <v>1892.54</v>
+        <v>2385.76</v>
       </c>
       <c r="I16" s="108" t="inlineStr">
         <is>
-          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
+          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
@@ -1971,183 +1968,183 @@
     </row>
     <row r="17" ht="50" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="113" t="inlineStr">
+      <c r="B17" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Russel Metals Inc.</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E17" s="109" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F17" s="109" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.468</v>
+        <v>0.355</v>
       </c>
       <c r="H17" s="110" t="n">
-        <v>2385.76</v>
+        <v>681.6799999999999</v>
       </c>
       <c r="I17" s="111" t="inlineStr">
         <is>
-          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="50" customHeight="1">
+    <row r="18" ht="84" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="113" t="inlineStr">
+      <c r="B18" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>Canadian Imperial Bank of Commerce</t>
         </is>
       </c>
       <c r="E18" s="106" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="106" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.374</v>
+        <v>0.327</v>
       </c>
       <c r="H18" s="107" t="n">
-        <v>681.6799999999999</v>
+        <v>101497.85</v>
       </c>
       <c r="I18" s="108" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="84" customHeight="1">
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="113" t="inlineStr">
+      <c r="B19" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce</t>
+          <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
       <c r="E19" s="109" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="109" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.342</v>
+        <v>0.32</v>
       </c>
       <c r="H19" s="110" t="n">
-        <v>101497.85</v>
+        <v>28518.97</v>
       </c>
       <c r="I19" s="111" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="50" customHeight="1">
+    <row r="20" ht="67" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="113" t="inlineStr">
+      <c r="B20" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation</t>
+          <t>Canadian Pacific Kansas City Limited</t>
         </is>
       </c>
       <c r="E20" s="106" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F20" s="106" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.316</v>
+        <v>0.315</v>
       </c>
       <c r="H20" s="107" t="n">
-        <v>28518.97</v>
+        <v>79823.21000000001</v>
       </c>
       <c r="I20" s="108" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="67" customHeight="1">
+    <row r="21" ht="50" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="113" t="inlineStr">
+      <c r="B21" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E21" s="109" t="inlineStr">
@@ -2157,18 +2154,18 @@
       </c>
       <c r="F21" s="109" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.298</v>
+        <v>0.223</v>
       </c>
       <c r="H21" s="110" t="n">
-        <v>79823.21000000001</v>
+        <v>576.85</v>
       </c>
       <c r="I21" s="111" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
@@ -2176,122 +2173,122 @@
     </row>
     <row r="22" ht="67" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="113" t="inlineStr">
+      <c r="B22" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>DBM</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Doman Building Materials Group Ltd.</t>
         </is>
       </c>
       <c r="E22" s="106" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="106" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.252</v>
+        <v>0.191</v>
       </c>
       <c r="H22" s="107" t="n">
-        <v>976.67</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="I22" s="108" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="50" customHeight="1">
+    <row r="23" ht="84" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="113" t="inlineStr">
+      <c r="B23" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>TOY</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>Spin Master Corp.</t>
         </is>
       </c>
       <c r="E23" s="109" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F23" s="109" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.229</v>
+        <v>0.181</v>
       </c>
       <c r="H23" s="110" t="n">
-        <v>576.85</v>
+        <v>1330.28</v>
       </c>
       <c r="I23" s="111" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="84" customHeight="1">
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="113" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B24" s="115" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>TOY</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Spin Master Corp.</t>
+          <t>ADF Group Inc.</t>
         </is>
       </c>
       <c r="E24" s="106" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="106" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.196</v>
+        <v>1.179</v>
       </c>
       <c r="H24" s="107" t="n">
-        <v>1330.28</v>
+        <v>284.57</v>
       </c>
       <c r="I24" s="108" t="inlineStr">
         <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -2299,19 +2296,19 @@
     </row>
     <row r="25" ht="67" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="113" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B25" s="115" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>DBM</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Doman Building Materials Group Ltd.</t>
+          <t>Canadian National Railway Company</t>
         </is>
       </c>
       <c r="E25" s="109" t="inlineStr">
@@ -2321,38 +2318,38 @@
       </c>
       <c r="F25" s="109" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.192</v>
+        <v>0.358</v>
       </c>
       <c r="H25" s="110" t="n">
-        <v>676.4400000000001</v>
+        <v>72839.50999999999</v>
       </c>
       <c r="I25" s="111" t="inlineStr">
         <is>
-          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="50" customHeight="1">
+    <row r="26" ht="67" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="113" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B26" s="115" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited</t>
+          <t>K-Bro Linen Inc.</t>
         </is>
       </c>
       <c r="E26" s="106" t="inlineStr">
@@ -2366,55 +2363,55 @@
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.178</v>
+        <v>0.357</v>
       </c>
       <c r="H26" s="107" t="n">
-        <v>927.72</v>
+        <v>390.27</v>
       </c>
       <c r="I26" s="108" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="50" customHeight="1">
+    <row r="27" ht="101" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="114" t="inlineStr">
+      <c r="B27" s="115" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>ADF Group Inc.</t>
+          <t>Sun Life Financial Inc.</t>
         </is>
       </c>
       <c r="E27" s="109" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F27" s="109" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>1.168</v>
+        <v>0.344</v>
       </c>
       <c r="H27" s="110" t="n">
-        <v>284.57</v>
+        <v>41467.31</v>
       </c>
       <c r="I27" s="111" t="inlineStr">
         <is>
-          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
@@ -2422,335 +2419,167 @@
     </row>
     <row r="28" ht="67" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="114" t="inlineStr">
+      <c r="B28" s="116" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>GWO</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>Great-West Lifeco Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="106" t="inlineStr">
+      <c r="C28" s="117" t="inlineStr">
+        <is>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="D28" s="118" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E28" s="119" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F28" s="106" t="inlineStr">
+      <c r="F28" s="119" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G28" s="89" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="H28" s="107" t="n">
-        <v>53011.04</v>
-      </c>
-      <c r="I28" s="108" t="inlineStr">
-        <is>
-          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
+      <c r="G28" s="120" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="H28" s="121" t="n">
+        <v>65572.44</v>
+      </c>
+      <c r="I28" s="122" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="67" customHeight="1">
+    <row r="29" ht="8" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="114" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>KBL</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F29" s="109" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G29" s="89" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="H29" s="110" t="n">
-        <v>390.27</v>
-      </c>
-      <c r="I29" s="111" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
-        </is>
-      </c>
+      <c r="B29" s="123" t="n"/>
+      <c r="C29" s="124" t="n"/>
+      <c r="D29" s="125" t="n"/>
+      <c r="E29" s="126" t="n"/>
+      <c r="F29" s="126" t="n"/>
+      <c r="G29" s="127" t="n"/>
+      <c r="H29" s="128" t="n"/>
+      <c r="I29" s="129" t="n"/>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="101" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="114" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="106" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F30" s="106" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G30" s="89" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H30" s="107" t="n">
-        <v>41467.31</v>
-      </c>
-      <c r="I30" s="108" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
-        </is>
-      </c>
+      <c r="B30" s="130" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C30" s="131" t="n"/>
+      <c r="D30" s="131" t="n"/>
+      <c r="E30" s="131" t="n"/>
+      <c r="F30" s="131" t="n"/>
+      <c r="G30" s="131" t="n"/>
+      <c r="H30" s="131" t="n"/>
+      <c r="I30" s="131" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="67" customHeight="1">
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="114" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>CNR</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company</t>
-        </is>
-      </c>
-      <c r="E31" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F31" s="109" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G31" s="89" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="H31" s="110" t="n">
-        <v>72839.50999999999</v>
-      </c>
-      <c r="I31" s="111" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
-        </is>
-      </c>
+      <c r="B31" s="132" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C31" s="133" t="n"/>
+      <c r="D31" s="133" t="n"/>
+      <c r="E31" s="133" t="n"/>
+      <c r="F31" s="133" t="n"/>
+      <c r="G31" s="133" t="n"/>
+      <c r="H31" s="133" t="n"/>
+      <c r="I31" s="133" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="67" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="114" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C32" s="38" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="D32" s="39" t="inlineStr">
-        <is>
-          <t>iA Financial Corporation Inc.</t>
-        </is>
-      </c>
-      <c r="E32" s="106" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F32" s="106" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G32" s="89" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H32" s="107" t="n">
-        <v>11282.66</v>
-      </c>
-      <c r="I32" s="108" t="inlineStr">
-        <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
-        </is>
-      </c>
+      <c r="B32" s="48" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="89" t="n"/>
+      <c r="H32" s="91" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="67" customHeight="1">
+    <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="114" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>MFC</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E33" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F33" s="109" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G33" s="89" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="H33" s="110" t="n">
-        <v>65572.44</v>
-      </c>
-      <c r="I33" s="111" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
-        </is>
-      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="89" t="n"/>
+      <c r="H33" s="93" t="n"/>
+      <c r="I33" s="54" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="67" customHeight="1">
+    <row r="34" ht="30.6" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C34" s="116" t="inlineStr">
-        <is>
-          <t>IFP</t>
-        </is>
-      </c>
-      <c r="D34" s="117" t="inlineStr">
-        <is>
-          <t>Interfor Corporation</t>
-        </is>
-      </c>
-      <c r="E34" s="118" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F34" s="118" t="inlineStr">
-        <is>
-          <t>Paper and Forest Products</t>
-        </is>
-      </c>
-      <c r="G34" s="119" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="H34" s="120" t="n">
-        <v>501.72</v>
-      </c>
-      <c r="I34" s="121" t="inlineStr">
-        <is>
-          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
-        </is>
-      </c>
+      <c r="B34" s="48" t="n"/>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="40" t="n"/>
+      <c r="F34" s="40" t="n"/>
+      <c r="G34" s="89" t="n"/>
+      <c r="H34" s="91" t="n"/>
+      <c r="I34" s="53" t="n"/>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="8" customHeight="1">
+    <row r="35" ht="30.6" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="122" t="n"/>
-      <c r="C35" s="123" t="n"/>
-      <c r="D35" s="124" t="n"/>
-      <c r="E35" s="125" t="n"/>
-      <c r="F35" s="125" t="n"/>
-      <c r="G35" s="126" t="n"/>
-      <c r="H35" s="127" t="n"/>
-      <c r="I35" s="128" t="n"/>
+      <c r="B35" s="49" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="89" t="n"/>
+      <c r="H35" s="93" t="n"/>
+      <c r="I35" s="54" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="40.8" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="129" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C36" s="130" t="n"/>
-      <c r="D36" s="130" t="n"/>
-      <c r="E36" s="130" t="n"/>
-      <c r="F36" s="130" t="n"/>
-      <c r="G36" s="130" t="n"/>
-      <c r="H36" s="130" t="n"/>
-      <c r="I36" s="130" t="n"/>
+      <c r="B36" s="48" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="89" t="n"/>
+      <c r="H36" s="91" t="n"/>
+      <c r="I36" s="53" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="28" customHeight="1">
+    <row r="37" ht="24" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="131" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C37" s="132" t="n"/>
-      <c r="D37" s="132" t="n"/>
-      <c r="E37" s="132" t="n"/>
-      <c r="F37" s="132" t="n"/>
-      <c r="G37" s="132" t="n"/>
-      <c r="H37" s="132" t="n"/>
-      <c r="I37" s="132" t="n"/>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="32" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="89" t="n"/>
+      <c r="H37" s="93" t="n"/>
+      <c r="I37" s="54" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
@@ -2913,12 +2742,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G34">
+  <conditionalFormatting sqref="G8:G28">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -3897,8 +3726,9 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46226.55952428059</v>
-      </c>
+        <v>46226.57685464746</v>
+      </c>
+      <c r="J2" s="83" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="44" t="n"/>
@@ -3954,12 +3784,7 @@
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="55" t="inlineStr">
-        <is>
-          <t>Chris White, CFA
-Head of Research</t>
-        </is>
-      </c>
+      <c r="J6" s="112" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
@@ -4008,7 +3833,7 @@
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="112" t="inlineStr">
+      <c r="B8" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4034,7 +3859,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.141</v>
+        <v>1.158</v>
       </c>
       <c r="H8" s="107" t="n">
         <v>12725.72</v>
@@ -4049,7 +3874,7 @@
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="112" t="inlineStr">
+      <c r="B9" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4075,7 +3900,7 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.785</v>
+        <v>0.773</v>
       </c>
       <c r="H9" s="110" t="n">
         <v>213908.98</v>
@@ -4090,7 +3915,7 @@
     </row>
     <row r="10" ht="84" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="112" t="inlineStr">
+      <c r="B10" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4116,7 +3941,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.335</v>
+        <v>0.326</v>
       </c>
       <c r="H10" s="107" t="n">
         <v>64533.41</v>
@@ -4131,7 +3956,7 @@
     </row>
     <row r="11" ht="67" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="112" t="inlineStr">
+      <c r="B11" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4157,7 +3982,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.33</v>
+        <v>0.322</v>
       </c>
       <c r="H11" s="110" t="n">
         <v>39380.19</v>
@@ -4172,7 +3997,7 @@
     </row>
     <row r="12" ht="33" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="112" t="inlineStr">
+      <c r="B12" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -4198,7 +4023,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.31</v>
+        <v>0.303</v>
       </c>
       <c r="H12" s="107" t="n">
         <v>62147.38</v>
@@ -4211,42 +4036,42 @@
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="50" customHeight="1">
+    <row r="13" ht="67" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="112" t="inlineStr">
+      <c r="B13" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>Ventas Inc.</t>
         </is>
       </c>
       <c r="E13" s="109" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F13" s="109" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.287</v>
+        <v>0.298</v>
       </c>
       <c r="H13" s="110" t="n">
-        <v>125211.85</v>
+        <v>41077.71</v>
       </c>
       <c r="I13" s="111" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>Ventas Inc is a leading S&amp;P 500 real estate investment trust enabling exceptional environments that benefit a large and growing aging population</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4254,81 +4079,81 @@
     </row>
     <row r="14" ht="67" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="112" t="inlineStr">
+      <c r="B14" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc.</t>
+          <t>United Rentals Inc.</t>
         </is>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F14" s="106" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.172</v>
+        <v>0.292</v>
       </c>
       <c r="H14" s="107" t="n">
-        <v>23624.19</v>
+        <v>66529.00999999999</v>
       </c>
       <c r="I14" s="108" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+          <t>United Rentals Inc through its subsidiaries operates as an equipment rental company in the United States Canada Europe Australia and New Zealand</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15" ht="50" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="112" t="inlineStr">
+      <c r="B15" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E15" s="109" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F15" s="109" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.165</v>
+        <v>0.28</v>
       </c>
       <c r="H15" s="110" t="n">
-        <v>834204.25</v>
+        <v>125211.85</v>
       </c>
       <c r="I15" s="111" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -4336,142 +4161,142 @@
     </row>
     <row r="16" ht="50" customHeight="1">
       <c r="A16" s="36" t="n"/>
-      <c r="B16" s="112" t="inlineStr">
+      <c r="B16" s="113" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>Everest Group Ltd.</t>
+          <t>Quest Diagnostics Incorporated</t>
         </is>
       </c>
       <c r="E16" s="106" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="106" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.149</v>
+        <v>0.274</v>
       </c>
       <c r="H16" s="107" t="n">
-        <v>13320.91</v>
+        <v>22520.63</v>
       </c>
       <c r="I16" s="108" t="inlineStr">
         <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+          <t>Quest Diagnostics Incorporated provides diagnostic testing and services in the United States</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="50" customHeight="1">
+    <row r="17" ht="67" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="113" t="inlineStr">
         <is>
-          <t>RPT</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Norfolk Southern Corporation</t>
         </is>
       </c>
       <c r="E17" s="109" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F17" s="109" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.882</v>
+        <v>0.244</v>
       </c>
       <c r="H17" s="110" t="n">
-        <v>77721.12</v>
+        <v>69486.00999999999</v>
       </c>
       <c r="I17" s="111" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Norfolk Southern Corporation together with its subsidiaries engages in the rail transportation of raw materials intermediate products and finished goods in the United States</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="84" customHeight="1">
+    <row r="18" ht="67" customHeight="1">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="113" t="inlineStr">
         <is>
-          <t>RPT</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Principal Financial Group Inc.</t>
         </is>
       </c>
       <c r="E18" s="106" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="106" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.752</v>
+        <v>0.164</v>
       </c>
       <c r="H18" s="107" t="n">
-        <v>77190.64999999999</v>
+        <v>23624.19</v>
       </c>
       <c r="I18" s="108" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="50" customHeight="1">
+    <row r="19" ht="33" customHeight="1">
       <c r="A19" s="28" t="n"/>
       <c r="B19" s="113" t="inlineStr">
         <is>
-          <t>RPT</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E19" s="109" t="inlineStr">
@@ -4481,18 +4306,18 @@
       </c>
       <c r="F19" s="109" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.458</v>
+        <v>0.161</v>
       </c>
       <c r="H19" s="110" t="n">
-        <v>44725.83</v>
+        <v>834204.25</v>
       </c>
       <c r="I19" s="111" t="inlineStr">
         <is>
-          <t>State Street Corporation provides various financial products and services to institutional investors</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
@@ -4502,202 +4327,202 @@
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="113" t="inlineStr">
         <is>
-          <t>RPT</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Services Inc.</t>
+          <t>Everest Group Ltd.</t>
         </is>
       </c>
       <c r="E20" s="106" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="106" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.407</v>
+        <v>0.145</v>
       </c>
       <c r="H20" s="107" t="n">
-        <v>26566.73</v>
+        <v>13320.91</v>
       </c>
       <c r="I20" s="108" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="50" customHeight="1">
+    <row r="21" ht="33" customHeight="1">
       <c r="A21" s="28" t="n"/>
       <c r="B21" s="113" t="inlineStr">
         <is>
-          <t>RPT</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Invesco Ltd.</t>
         </is>
       </c>
       <c r="E21" s="109" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="109" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.365</v>
+        <v>0.076</v>
       </c>
       <c r="H21" s="110" t="n">
-        <v>158667.48</v>
+        <v>12167.61</v>
       </c>
       <c r="I21" s="111" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>Invesco Ltd is a publicly owned investment manager</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="67" customHeight="1">
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="113" t="inlineStr">
+      <c r="B22" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E22" s="106" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="106" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.353</v>
+        <v>0.862</v>
       </c>
       <c r="H22" s="107" t="n">
-        <v>148209.56</v>
+        <v>77721.12</v>
       </c>
       <c r="I22" s="108" t="inlineStr">
         <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="33" customHeight="1">
+    <row r="23" ht="84" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="113" t="inlineStr">
+      <c r="B23" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="E23" s="109" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="109" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.322</v>
+        <v>0.733</v>
       </c>
       <c r="H23" s="110" t="n">
-        <v>16078.79</v>
+        <v>77190.64999999999</v>
       </c>
       <c r="I23" s="111" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="67" customHeight="1">
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="113" t="inlineStr">
+      <c r="B24" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="E24" s="106" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="106" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.29</v>
+        <v>0.463</v>
       </c>
       <c r="H24" s="107" t="n">
-        <v>14353.95</v>
+        <v>44725.83</v>
       </c>
       <c r="I24" s="108" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
@@ -4705,40 +4530,40 @@
     </row>
     <row r="25" ht="50" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="113" t="inlineStr">
+      <c r="B25" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E25" s="109" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="109" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.261</v>
+        <v>0.363</v>
       </c>
       <c r="H25" s="110" t="n">
-        <v>4309578.68</v>
+        <v>158667.48</v>
       </c>
       <c r="I25" s="111" t="inlineStr">
         <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -4746,81 +4571,81 @@
     </row>
     <row r="26" ht="67" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="113" t="inlineStr">
+      <c r="B26" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>Globe Life Inc.</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E26" s="106" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F26" s="106" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.23</v>
+        <v>0.353</v>
       </c>
       <c r="H26" s="107" t="n">
-        <v>12644.53</v>
+        <v>148209.56</v>
       </c>
       <c r="I26" s="108" t="inlineStr">
         <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="84" customHeight="1">
+    <row r="27" ht="33" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="113" t="inlineStr">
+      <c r="B27" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E27" s="109" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="109" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.191</v>
+        <v>0.314</v>
       </c>
       <c r="H27" s="110" t="n">
-        <v>388502.86</v>
+        <v>16078.79</v>
       </c>
       <c r="I27" s="111" t="inlineStr">
         <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
@@ -4828,101 +4653,101 @@
     </row>
     <row r="28" ht="67" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="113" t="inlineStr">
+      <c r="B28" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>Block Inc.</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E28" s="106" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F28" s="106" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.173</v>
+        <v>0.291</v>
       </c>
       <c r="H28" s="107" t="n">
-        <v>40474.89</v>
+        <v>14353.95</v>
       </c>
       <c r="I28" s="108" t="inlineStr">
         <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="67" customHeight="1">
+    <row r="29" ht="50" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="113" t="inlineStr">
+      <c r="B29" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E29" s="109" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F29" s="109" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.164</v>
+        <v>0.255</v>
       </c>
       <c r="H29" s="110" t="n">
-        <v>89144.46000000001</v>
+        <v>4309578.68</v>
       </c>
       <c r="I29" s="111" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="84" customHeight="1">
+    <row r="30" ht="67" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="113" t="inlineStr">
+      <c r="B30" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc.</t>
+          <t>Globe Life Inc.</t>
         </is>
       </c>
       <c r="E30" s="106" t="inlineStr">
@@ -4932,38 +4757,38 @@
       </c>
       <c r="F30" s="106" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.159</v>
+        <v>0.235</v>
       </c>
       <c r="H30" s="107" t="n">
-        <v>27585.86</v>
+        <v>12644.53</v>
       </c>
       <c r="I30" s="108" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="67" customHeight="1">
+    <row r="31" ht="84" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="113" t="inlineStr">
+      <c r="B31" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E31" s="109" t="inlineStr">
@@ -4977,14 +4802,14 @@
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.145</v>
+        <v>0.185</v>
       </c>
       <c r="H31" s="110" t="n">
-        <v>47955.66</v>
+        <v>388502.86</v>
       </c>
       <c r="I31" s="111" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
@@ -4992,7 +4817,7 @@
     </row>
     <row r="32" ht="67" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="113" t="inlineStr">
+      <c r="B32" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -5018,7 +4843,7 @@
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.132</v>
+        <v>0.118</v>
       </c>
       <c r="H32" s="107" t="n">
         <v>21453.67</v>
@@ -5033,7 +4858,7 @@
     </row>
     <row r="33" ht="67" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="113" t="inlineStr">
+      <c r="B33" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
@@ -5059,7 +4884,7 @@
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.112</v>
+        <v>0.105</v>
       </c>
       <c r="H33" s="110" t="n">
         <v>36717.82</v>
@@ -5072,62 +4897,62 @@
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="50" customHeight="1">
+    <row r="34" ht="84" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="113" t="inlineStr">
+      <c r="B34" s="114" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>BXP Inc.</t>
+          <t>Paychex Inc.</t>
         </is>
       </c>
       <c r="E34" s="106" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F34" s="106" t="inlineStr">
         <is>
-          <t>Office REITs</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.077</v>
+        <v>0.062</v>
       </c>
       <c r="H34" s="107" t="n">
-        <v>11826.25</v>
+        <v>36258.68</v>
       </c>
       <c r="I34" s="108" t="inlineStr">
         <is>
-          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="84" customHeight="1">
+    <row r="35" ht="50" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="113" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B35" s="115" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Paychex Inc.</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E35" s="109" t="inlineStr">
@@ -5137,18 +4962,18 @@
       </c>
       <c r="F35" s="109" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.076</v>
+        <v>0.412</v>
       </c>
       <c r="H35" s="110" t="n">
-        <v>36258.68</v>
+        <v>86617.14</v>
       </c>
       <c r="I35" s="111" t="inlineStr">
         <is>
-          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
+          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
       <c r="J35" s="54" t="n"/>
@@ -5156,171 +4981,115 @@
     </row>
     <row r="36" ht="50" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="114" t="inlineStr">
+      <c r="B36" s="116" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>CSX</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>CSX Corporation</t>
-        </is>
-      </c>
-      <c r="E36" s="106" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F36" s="106" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G36" s="89" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="H36" s="107" t="n">
-        <v>86617.14</v>
-      </c>
-      <c r="I36" s="108" t="inlineStr">
-        <is>
-          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+      <c r="C36" s="117" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="D36" s="118" t="inlineStr">
+        <is>
+          <t>MetLife Inc.</t>
+        </is>
+      </c>
+      <c r="E36" s="119" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F36" s="119" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G36" s="120" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="H36" s="121" t="n">
+        <v>55851.6</v>
+      </c>
+      <c r="I36" s="122" t="inlineStr">
+        <is>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="50" customHeight="1">
+    <row r="37" ht="8" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="114" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>MetLife Inc.</t>
-        </is>
-      </c>
-      <c r="E37" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F37" s="109" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G37" s="89" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="H37" s="110" t="n">
-        <v>55851.6</v>
-      </c>
-      <c r="I37" s="111" t="inlineStr">
-        <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
-        </is>
-      </c>
+      <c r="B37" s="123" t="n"/>
+      <c r="C37" s="124" t="n"/>
+      <c r="D37" s="125" t="n"/>
+      <c r="E37" s="126" t="n"/>
+      <c r="F37" s="126" t="n"/>
+      <c r="G37" s="127" t="n"/>
+      <c r="H37" s="128" t="n"/>
+      <c r="I37" s="129" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="50" customHeight="1">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C38" s="116" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D38" s="117" t="inlineStr">
-        <is>
-          <t>Visa Inc.</t>
-        </is>
-      </c>
-      <c r="E38" s="118" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F38" s="118" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="H38" s="120" t="n">
-        <v>612046.08</v>
-      </c>
-      <c r="I38" s="121" t="inlineStr">
-        <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
-        </is>
-      </c>
+      <c r="B38" s="130" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C38" s="131" t="n"/>
+      <c r="D38" s="131" t="n"/>
+      <c r="E38" s="131" t="n"/>
+      <c r="F38" s="131" t="n"/>
+      <c r="G38" s="131" t="n"/>
+      <c r="H38" s="131" t="n"/>
+      <c r="I38" s="131" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="8" customHeight="1">
+    <row r="39" ht="28" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="122" t="n"/>
-      <c r="C39" s="123" t="n"/>
-      <c r="D39" s="124" t="n"/>
-      <c r="E39" s="125" t="n"/>
-      <c r="F39" s="125" t="n"/>
-      <c r="G39" s="126" t="n"/>
-      <c r="H39" s="127" t="n"/>
-      <c r="I39" s="128" t="n"/>
+      <c r="B39" s="132" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C39" s="133" t="n"/>
+      <c r="D39" s="133" t="n"/>
+      <c r="E39" s="133" t="n"/>
+      <c r="F39" s="133" t="n"/>
+      <c r="G39" s="133" t="n"/>
+      <c r="H39" s="133" t="n"/>
+      <c r="I39" s="133" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="34" customHeight="1">
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="129" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C40" s="130" t="n"/>
-      <c r="D40" s="130" t="n"/>
-      <c r="E40" s="130" t="n"/>
-      <c r="F40" s="130" t="n"/>
-      <c r="G40" s="130" t="n"/>
-      <c r="H40" s="130" t="n"/>
-      <c r="I40" s="130" t="n"/>
+      <c r="B40" s="48" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="89" t="n"/>
+      <c r="H40" s="91" t="n"/>
+      <c r="I40" s="53" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="28" customHeight="1">
+    <row r="41" ht="30.6" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="131" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C41" s="132" t="n"/>
-      <c r="D41" s="132" t="n"/>
-      <c r="E41" s="132" t="n"/>
-      <c r="F41" s="132" t="n"/>
-      <c r="G41" s="132" t="n"/>
-      <c r="H41" s="132" t="n"/>
-      <c r="I41" s="132" t="n"/>
+      <c r="B41" s="49" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="89" t="n"/>
+      <c r="H41" s="93" t="n"/>
+      <c r="I41" s="54" t="n"/>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
@@ -5432,11 +5201,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B38:I38"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B40:I40"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G38">
+  <conditionalFormatting sqref="G8:G36">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="37">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -225,9 +225,43 @@
       <sz val="9.5"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="7"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2563A8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF6B7A8D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF166534"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF4B5563"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -528,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -816,34 +850,73 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -867,29 +940,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,172 +961,34 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <oneCellAnchor>
     <from>
       <col>8</col>
       <colOff>2268855</colOff>
       <row>0</row>
       <rowOff>76143</rowOff>
     </from>
-    <to>
-      <col>9</col>
-      <colOff>59055</colOff>
-      <row>1</row>
-      <rowOff>282839</rowOff>
-    </to>
+    <ext cx="1666875" cy="352425"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Picture 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9584055" y="76143"/>
-          <a:ext cx="1624965" cy="279086"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
     </pic>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>6</col>
-      <colOff>676230</colOff>
-      <row>4</row>
-      <rowOff>53556</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>880082</colOff>
-      <row>5</row>
-      <rowOff>244251</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Picture 11"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="6129293" y="958431"/>
-          <a:ext cx="203852" cy="260466"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>907842</colOff>
-      <row>4</row>
-      <rowOff>69534</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>16690</colOff>
-      <row>5</row>
-      <rowOff>190501</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Picture 13"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3824873" y="974409"/>
-          <a:ext cx="196603" cy="198358"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>1131570</colOff>
-      <row>4</row>
-      <rowOff>53030</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>1353820</colOff>
-      <row>5</row>
-      <rowOff>224912</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Picture 18"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5163820" y="961080"/>
-          <a:ext cx="212725" cy="248082"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1325,172 +1245,34 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <oneCellAnchor>
     <from>
       <col>8</col>
       <colOff>2268855</colOff>
       <row>0</row>
       <rowOff>76143</rowOff>
     </from>
-    <to>
-      <col>9</col>
-      <colOff>59055</colOff>
-      <row>1</row>
-      <rowOff>282839</rowOff>
-    </to>
+    <ext cx="1666875" cy="352425"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Picture 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9580245" y="76143"/>
-          <a:ext cx="1628775" cy="286706"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
     </pic>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>6</col>
-      <colOff>676230</colOff>
-      <row>4</row>
-      <rowOff>53556</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>880082</colOff>
-      <row>5</row>
-      <rowOff>244251</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Picture 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="6132150" y="962241"/>
-          <a:ext cx="205757" cy="266895"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>4</col>
-      <colOff>907842</colOff>
-      <row>4</row>
-      <rowOff>69534</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>16690</colOff>
-      <row>5</row>
-      <rowOff>190501</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Picture 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3830112" y="972504"/>
-          <a:ext cx="209938" cy="199072"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>1131570</colOff>
-      <row>4</row>
-      <rowOff>53030</rowOff>
-    </from>
-    <to>
-      <col>5</col>
-      <colOff>1353820</colOff>
-      <row>5</row>
-      <rowOff>224912</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Picture 11"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5149215" y="961715"/>
-          <a:ext cx="220345" cy="244272"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2289,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46227.52567949516</v>
+        <v>46227.60782800688</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2351,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46227.52567949516</v>
+        <v>46227.60782800688</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2413,42 +2195,42 @@
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="113" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="113" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="114" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="114" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="114" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="113" t="inlineStr">
         <is>
           <t>6-Mo Return</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="113" t="inlineStr">
         <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="114" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
@@ -2456,40 +2238,40 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="50" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="113" t="inlineStr">
+      <c r="B8" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="115" t="inlineStr">
         <is>
           <t>SOBO</t>
         </is>
       </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="D8" s="116" t="inlineStr">
         <is>
           <t>South Bow Corporation</t>
         </is>
       </c>
-      <c r="E8" s="106" t="inlineStr">
+      <c r="E8" s="117" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F8" s="106" t="inlineStr">
+      <c r="F8" s="117" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G8" s="89" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="H8" s="107" t="n">
+      <c r="G8" s="118" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="H8" s="119" t="n">
         <v>7850.04</v>
       </c>
-      <c r="I8" s="108" t="inlineStr">
+      <c r="I8" s="120" t="inlineStr">
         <is>
           <t>South Bow Corporation operates as an energy infrastructure company</t>
         </is>
@@ -2497,40 +2279,40 @@
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="67" customHeight="1">
+    <row r="9" ht="88" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="113" t="inlineStr">
+      <c r="B9" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="121" t="inlineStr">
         <is>
           <t>BDGI</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="122" t="inlineStr">
         <is>
           <t>Badger Infrastructure Solutions Ltd.</t>
         </is>
       </c>
-      <c r="E9" s="109" t="inlineStr">
+      <c r="E9" s="123" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F9" s="109" t="inlineStr">
+      <c r="F9" s="123" t="inlineStr">
         <is>
           <t>Construction and Engineering</t>
         </is>
       </c>
-      <c r="G9" s="89" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="H9" s="110" t="n">
+      <c r="G9" s="118" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H9" s="124" t="n">
         <v>2215.94</v>
       </c>
-      <c r="I9" s="111" t="inlineStr">
+      <c r="I9" s="125" t="inlineStr">
         <is>
           <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
@@ -2538,40 +2320,40 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="50" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="113" t="inlineStr">
+      <c r="B10" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="115" t="inlineStr">
         <is>
           <t>DFY</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="116" t="inlineStr">
         <is>
           <t>Definity Financial Corporation</t>
         </is>
       </c>
-      <c r="E10" s="106" t="inlineStr">
+      <c r="E10" s="117" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F10" s="106" t="inlineStr">
+      <c r="F10" s="117" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G10" s="89" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="H10" s="107" t="n">
+      <c r="G10" s="118" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="H10" s="119" t="n">
         <v>6226.62</v>
       </c>
-      <c r="I10" s="108" t="inlineStr">
+      <c r="I10" s="120" t="inlineStr">
         <is>
           <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
         </is>
@@ -2579,40 +2361,40 @@
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="50" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="114" t="inlineStr">
+      <c r="B11" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="121" t="inlineStr">
         <is>
           <t>MTL</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="122" t="inlineStr">
         <is>
           <t>Mullen Group Ltd.</t>
         </is>
       </c>
-      <c r="E11" s="109" t="inlineStr">
+      <c r="E11" s="123" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F11" s="109" t="inlineStr">
+      <c r="F11" s="123" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
-      <c r="G11" s="89" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="H11" s="110" t="n">
+      <c r="G11" s="118" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H11" s="124" t="n">
         <v>1565.38</v>
       </c>
-      <c r="I11" s="111" t="inlineStr">
+      <c r="I11" s="125" t="inlineStr">
         <is>
           <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
@@ -2620,40 +2402,40 @@
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="67" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="114" t="inlineStr">
+      <c r="B12" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="115" t="inlineStr">
         <is>
           <t>NFI</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D12" s="116" t="inlineStr">
         <is>
           <t>NFI Group Inc.</t>
         </is>
       </c>
-      <c r="E12" s="106" t="inlineStr">
+      <c r="E12" s="117" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F12" s="106" t="inlineStr">
+      <c r="F12" s="117" t="inlineStr">
         <is>
           <t>Machinery</t>
         </is>
       </c>
-      <c r="G12" s="89" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="H12" s="107" t="n">
+      <c r="G12" s="118" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="H12" s="119" t="n">
         <v>1892.54</v>
       </c>
-      <c r="I12" s="108" t="inlineStr">
+      <c r="I12" s="120" t="inlineStr">
         <is>
           <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
         </is>
@@ -2661,81 +2443,81 @@
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="50" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="114" t="inlineStr">
+      <c r="B13" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>Russel Metals Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F13" s="109" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G13" s="89" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="H13" s="110" t="n">
-        <v>2385.76</v>
-      </c>
-      <c r="I13" s="111" t="inlineStr">
-        <is>
-          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
+      <c r="C13" s="121" t="inlineStr">
+        <is>
+          <t>POW</t>
+        </is>
+      </c>
+      <c r="D13" s="122" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F13" s="123" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G13" s="118" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="H13" s="124" t="n">
+        <v>38174.66</v>
+      </c>
+      <c r="I13" s="125" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="50" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="114" t="inlineStr">
+      <c r="B14" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="115" t="inlineStr">
         <is>
           <t>ARG</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr">
+      <c r="D14" s="116" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
-      <c r="E14" s="106" t="inlineStr">
+      <c r="E14" s="117" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F14" s="106" t="inlineStr">
+      <c r="F14" s="117" t="inlineStr">
         <is>
           <t>Metals and Mining</t>
         </is>
       </c>
-      <c r="G14" s="89" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="H14" s="107" t="n">
+      <c r="G14" s="118" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H14" s="119" t="n">
         <v>681.6799999999999</v>
       </c>
-      <c r="I14" s="108" t="inlineStr">
+      <c r="I14" s="120" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
@@ -2743,583 +2525,443 @@
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="50" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="114" t="inlineStr">
+      <c r="B15" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>POW</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada</t>
-        </is>
-      </c>
-      <c r="E15" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F15" s="109" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G15" s="89" t="n">
+      <c r="C15" s="121" t="inlineStr">
+        <is>
+          <t>PPL</t>
+        </is>
+      </c>
+      <c r="D15" s="122" t="inlineStr">
+        <is>
+          <t>Pembina Pipeline Corporation</t>
+        </is>
+      </c>
+      <c r="E15" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F15" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G15" s="118" t="n">
         <v>0.331</v>
       </c>
-      <c r="H15" s="110" t="n">
-        <v>38174.66</v>
-      </c>
-      <c r="I15" s="111" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+      <c r="H15" s="124" t="n">
+        <v>28518.97</v>
+      </c>
+      <c r="I15" s="125" t="inlineStr">
+        <is>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="50" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="114" t="inlineStr">
+      <c r="B16" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>PPL</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>Pembina Pipeline Corporation</t>
-        </is>
-      </c>
-      <c r="E16" s="106" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F16" s="106" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G16" s="89" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="H16" s="107" t="n">
-        <v>28518.97</v>
-      </c>
-      <c r="I16" s="108" t="inlineStr">
-        <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+      <c r="C16" s="115" t="inlineStr">
+        <is>
+          <t>CU</t>
+        </is>
+      </c>
+      <c r="D16" s="116" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited</t>
+        </is>
+      </c>
+      <c r="E16" s="117" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F16" s="117" t="inlineStr">
+        <is>
+          <t>Multi-Utilities</t>
+        </is>
+      </c>
+      <c r="G16" s="118" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H16" s="119" t="n">
+        <v>10045.65</v>
+      </c>
+      <c r="I16" s="120" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="67" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="114" t="inlineStr">
+      <c r="B17" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited</t>
-        </is>
-      </c>
-      <c r="E17" s="109" t="inlineStr">
+      <c r="C17" s="121" t="inlineStr">
+        <is>
+          <t>DXT</t>
+        </is>
+      </c>
+      <c r="D17" s="122" t="inlineStr">
+        <is>
+          <t>Dexterra Group Inc.</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F17" s="109" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G17" s="89" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="H17" s="110" t="n">
-        <v>79823.21000000001</v>
-      </c>
-      <c r="I17" s="111" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+      <c r="F17" s="123" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G17" s="118" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="H17" s="124" t="n">
+        <v>576.85</v>
+      </c>
+      <c r="I17" s="125" t="inlineStr">
+        <is>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="67" customHeight="1">
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="114" t="inlineStr">
+      <c r="B18" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>CU</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited</t>
-        </is>
-      </c>
-      <c r="E18" s="106" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F18" s="106" t="inlineStr">
-        <is>
-          <t>Multi-Utilities</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H18" s="107" t="n">
-        <v>10045.65</v>
-      </c>
-      <c r="I18" s="108" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+      <c r="C18" s="115" t="inlineStr">
+        <is>
+          <t>TOY</t>
+        </is>
+      </c>
+      <c r="D18" s="116" t="inlineStr">
+        <is>
+          <t>Spin Master Corp.</t>
+        </is>
+      </c>
+      <c r="E18" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F18" s="117" t="inlineStr">
+        <is>
+          <t>Leisure Products</t>
+        </is>
+      </c>
+      <c r="G18" s="118" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H18" s="119" t="n">
+        <v>1330.28</v>
+      </c>
+      <c r="I18" s="120" t="inlineStr">
+        <is>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="50" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>DXT</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>Dexterra Group Inc.</t>
-        </is>
-      </c>
-      <c r="E19" s="109" t="inlineStr">
+      <c r="B19" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C19" s="121" t="inlineStr">
+        <is>
+          <t>KBL</t>
+        </is>
+      </c>
+      <c r="D19" s="122" t="inlineStr">
+        <is>
+          <t>K-Bro Linen Inc.</t>
+        </is>
+      </c>
+      <c r="E19" s="123" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F19" s="109" t="inlineStr">
+      <c r="F19" s="123" t="inlineStr">
         <is>
           <t>Commercial Services and Supplies</t>
         </is>
       </c>
-      <c r="G19" s="89" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="H19" s="110" t="n">
-        <v>576.85</v>
-      </c>
-      <c r="I19" s="111" t="inlineStr">
-        <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+      <c r="G19" s="118" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="H19" s="124" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="I19" s="125" t="inlineStr">
+        <is>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="67" customHeight="1">
+    <row r="20" ht="124" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>DBM</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Doman Building Materials Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E20" s="106" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F20" s="106" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="H20" s="107" t="n">
-        <v>676.4400000000001</v>
-      </c>
-      <c r="I20" s="108" t="inlineStr">
-        <is>
-          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
+      <c r="B20" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C20" s="115" t="inlineStr">
+        <is>
+          <t>SLF</t>
+        </is>
+      </c>
+      <c r="D20" s="116" t="inlineStr">
+        <is>
+          <t>Sun Life Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E20" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F20" s="117" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G20" s="118" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="H20" s="119" t="n">
+        <v>41467.31</v>
+      </c>
+      <c r="I20" s="120" t="inlineStr">
+        <is>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="84" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>TOY</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Spin Master Corp.</t>
-        </is>
-      </c>
-      <c r="E21" s="109" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F21" s="109" t="inlineStr">
-        <is>
-          <t>Leisure Products</t>
-        </is>
-      </c>
-      <c r="G21" s="89" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="H21" s="110" t="n">
-        <v>1330.28</v>
-      </c>
-      <c r="I21" s="111" t="inlineStr">
-        <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+      <c r="B21" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C21" s="121" t="inlineStr">
+        <is>
+          <t>CNR</t>
+        </is>
+      </c>
+      <c r="D21" s="122" t="inlineStr">
+        <is>
+          <t>Canadian National Railway Company</t>
+        </is>
+      </c>
+      <c r="E21" s="123" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F21" s="123" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G21" s="118" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H21" s="124" t="n">
+        <v>72839.50999999999</v>
+      </c>
+      <c r="I21" s="125" t="inlineStr">
+        <is>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="50" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="115" t="inlineStr">
+      <c r="B22" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>EXE</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>Extendicare Inc.</t>
-        </is>
-      </c>
-      <c r="E22" s="106" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F22" s="106" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="H22" s="107" t="n">
-        <v>2258.51</v>
-      </c>
-      <c r="I22" s="108" t="inlineStr">
-        <is>
-          <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
+      <c r="C22" s="130" t="inlineStr">
+        <is>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="D22" s="131" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E22" s="132" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F22" s="132" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G22" s="133" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="H22" s="134" t="n">
+        <v>65572.44</v>
+      </c>
+      <c r="I22" s="135" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="67" customHeight="1">
+    <row r="23" ht="8" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>KBL</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc.</t>
-        </is>
-      </c>
-      <c r="E23" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F23" s="109" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H23" s="110" t="n">
-        <v>390.27</v>
-      </c>
-      <c r="I23" s="111" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
-        </is>
-      </c>
+      <c r="B23" s="136" t="n"/>
+      <c r="C23" s="137" t="n"/>
+      <c r="D23" s="138" t="n"/>
+      <c r="E23" s="139" t="n"/>
+      <c r="F23" s="139" t="n"/>
+      <c r="G23" s="140" t="n"/>
+      <c r="H23" s="141" t="n"/>
+      <c r="I23" s="142" t="n"/>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="67" customHeight="1">
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>CNR</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company</t>
-        </is>
-      </c>
-      <c r="E24" s="106" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F24" s="106" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G24" s="89" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="H24" s="107" t="n">
-        <v>72839.50999999999</v>
-      </c>
-      <c r="I24" s="108" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
-        </is>
-      </c>
+      <c r="B24" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C24" s="144" t="n"/>
+      <c r="D24" s="144" t="n"/>
+      <c r="E24" s="144" t="n"/>
+      <c r="F24" s="144" t="n"/>
+      <c r="G24" s="144" t="n"/>
+      <c r="H24" s="144" t="n"/>
+      <c r="I24" s="144" t="n"/>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="101" customHeight="1">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E25" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F25" s="109" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G25" s="89" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="H25" s="110" t="n">
-        <v>41467.31</v>
-      </c>
-      <c r="I25" s="111" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
-        </is>
-      </c>
+      <c r="B25" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C25" s="146" t="n"/>
+      <c r="D25" s="146" t="n"/>
+      <c r="E25" s="146" t="n"/>
+      <c r="F25" s="146" t="n"/>
+      <c r="G25" s="146" t="n"/>
+      <c r="H25" s="146" t="n"/>
+      <c r="I25" s="146" t="n"/>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="84" customHeight="1">
+    <row r="26" ht="20.4" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Imperial Bank of Commerce</t>
-        </is>
-      </c>
-      <c r="E26" s="106" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F26" s="106" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G26" s="89" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="H26" s="107" t="n">
-        <v>101497.85</v>
-      </c>
-      <c r="I26" s="108" t="inlineStr">
-        <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
-        </is>
-      </c>
+      <c r="B26" s="48" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="40" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="89" t="n"/>
+      <c r="H26" s="91" t="n"/>
+      <c r="I26" s="53" t="n"/>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="67" customHeight="1">
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="116" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C27" s="117" t="inlineStr">
-        <is>
-          <t>MFC</t>
-        </is>
-      </c>
-      <c r="D27" s="118" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E27" s="119" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F27" s="119" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G27" s="120" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="H27" s="121" t="n">
-        <v>65572.44</v>
-      </c>
-      <c r="I27" s="122" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
-        </is>
-      </c>
+      <c r="B27" s="48" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="40" t="n"/>
+      <c r="F27" s="40" t="n"/>
+      <c r="G27" s="89" t="n"/>
+      <c r="H27" s="91" t="n"/>
+      <c r="I27" s="53" t="n"/>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="8" customHeight="1">
+    <row r="28" ht="20.4" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="123" t="n"/>
-      <c r="C28" s="124" t="n"/>
-      <c r="D28" s="125" t="n"/>
-      <c r="E28" s="126" t="n"/>
-      <c r="F28" s="126" t="n"/>
-      <c r="G28" s="127" t="n"/>
-      <c r="H28" s="128" t="n"/>
-      <c r="I28" s="129" t="n"/>
+      <c r="B28" s="49" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="89" t="n"/>
+      <c r="H28" s="93" t="n"/>
+      <c r="I28" s="54" t="n"/>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="24" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="130" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C29" s="131" t="n"/>
-      <c r="D29" s="131" t="n"/>
-      <c r="E29" s="131" t="n"/>
-      <c r="F29" s="131" t="n"/>
-      <c r="G29" s="131" t="n"/>
-      <c r="H29" s="131" t="n"/>
-      <c r="I29" s="131" t="n"/>
+      <c r="B29" s="48" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="40" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="89" t="n"/>
+      <c r="H29" s="91" t="n"/>
+      <c r="I29" s="53" t="n"/>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="28" customHeight="1">
+    <row r="30" ht="30.6" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="132" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C30" s="133" t="n"/>
-      <c r="D30" s="133" t="n"/>
-      <c r="E30" s="133" t="n"/>
-      <c r="F30" s="133" t="n"/>
-      <c r="G30" s="133" t="n"/>
-      <c r="H30" s="133" t="n"/>
-      <c r="I30" s="133" t="n"/>
+      <c r="B30" s="48" t="n"/>
+      <c r="C30" s="38" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
+      <c r="G30" s="89" t="n"/>
+      <c r="H30" s="91" t="n"/>
+      <c r="I30" s="53" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
@@ -3573,12 +3215,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B24:I24"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G27">
+  <conditionalFormatting sqref="G8:G22">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4559,7 +4201,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46227.52567949516</v>
+        <v>46227.60782800688</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4621,42 +4263,42 @@
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="113" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="113" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="114" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="114" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="114" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="G7" s="113" t="inlineStr">
         <is>
           <t>6-Mo Return</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="113" t="inlineStr">
         <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="114" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
@@ -4664,40 +4306,40 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="84" customHeight="1">
+    <row r="8" ht="88" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="113" t="inlineStr">
+      <c r="B8" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="115" t="inlineStr">
         <is>
           <t>HWM</t>
         </is>
       </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="D8" s="116" t="inlineStr">
         <is>
           <t>Howmet Aerospace Inc.</t>
         </is>
       </c>
-      <c r="E8" s="106" t="inlineStr">
+      <c r="E8" s="117" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F8" s="106" t="inlineStr">
+      <c r="F8" s="117" t="inlineStr">
         <is>
           <t>Aerospace and Defense</t>
         </is>
       </c>
-      <c r="G8" s="89" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="H8" s="107" t="n">
+      <c r="G8" s="118" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="H8" s="119" t="n">
         <v>100601.02</v>
       </c>
-      <c r="I8" s="108" t="inlineStr">
+      <c r="I8" s="120" t="inlineStr">
         <is>
           <t>Howmet Aerospace Inc provides advanced engineered solutions for the aerospace and transportation industries in the United States Japan France Germany the United Kingdom Mexico Italy Canada Poland China and internationally</t>
         </is>
@@ -4705,40 +4347,40 @@
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="67" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="113" t="inlineStr">
+      <c r="B9" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="121" t="inlineStr">
         <is>
           <t>VTR</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="122" t="inlineStr">
         <is>
           <t>Ventas Inc.</t>
         </is>
       </c>
-      <c r="E9" s="109" t="inlineStr">
+      <c r="E9" s="123" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="F9" s="109" t="inlineStr">
+      <c r="F9" s="123" t="inlineStr">
         <is>
           <t>Health Care REITs</t>
         </is>
       </c>
-      <c r="G9" s="89" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="H9" s="110" t="n">
+      <c r="G9" s="118" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H9" s="124" t="n">
         <v>41077.71</v>
       </c>
-      <c r="I9" s="111" t="inlineStr">
+      <c r="I9" s="125" t="inlineStr">
         <is>
           <t>Ventas Inc is a leading S&amp;P 500 real estate investment trust enabling exceptional environments that benefit a large and growing aging population</t>
         </is>
@@ -4746,40 +4388,40 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="67" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="113" t="inlineStr">
+      <c r="B10" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="115" t="inlineStr">
         <is>
           <t>WAB</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="116" t="inlineStr">
         <is>
           <t>Westinghouse Air Brake Technologies Corporation</t>
         </is>
       </c>
-      <c r="E10" s="106" t="inlineStr">
+      <c r="E10" s="117" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F10" s="106" t="inlineStr">
+      <c r="F10" s="117" t="inlineStr">
         <is>
           <t>Machinery</t>
         </is>
       </c>
-      <c r="G10" s="89" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="H10" s="107" t="n">
+      <c r="G10" s="118" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="H10" s="119" t="n">
         <v>43435.03</v>
       </c>
-      <c r="I10" s="108" t="inlineStr">
+      <c r="I10" s="120" t="inlineStr">
         <is>
           <t>Westinghouse Air Brake Technologies Corporation provides locomotives equipment systems and services for the freight rail and passenger transit industries worldwide</t>
         </is>
@@ -4787,737 +4429,737 @@
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="67" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="113" t="inlineStr">
+      <c r="B11" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>NSC</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>Norfolk Southern Corporation</t>
-        </is>
-      </c>
-      <c r="E11" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F11" s="109" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G11" s="89" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H11" s="110" t="n">
-        <v>69486.00999999999</v>
-      </c>
-      <c r="I11" s="111" t="inlineStr">
-        <is>
-          <t>Norfolk Southern Corporation together with its subsidiaries engages in the rail transportation of raw materials intermediate products and finished goods in the United States</t>
+      <c r="C11" s="121" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="D11" s="122" t="inlineStr">
+        <is>
+          <t>Quest Diagnostics Incorporated</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F11" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G11" s="118" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H11" s="124" t="n">
+        <v>22520.63</v>
+      </c>
+      <c r="I11" s="125" t="inlineStr">
+        <is>
+          <t>Quest Diagnostics Incorporated provides diagnostic testing and services in the United States</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="33" customHeight="1">
+    <row r="12" ht="106" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="113" t="inlineStr">
+      <c r="B12" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase &amp; Co.</t>
-        </is>
-      </c>
-      <c r="E12" s="106" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F12" s="106" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G12" s="89" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="H12" s="107" t="n">
-        <v>834204.25</v>
-      </c>
-      <c r="I12" s="108" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase &amp; Co</t>
+      <c r="C12" s="115" t="inlineStr">
+        <is>
+          <t>FRT</t>
+        </is>
+      </c>
+      <c r="D12" s="116" t="inlineStr">
+        <is>
+          <t>Federal Realty Investment Trust</t>
+        </is>
+      </c>
+      <c r="E12" s="117" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F12" s="117" t="inlineStr">
+        <is>
+          <t>Retail REITs</t>
+        </is>
+      </c>
+      <c r="G12" s="118" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="H12" s="119" t="n">
+        <v>10799.18</v>
+      </c>
+      <c r="I12" s="120" t="inlineStr">
+        <is>
+          <t>Federal Realty Investment Trust is a recognized leader in the ownership operation and redevelopment of high-quality retail-based properties located primarily in major coastal markets and select underserved regions with strong economic and demographic fundamentals</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="67" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="113" t="inlineStr">
+      <c r="B13" s="126" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>INCY</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>Incyte Corporation</t>
-        </is>
-      </c>
-      <c r="E13" s="109" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F13" s="109" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="G13" s="89" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="H13" s="110" t="n">
-        <v>21073.82</v>
-      </c>
-      <c r="I13" s="111" t="inlineStr">
-        <is>
-          <t>Incyte Corporation a biopharmaceutical company engages in the discovery development and commercialization of therapeutics in the United States Europe Canada and Japan</t>
+      <c r="C13" s="121" t="inlineStr">
+        <is>
+          <t>NSC</t>
+        </is>
+      </c>
+      <c r="D13" s="122" t="inlineStr">
+        <is>
+          <t>Norfolk Southern Corporation</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F13" s="123" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G13" s="118" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="H13" s="124" t="n">
+        <v>69486.00999999999</v>
+      </c>
+      <c r="I13" s="125" t="inlineStr">
+        <is>
+          <t>Norfolk Southern Corporation together with its subsidiaries engages in the rail transportation of raw materials intermediate products and finished goods in the United States</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="50" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>DVA</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>DaVita Inc.</t>
-        </is>
-      </c>
-      <c r="E14" s="106" t="inlineStr">
+      <c r="B14" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C14" s="115" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="D14" s="116" t="inlineStr">
+        <is>
+          <t>AbbVie Inc.</t>
+        </is>
+      </c>
+      <c r="E14" s="117" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-      <c r="F14" s="106" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G14" s="89" t="n">
-        <v>1.179</v>
-      </c>
-      <c r="H14" s="107" t="n">
-        <v>12725.72</v>
-      </c>
-      <c r="I14" s="108" t="inlineStr">
-        <is>
-          <t>DaVita Inc provides kidney dialysis services for patients suffering from chronic kidney failure in the United States</t>
+      <c r="F14" s="117" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G14" s="118" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="H14" s="119" t="n">
+        <v>398482.45</v>
+      </c>
+      <c r="I14" s="120" t="inlineStr">
+        <is>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="50" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum Corporation</t>
-        </is>
-      </c>
-      <c r="E15" s="109" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F15" s="109" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G15" s="89" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="H15" s="110" t="n">
-        <v>77721.12</v>
-      </c>
-      <c r="I15" s="111" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+      <c r="B15" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C15" s="121" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="D15" s="122" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="E15" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F15" s="123" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G15" s="118" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="H15" s="124" t="n">
+        <v>834204.25</v>
+      </c>
+      <c r="I15" s="125" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="84" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="36" t="n"/>
-      <c r="B16" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>VLO</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>Valero Energy Corporation</t>
-        </is>
-      </c>
-      <c r="E16" s="106" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F16" s="106" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G16" s="89" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="H16" s="107" t="n">
-        <v>77190.64999999999</v>
-      </c>
-      <c r="I16" s="108" t="inlineStr">
-        <is>
-          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
+      <c r="B16" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C16" s="115" t="inlineStr">
+        <is>
+          <t>INCY</t>
+        </is>
+      </c>
+      <c r="D16" s="116" t="inlineStr">
+        <is>
+          <t>Incyte Corporation</t>
+        </is>
+      </c>
+      <c r="E16" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F16" s="117" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="G16" s="118" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="H16" s="119" t="n">
+        <v>21073.82</v>
+      </c>
+      <c r="I16" s="120" t="inlineStr">
+        <is>
+          <t>Incyte Corporation a biopharmaceutical company engages in the discovery development and commercialization of therapeutics in the United States Europe Canada and Japan</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="50" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="28" t="n"/>
-      <c r="B17" s="114" t="inlineStr">
+      <c r="B17" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>State Street Corporation</t>
-        </is>
-      </c>
-      <c r="E17" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F17" s="109" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G17" s="89" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="H17" s="110" t="n">
-        <v>44725.83</v>
-      </c>
-      <c r="I17" s="111" t="inlineStr">
-        <is>
-          <t>State Street Corporation provides various financial products and services to institutional investors</t>
+      <c r="C17" s="121" t="inlineStr">
+        <is>
+          <t>DVA</t>
+        </is>
+      </c>
+      <c r="D17" s="122" t="inlineStr">
+        <is>
+          <t>DaVita Inc.</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F17" s="123" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G17" s="118" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="H17" s="124" t="n">
+        <v>12725.72</v>
+      </c>
+      <c r="I17" s="125" t="inlineStr">
+        <is>
+          <t>DaVita Inc provides kidney dialysis services for patients suffering from chronic kidney failure in the United States</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="67" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="114" t="inlineStr">
+      <c r="B18" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>WELL</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>Welltower Inc.</t>
-        </is>
-      </c>
-      <c r="E18" s="106" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F18" s="106" t="inlineStr">
-        <is>
-          <t>Health Care REITs</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="H18" s="107" t="n">
-        <v>148209.56</v>
-      </c>
-      <c r="I18" s="108" t="inlineStr">
-        <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+      <c r="C18" s="115" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D18" s="116" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation</t>
+        </is>
+      </c>
+      <c r="E18" s="117" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F18" s="117" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G18" s="118" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="H18" s="119" t="n">
+        <v>77721.12</v>
+      </c>
+      <c r="I18" s="120" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="50" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="114" t="inlineStr">
+      <c r="B19" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>The Bank of New York Mellon Corporation</t>
-        </is>
-      </c>
-      <c r="E19" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F19" s="109" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G19" s="89" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="H19" s="110" t="n">
-        <v>96186.41</v>
-      </c>
-      <c r="I19" s="111" t="inlineStr">
-        <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+      <c r="C19" s="121" t="inlineStr">
+        <is>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="D19" s="122" t="inlineStr">
+        <is>
+          <t>Valero Energy Corporation</t>
+        </is>
+      </c>
+      <c r="E19" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F19" s="123" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G19" s="118" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="H19" s="124" t="n">
+        <v>77190.64999999999</v>
+      </c>
+      <c r="I19" s="125" t="inlineStr">
+        <is>
+          <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="84" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="114" t="inlineStr">
+      <c r="B20" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>The Travelers Companies Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="106" t="inlineStr">
+      <c r="C20" s="115" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="D20" s="116" t="inlineStr">
+        <is>
+          <t>State Street Corporation</t>
+        </is>
+      </c>
+      <c r="E20" s="117" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F20" s="106" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="H20" s="107" t="n">
-        <v>64533.41</v>
-      </c>
-      <c r="I20" s="108" t="inlineStr">
-        <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+      <c r="F20" s="117" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G20" s="118" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="H20" s="119" t="n">
+        <v>44725.83</v>
+      </c>
+      <c r="I20" s="120" t="inlineStr">
+        <is>
+          <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="50" customHeight="1">
+    <row r="21" ht="106" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="114" t="inlineStr">
+      <c r="B21" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation</t>
-        </is>
-      </c>
-      <c r="E21" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F21" s="109" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G21" s="89" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="H21" s="110" t="n">
-        <v>158667.48</v>
-      </c>
-      <c r="I21" s="111" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+      <c r="C21" s="121" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="D21" s="122" t="inlineStr">
+        <is>
+          <t>The Travelers Companies Inc.</t>
+        </is>
+      </c>
+      <c r="E21" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F21" s="123" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G21" s="118" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="H21" s="124" t="n">
+        <v>64533.41</v>
+      </c>
+      <c r="I21" s="125" t="inlineStr">
+        <is>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="33" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="114" t="inlineStr">
+      <c r="B22" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>GWW</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>W.W. Grainger Inc.</t>
-        </is>
-      </c>
-      <c r="E22" s="106" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F22" s="106" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0.307</v>
-      </c>
-      <c r="H22" s="107" t="n">
-        <v>62147.38</v>
-      </c>
-      <c r="I22" s="108" t="inlineStr">
-        <is>
-          <t>W</t>
+      <c r="C22" s="115" t="inlineStr">
+        <is>
+          <t>WELL</t>
+        </is>
+      </c>
+      <c r="D22" s="116" t="inlineStr">
+        <is>
+          <t>Welltower Inc.</t>
+        </is>
+      </c>
+      <c r="E22" s="117" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F22" s="117" t="inlineStr">
+        <is>
+          <t>Health Care REITs</t>
+        </is>
+      </c>
+      <c r="G22" s="118" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="H22" s="119" t="n">
+        <v>148209.56</v>
+      </c>
+      <c r="I22" s="120" t="inlineStr">
+        <is>
+          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="67" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="114" t="inlineStr">
+      <c r="B23" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>Archer-Daniels-Midland Company</t>
-        </is>
-      </c>
-      <c r="E23" s="109" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F23" s="109" t="inlineStr">
-        <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H23" s="110" t="n">
-        <v>39380.19</v>
-      </c>
-      <c r="I23" s="111" t="inlineStr">
-        <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+      <c r="C23" s="121" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="D23" s="122" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon Corporation</t>
+        </is>
+      </c>
+      <c r="E23" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F23" s="123" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G23" s="118" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="H23" s="124" t="n">
+        <v>96186.41</v>
+      </c>
+      <c r="I23" s="125" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="50" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="114" t="inlineStr">
+      <c r="B24" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation</t>
-        </is>
-      </c>
-      <c r="E24" s="106" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F24" s="106" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G24" s="89" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="H24" s="107" t="n">
-        <v>125211.85</v>
-      </c>
-      <c r="I24" s="108" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+      <c r="C24" s="115" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="D24" s="116" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation</t>
+        </is>
+      </c>
+      <c r="E24" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F24" s="117" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G24" s="118" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H24" s="119" t="n">
+        <v>158667.48</v>
+      </c>
+      <c r="I24" s="120" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="67" customHeight="1">
+    <row r="25" ht="88" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="114" t="inlineStr">
+      <c r="B25" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>Healthpeak Properties Inc.</t>
-        </is>
-      </c>
-      <c r="E25" s="109" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F25" s="109" t="inlineStr">
-        <is>
-          <t>Health Care REITs</t>
-        </is>
-      </c>
-      <c r="G25" s="89" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="H25" s="110" t="n">
-        <v>14353.95</v>
-      </c>
-      <c r="I25" s="111" t="inlineStr">
-        <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+      <c r="C25" s="121" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="D25" s="122" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company</t>
+        </is>
+      </c>
+      <c r="E25" s="123" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F25" s="123" t="inlineStr">
+        <is>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="G25" s="118" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="H25" s="124" t="n">
+        <v>39380.19</v>
+      </c>
+      <c r="I25" s="125" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="50" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="114" t="inlineStr">
+      <c r="B26" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="E26" s="106" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F26" s="106" t="inlineStr">
-        <is>
-          <t>Technology Hardware Storage and Peripherals</t>
-        </is>
-      </c>
-      <c r="G26" s="89" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="H26" s="107" t="n">
-        <v>4309578.68</v>
-      </c>
-      <c r="I26" s="108" t="inlineStr">
-        <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+      <c r="C26" s="115" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D26" s="116" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation</t>
+        </is>
+      </c>
+      <c r="E26" s="117" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F26" s="117" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G26" s="118" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H26" s="119" t="n">
+        <v>125211.85</v>
+      </c>
+      <c r="I26" s="120" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="67" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="114" t="inlineStr">
+      <c r="B27" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C27" s="30" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>Globe Life Inc.</t>
-        </is>
-      </c>
-      <c r="E27" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F27" s="109" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G27" s="89" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="H27" s="110" t="n">
-        <v>12644.53</v>
-      </c>
-      <c r="I27" s="111" t="inlineStr">
-        <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+      <c r="C27" s="121" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="D27" s="122" t="inlineStr">
+        <is>
+          <t>Healthpeak Properties Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="123" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F27" s="123" t="inlineStr">
+        <is>
+          <t>Health Care REITs</t>
+        </is>
+      </c>
+      <c r="G27" s="118" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H27" s="124" t="n">
+        <v>14353.95</v>
+      </c>
+      <c r="I27" s="125" t="inlineStr">
+        <is>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="84" customHeight="1">
+    <row r="28" ht="88" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="114" t="inlineStr">
+      <c r="B28" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="115" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="D28" s="39" t="inlineStr">
+      <c r="D28" s="116" t="inlineStr">
         <is>
           <t>Bank of America Corporation</t>
         </is>
       </c>
-      <c r="E28" s="106" t="inlineStr">
+      <c r="E28" s="117" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F28" s="106" t="inlineStr">
+      <c r="F28" s="117" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="G28" s="89" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="H28" s="107" t="n">
+      <c r="G28" s="118" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="H28" s="119" t="n">
         <v>388502.86</v>
       </c>
-      <c r="I28" s="108" t="inlineStr">
+      <c r="I28" s="120" t="inlineStr">
         <is>
           <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
@@ -5525,460 +5167,348 @@
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="67" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="114" t="inlineStr">
+      <c r="B29" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Principal Financial Group Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="109" t="inlineStr">
+      <c r="C29" s="121" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D29" s="122" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F29" s="109" t="inlineStr">
+      <c r="F29" s="123" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G29" s="89" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="H29" s="110" t="n">
-        <v>23624.19</v>
-      </c>
-      <c r="I29" s="111" t="inlineStr">
-        <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+      <c r="G29" s="118" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="H29" s="124" t="n">
+        <v>13320.91</v>
+      </c>
+      <c r="I29" s="125" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="50" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="114" t="inlineStr">
+      <c r="B30" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>Everest Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E30" s="106" t="inlineStr">
+      <c r="C30" s="115" t="inlineStr">
+        <is>
+          <t>PRU</t>
+        </is>
+      </c>
+      <c r="D30" s="116" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="117" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F30" s="106" t="inlineStr">
+      <c r="F30" s="117" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G30" s="89" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="H30" s="107" t="n">
-        <v>13320.91</v>
-      </c>
-      <c r="I30" s="108" t="inlineStr">
-        <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+      <c r="G30" s="118" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="H30" s="119" t="n">
+        <v>36717.82</v>
+      </c>
+      <c r="I30" s="120" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="67" customHeight="1">
+    <row r="31" ht="88" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="114" t="inlineStr">
+      <c r="B31" s="127" t="inlineStr">
         <is>
           <t>RPT</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>EXPD</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>Expeditors International of Washington Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="109" t="inlineStr">
+      <c r="C31" s="121" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="D31" s="122" t="inlineStr">
+        <is>
+          <t>Paychex Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F31" s="109" t="inlineStr">
-        <is>
-          <t>Air Freight and Logistics</t>
-        </is>
-      </c>
-      <c r="G31" s="89" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="H31" s="110" t="n">
-        <v>21453.67</v>
-      </c>
-      <c r="I31" s="111" t="inlineStr">
-        <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+      <c r="F31" s="123" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="G31" s="118" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="H31" s="124" t="n">
+        <v>36258.68</v>
+      </c>
+      <c r="I31" s="125" t="inlineStr">
+        <is>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="67" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C32" s="38" t="inlineStr">
-        <is>
-          <t>PRU</t>
-        </is>
-      </c>
-      <c r="D32" s="39" t="inlineStr">
-        <is>
-          <t>Prudential Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E32" s="106" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F32" s="106" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G32" s="89" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="H32" s="107" t="n">
-        <v>36717.82</v>
-      </c>
-      <c r="I32" s="108" t="inlineStr">
-        <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+      <c r="B32" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C32" s="115" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D32" s="116" t="inlineStr">
+        <is>
+          <t>CSX Corporation</t>
+        </is>
+      </c>
+      <c r="E32" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F32" s="117" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G32" s="118" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H32" s="119" t="n">
+        <v>86617.14</v>
+      </c>
+      <c r="I32" s="120" t="inlineStr">
+        <is>
+          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="84" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="114" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>Paychex Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F33" s="109" t="inlineStr">
-        <is>
-          <t>Professional Services</t>
-        </is>
-      </c>
-      <c r="G33" s="89" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="H33" s="110" t="n">
-        <v>36258.68</v>
-      </c>
-      <c r="I33" s="111" t="inlineStr">
-        <is>
-          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
+      <c r="B33" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C33" s="121" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D33" s="122" t="inlineStr">
+        <is>
+          <t>The Allstate Corporation</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F33" s="123" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G33" s="118" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="H33" s="124" t="n">
+        <v>57507.32</v>
+      </c>
+      <c r="I33" s="125" t="inlineStr">
+        <is>
+          <t>The Allstate Corporation together with its subsidiaries provides property and casualty and other insurance products in the United States and Canada</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="50" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="115" t="inlineStr">
+      <c r="B34" s="129" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="C34" s="38" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>Palo Alto Networks Inc.</t>
-        </is>
-      </c>
-      <c r="E34" s="106" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F34" s="106" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="G34" s="89" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="H34" s="107" t="n">
-        <v>213908.98</v>
-      </c>
-      <c r="I34" s="108" t="inlineStr">
-        <is>
-          <t>Palo Alto Networks Inc provides cybersecurity solutions in the Americas Europe the Middle East Africa the Asia Pacific and Japan</t>
+      <c r="C34" s="130" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="D34" s="131" t="inlineStr">
+        <is>
+          <t>Best Buy Co. Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="132" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F34" s="132" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G34" s="133" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="H34" s="134" t="n">
+        <v>16078.79</v>
+      </c>
+      <c r="I34" s="135" t="inlineStr">
+        <is>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="50" customHeight="1">
+    <row r="35" ht="8" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>CSX</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>CSX Corporation</t>
-        </is>
-      </c>
-      <c r="E35" s="109" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F35" s="109" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G35" s="89" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="H35" s="110" t="n">
-        <v>86617.14</v>
-      </c>
-      <c r="I35" s="111" t="inlineStr">
-        <is>
-          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
-        </is>
-      </c>
+      <c r="B35" s="136" t="n"/>
+      <c r="C35" s="137" t="n"/>
+      <c r="D35" s="138" t="n"/>
+      <c r="E35" s="139" t="n"/>
+      <c r="F35" s="139" t="n"/>
+      <c r="G35" s="140" t="n"/>
+      <c r="H35" s="141" t="n"/>
+      <c r="I35" s="142" t="n"/>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="67" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>The Allstate Corporation</t>
-        </is>
-      </c>
-      <c r="E36" s="106" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F36" s="106" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G36" s="89" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="H36" s="107" t="n">
-        <v>57507.32</v>
-      </c>
-      <c r="I36" s="108" t="inlineStr">
-        <is>
-          <t>The Allstate Corporation together with its subsidiaries provides property and casualty and other insurance products in the United States and Canada</t>
-        </is>
-      </c>
+      <c r="B36" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C36" s="144" t="n"/>
+      <c r="D36" s="144" t="n"/>
+      <c r="E36" s="144" t="n"/>
+      <c r="F36" s="144" t="n"/>
+      <c r="G36" s="144" t="n"/>
+      <c r="H36" s="144" t="n"/>
+      <c r="I36" s="144" t="n"/>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="33" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="115" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>BBY</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>Best Buy Co. Inc.</t>
-        </is>
-      </c>
-      <c r="E37" s="109" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F37" s="109" t="inlineStr">
-        <is>
-          <t>Specialty Retail</t>
-        </is>
-      </c>
-      <c r="G37" s="89" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="H37" s="110" t="n">
-        <v>16078.79</v>
-      </c>
-      <c r="I37" s="111" t="inlineStr">
-        <is>
-          <t>Best Buy Co</t>
-        </is>
-      </c>
+      <c r="B37" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C37" s="146" t="n"/>
+      <c r="D37" s="146" t="n"/>
+      <c r="E37" s="146" t="n"/>
+      <c r="F37" s="146" t="n"/>
+      <c r="G37" s="146" t="n"/>
+      <c r="H37" s="146" t="n"/>
+      <c r="I37" s="146" t="n"/>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="50" customHeight="1">
+    <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="116" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C38" s="134" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="D38" s="135" t="inlineStr">
-        <is>
-          <t>MetLife Inc.</t>
-        </is>
-      </c>
-      <c r="E38" s="136" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F38" s="136" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G38" s="120" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="H38" s="137" t="n">
-        <v>55851.6</v>
-      </c>
-      <c r="I38" s="138" t="inlineStr">
-        <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
-        </is>
-      </c>
+      <c r="B38" s="48" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="40" t="n"/>
+      <c r="F38" s="40" t="n"/>
+      <c r="G38" s="89" t="n"/>
+      <c r="H38" s="91" t="n"/>
+      <c r="I38" s="53" t="n"/>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="8" customHeight="1">
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="123" t="n"/>
-      <c r="C39" s="124" t="n"/>
-      <c r="D39" s="125" t="n"/>
-      <c r="E39" s="126" t="n"/>
-      <c r="F39" s="126" t="n"/>
-      <c r="G39" s="127" t="n"/>
-      <c r="H39" s="128" t="n"/>
-      <c r="I39" s="129" t="n"/>
+      <c r="B39" s="49" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="89" t="n"/>
+      <c r="H39" s="93" t="n"/>
+      <c r="I39" s="54" t="n"/>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="34" customHeight="1">
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="130" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C40" s="131" t="n"/>
-      <c r="D40" s="131" t="n"/>
-      <c r="E40" s="131" t="n"/>
-      <c r="F40" s="131" t="n"/>
-      <c r="G40" s="131" t="n"/>
-      <c r="H40" s="131" t="n"/>
-      <c r="I40" s="131" t="n"/>
+      <c r="B40" s="48" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="89" t="n"/>
+      <c r="H40" s="91" t="n"/>
+      <c r="I40" s="53" t="n"/>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="28" customHeight="1">
+    <row r="41" ht="30.6" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="132" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C41" s="133" t="n"/>
-      <c r="D41" s="133" t="n"/>
-      <c r="E41" s="133" t="n"/>
-      <c r="F41" s="133" t="n"/>
-      <c r="G41" s="133" t="n"/>
-      <c r="H41" s="133" t="n"/>
-      <c r="I41" s="133" t="n"/>
+      <c r="B41" s="49" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="89" t="n"/>
+      <c r="H41" s="93" t="n"/>
+      <c r="I41" s="54" t="n"/>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
@@ -6090,11 +5620,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B40:I40"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G38">
+  <conditionalFormatting sqref="G8:G34">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_latest.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -383,7 +383,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -558,11 +558,35 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -963,6 +987,7 @@
     <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2086,7 +2111,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46230.56563682047</v>
+        <v>46230.8070455554</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2148,7 +2173,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46230.56563682047</v>
+        <v>46230.8070455554</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2281,10 +2306,10 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.441</v>
+        <v>0.409</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>7850.04</v>
+        <v>7816.25</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
@@ -2322,10 +2347,10 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.271</v>
+        <v>0.162</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>2215.94</v>
+        <v>2145.48</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
@@ -2363,10 +2388,10 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.773</v>
+        <v>0.761</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>1565.38</v>
+        <v>1924.02</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
@@ -2404,10 +2429,10 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.481</v>
+        <v>0.434</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>2385.76</v>
+        <v>2667.47</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
@@ -2445,10 +2470,10 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.382</v>
+        <v>0.375</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>38174.66</v>
+        <v>40943.84</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
@@ -2467,39 +2492,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.292</v>
+        <v>0.276</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>681.6799999999999</v>
+        <v>29189.48</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="127" t="inlineStr">
         <is>
@@ -2508,39 +2533,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation</t>
+          <t>Canadian Utilities Limited</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.286</v>
+        <v>0.276</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>28518.97</v>
+        <v>10629.48</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="127" t="inlineStr">
         <is>
@@ -2549,33 +2574,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.274</v>
+        <v>0.264</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>10045.65</v>
+        <v>845.1</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2609,10 +2634,10 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.257</v>
+        <v>0.239</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>576.85</v>
+        <v>703.8</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
@@ -2622,7 +2647,7 @@
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="88" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="127" t="inlineStr">
         <is>
@@ -2631,39 +2656,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>TOY</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Spin Master Corp.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.236</v>
+        <v>0.23</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>65572.44</v>
+        <v>1621.94</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="88" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="127" t="inlineStr">
         <is>
@@ -2672,33 +2697,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>TOY</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Spin Master Corp.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.236</v>
+        <v>0.217</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>1330.28</v>
+        <v>73319.98</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
@@ -2732,10 +2757,10 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>1.263</v>
+        <v>1.252</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>284.57</v>
+        <v>365.09</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
@@ -2773,10 +2798,10 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.538</v>
+        <v>0.54</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>1892.54</v>
+        <v>2189.94</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
@@ -2786,7 +2811,7 @@
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="124" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="128" t="inlineStr">
         <is>
@@ -2795,39 +2820,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc.</t>
+          <t>Sun Life Financial Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.419</v>
+        <v>0.39</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>390.27</v>
+        <v>46289</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="124" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="128" t="inlineStr">
         <is>
@@ -2836,39 +2861,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc.</t>
+          <t>Canadian National Railway Company</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.393</v>
+        <v>0.356</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>41467.31</v>
+        <v>78116.71000000001</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="129" t="inlineStr">
         <is>
@@ -2877,33 +2902,33 @@
       </c>
       <c r="C23" s="130" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>DFY</t>
         </is>
       </c>
       <c r="D23" s="131" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company</t>
+          <t>Definity Financial Corporation</t>
         </is>
       </c>
       <c r="E23" s="132" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="132" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G23" s="133" t="n">
-        <v>0.38</v>
+        <v>0.197</v>
       </c>
       <c r="H23" s="134" t="n">
-        <v>72839.50999999999</v>
+        <v>6877.44</v>
       </c>
       <c r="I23" s="135" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
+          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -4244,7 +4269,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46230.56563682047</v>
+        <v>46230.8070455554</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4377,10 +4402,10 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.415</v>
+        <v>0.399</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>16769.06</v>
+        <v>17248.28</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
@@ -4418,10 +4443,10 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.401</v>
+        <v>0.377</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>100601.02</v>
+        <v>114863.66</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
@@ -4431,7 +4456,7 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="88" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4440,33 +4465,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Ventas Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.335</v>
+        <v>0.374</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>41077.71</v>
+        <v>20595.11</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Ventas Inc is a leading S&amp;P 500 real estate investment trust enabling exceptional environments that benefit a large and growing aging population</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -4500,10 +4525,10 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>57507.32</v>
+        <v>67232.17</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
@@ -4513,7 +4538,7 @@
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4522,39 +4547,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Westinghouse Air Brake Technologies Corporation</t>
+          <t>Ventas Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.326</v>
+        <v>0.317</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>43435.03</v>
+        <v>49034.35</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Westinghouse Air Brake Technologies Corporation provides locomotives equipment systems and services for the freight rail and passenger transit industries worldwide</t>
+          <t>Ventas Inc is an S&amp;P 500 company enabling exceptional environments that benefit a large and growing aging population</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="106" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4563,12 +4588,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -4582,14 +4607,14 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.289</v>
+        <v>0.308</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>10799.18</v>
+        <v>17903.06</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust is a recognized leader in the ownership operation and redevelopment of high-quality retail-based properties located primarily in major coastal markets and select underserved regions with strong economic and demographic fundamentals</t>
+          <t>Kimco Realty Corporation is a real estate investment trust (REIT) and leading owner and operator of high-quality open-air grocery-anchored shopping centers and mixed-use properties in the United States</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4604,33 +4629,33 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Norfolk Southern Corporation</t>
+          <t>Federal Realty Investment Trust</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Retail REITs</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.233</v>
+        <v>0.292</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>69486.00999999999</v>
+        <v>11052.19</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Norfolk Southern Corporation together with its subsidiaries engages in the rail transportation of raw materials intermediate products and finished goods in the United States</t>
+          <t>Federal Realty Investment Trust is a recognized leader in the ownership operation and redevelopment of high-quality retail-based properties</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -4645,33 +4670,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Westinghouse Air Brake Technologies Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.215</v>
+        <v>0.292</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>398482.45</v>
+        <v>50386.28</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>Westinghouse Air Brake Technologies Corporation provides locomotives equipment systems and services for the freight rail and passenger transit industries worldwide</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -4686,39 +4711,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Quest Diagnostics Incorporated</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.203</v>
+        <v>0.279</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>834204.25</v>
+        <v>25502.21</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Quest Diagnostics Incorporated provides diagnostic testing and services in the United States</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -4727,33 +4752,33 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Simon Property Group Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Retail REITs</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.182</v>
+        <v>0.245</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>21073.82</v>
+        <v>87858.7</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Incyte Corporation a biopharmaceutical company engages in the discovery development and commercialization of therapeutics in the United States Europe Canada and Japan</t>
+          <t>Simon Property Group Inc is a self-administered and self-managed real estate investment trust (REIT)</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
@@ -4761,101 +4786,101 @@
     </row>
     <row r="18" ht="70" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Norfolk Southern Corporation</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.191</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>77721.12</v>
+        <v>76545.41</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Norfolk Southern Corporation together with its subsidiaries engages in the rail transportation of raw materials intermediate products and finished goods in the United States</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.475</v>
+        <v>0.189</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>44725.83</v>
+        <v>455592.26</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>State Street Corporation provides various financial products and services to institutional investors</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
@@ -4865,38 +4890,38 @@
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.46</v>
+        <v>0.178</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>125211.85</v>
+        <v>23859.58</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>Incyte Corporation a biopharmaceutical company engages in the discovery development and commercialization of therapeutics in the United States Europe Canada and Japan</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="106" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc.</t>
+          <t>Assurant Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -4910,61 +4935,61 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.39</v>
+        <v>0.173</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>64533.41</v>
+        <v>13786.88</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+          <t>Assurant Inc provides protection services to connected devices homes and automobiles in North America Latin America Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B22" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.37</v>
+        <v>0.171</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>148209.56</v>
+        <v>945144.28</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="34" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -4973,33 +4998,33 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>DaVita Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.357</v>
+        <v>1.203</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>16078.79</v>
+        <v>15188.76</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>DaVita Inc provides kidney dialysis services for patients suffering from chronic kidney failure in the United States</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -5014,39 +5039,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.351</v>
+        <v>0.797</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>96186.41</v>
+        <v>91152.84</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -5055,39 +5080,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>158667.48</v>
+        <v>137372.71</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -5096,39 +5121,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.345</v>
+        <v>0.415</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>14353.95</v>
+        <v>50462.03</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -5137,39 +5162,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.311</v>
+        <v>0.401</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>4309578.68</v>
+        <v>18710.64</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="88" customHeight="1">
+    <row r="28" ht="106" customHeight="1">
       <c r="A28" s="36" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -5178,39 +5203,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>The Travelers Companies Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.26</v>
+        <v>0.382</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>39380.19</v>
+        <v>81399.95</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="88" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -5219,33 +5244,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.225</v>
+        <v>0.355</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>388502.86</v>
+        <v>15755.27</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+          <t>Healthpeak Properties Inc is a fully integrated real estate investment trust (REIT) and S&amp;P 500 company</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5260,33 +5285,33 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Everest Group Ltd.</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.21</v>
+        <v>0.353</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>13320.91</v>
+        <v>176578.15</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+          <t>Welltower Inc an S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -5301,12 +5326,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc.</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -5316,24 +5341,24 @@
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.157</v>
+        <v>0.306</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>36717.82</v>
+        <v>107234.16</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="34" customHeight="1">
+    <row r="32" ht="52" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="127" t="inlineStr">
         <is>
@@ -5342,33 +5367,33 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Invesco Ltd.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.127</v>
+        <v>0.302</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>12167.61</v>
+        <v>4930986.03</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Invesco Ltd is a publicly owned investment manager</t>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -5376,19 +5401,19 @@
     </row>
     <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -5402,234 +5427,514 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.41</v>
+        <v>0.294</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>86617.14</v>
+        <v>176506.37</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C34" s="147" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="D34" s="148" t="inlineStr">
-        <is>
-          <t>MetLife Inc.</t>
-        </is>
-      </c>
-      <c r="E34" s="149" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F34" s="149" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G34" s="133" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="H34" s="150" t="n">
-        <v>55851.6</v>
-      </c>
-      <c r="I34" s="151" t="inlineStr">
-        <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+      <c r="B34" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C34" s="115" t="inlineStr">
+        <is>
+          <t>GWW</t>
+        </is>
+      </c>
+      <c r="D34" s="116" t="inlineStr">
+        <is>
+          <t>W.W. Grainger Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F34" s="117" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G34" s="118" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H34" s="119" t="n">
+        <v>65761.08</v>
+      </c>
+      <c r="I34" s="120" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="8" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="136" t="n"/>
-      <c r="C35" s="137" t="n"/>
-      <c r="D35" s="138" t="n"/>
-      <c r="E35" s="139" t="n"/>
-      <c r="F35" s="139" t="n"/>
-      <c r="G35" s="140" t="n"/>
-      <c r="H35" s="141" t="n"/>
-      <c r="I35" s="142" t="n"/>
+      <c r="B35" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C35" s="121" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="D35" s="122" t="inlineStr">
+        <is>
+          <t>Block Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F35" s="123" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G35" s="118" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H35" s="124" t="n">
+        <v>48278.54</v>
+      </c>
+      <c r="I35" s="125" t="inlineStr">
+        <is>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+        </is>
+      </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="88" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C36" s="144" t="n"/>
-      <c r="D36" s="144" t="n"/>
-      <c r="E36" s="144" t="n"/>
-      <c r="F36" s="144" t="n"/>
-      <c r="G36" s="144" t="n"/>
-      <c r="H36" s="144" t="n"/>
-      <c r="I36" s="144" t="n"/>
+      <c r="B36" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C36" s="115" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="D36" s="116" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company</t>
+        </is>
+      </c>
+      <c r="E36" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F36" s="117" t="inlineStr">
+        <is>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="G36" s="118" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H36" s="119" t="n">
+        <v>40086.25</v>
+      </c>
+      <c r="I36" s="120" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+        </is>
+      </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="28" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C37" s="146" t="n"/>
-      <c r="D37" s="146" t="n"/>
-      <c r="E37" s="146" t="n"/>
-      <c r="F37" s="146" t="n"/>
-      <c r="G37" s="146" t="n"/>
-      <c r="H37" s="146" t="n"/>
-      <c r="I37" s="146" t="n"/>
+      <c r="B37" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C37" s="121" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D37" s="122" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F37" s="123" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G37" s="118" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="H37" s="124" t="n">
+        <v>15393</v>
+      </c>
+      <c r="I37" s="125" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+        </is>
+      </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="20.4" customHeight="1">
+    <row r="38" ht="88" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="39" t="n"/>
-      <c r="E38" s="40" t="n"/>
-      <c r="F38" s="40" t="n"/>
-      <c r="G38" s="89" t="n"/>
-      <c r="H38" s="91" t="n"/>
-      <c r="I38" s="53" t="n"/>
+      <c r="B38" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C38" s="115" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D38" s="116" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation</t>
+        </is>
+      </c>
+      <c r="E38" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F38" s="117" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G38" s="118" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="H38" s="119" t="n">
+        <v>436335.11</v>
+      </c>
+      <c r="I38" s="120" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+        </is>
+      </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1">
+    <row r="39" ht="106" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="31" t="n"/>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="89" t="n"/>
-      <c r="H39" s="93" t="n"/>
-      <c r="I39" s="54" t="n"/>
+      <c r="B39" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C39" s="121" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="D39" s="122" t="inlineStr">
+        <is>
+          <t>Paychex Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="123" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F39" s="123" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="G39" s="118" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="H39" s="124" t="n">
+        <v>41283.4</v>
+      </c>
+      <c r="I39" s="125" t="inlineStr">
+        <is>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for human resources payroll processing employee benefits and insurance services for small to medium-sized businesses in the United States Europe Canada India and Israel</t>
+        </is>
+      </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="24" customHeight="1">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="40" t="n"/>
-      <c r="F40" s="40" t="n"/>
-      <c r="G40" s="89" t="n"/>
-      <c r="H40" s="91" t="n"/>
-      <c r="I40" s="53" t="n"/>
+      <c r="B40" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C40" s="115" t="inlineStr">
+        <is>
+          <t>PRU</t>
+        </is>
+      </c>
+      <c r="D40" s="116" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E40" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F40" s="117" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G40" s="118" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="H40" s="119" t="n">
+        <v>42168.74</v>
+      </c>
+      <c r="I40" s="120" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+        </is>
+      </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="30.6" customHeight="1">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="93" t="n"/>
-      <c r="I41" s="54" t="n"/>
+      <c r="B41" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C41" s="121" t="inlineStr">
+        <is>
+          <t>IVZ</t>
+        </is>
+      </c>
+      <c r="D41" s="122" t="inlineStr">
+        <is>
+          <t>Invesco Ltd.</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F41" s="123" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G41" s="118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="124" t="n">
+        <v>13256.34</v>
+      </c>
+      <c r="I41" s="125" t="inlineStr">
+        <is>
+          <t>Invesco Ltd is a publicly owned investment manager</t>
+        </is>
+      </c>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="24.6" customHeight="1" thickBot="1">
+    <row r="42" ht="52" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="76" t="n"/>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="78" t="n"/>
-      <c r="E42" s="79" t="n"/>
-      <c r="F42" s="79" t="n"/>
-      <c r="G42" s="94" t="n"/>
-      <c r="H42" s="105" t="n"/>
-      <c r="I42" s="81" t="n"/>
+      <c r="B42" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D42" s="116" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E42" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F42" s="117" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G42" s="118" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="H42" s="119" t="n">
+        <v>682683.01</v>
+      </c>
+      <c r="I42" s="120" t="inlineStr">
+        <is>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+        </is>
+      </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C43" s="121" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D43" s="122" t="inlineStr">
+        <is>
+          <t>CSX Corporation</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F43" s="123" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G43" s="118" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="H43" s="124" t="n">
+        <v>95620</v>
+      </c>
+      <c r="I43" s="125" t="inlineStr">
+        <is>
+          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+        </is>
+      </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="15.6" customHeight="1" thickBot="1">
+    <row r="44" ht="70" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="43" t="n"/>
-      <c r="E44" s="43" t="n"/>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="43" t="n"/>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="43" t="n"/>
+      <c r="B44" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C44" s="147" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="D44" s="148" t="inlineStr">
+        <is>
+          <t>MetLife Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="149" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F44" s="149" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G44" s="133" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="H44" s="150" t="n">
+        <v>61293.14</v>
+      </c>
+      <c r="I44" s="151" t="inlineStr">
+        <is>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+        </is>
+      </c>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="10.2" customHeight="1">
+    <row r="45" ht="8" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="58" t="n"/>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
-      <c r="G45" s="59" t="n"/>
-      <c r="H45" s="59" t="n"/>
-      <c r="I45" s="60" t="n"/>
+      <c r="B45" s="152" t="n"/>
+      <c r="C45" s="152" t="n"/>
+      <c r="D45" s="152" t="n"/>
+      <c r="E45" s="152" t="n"/>
+      <c r="F45" s="152" t="n"/>
+      <c r="G45" s="152" t="n"/>
+      <c r="H45" s="152" t="n"/>
+      <c r="I45" s="152" t="n"/>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="34" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="67" t="n"/>
-      <c r="C46" s="64" t="n"/>
-      <c r="D46" s="64" t="n"/>
-      <c r="E46" s="64" t="n"/>
-      <c r="F46" s="64" t="n"/>
-      <c r="G46" s="64" t="n"/>
-      <c r="H46" s="64" t="n"/>
-      <c r="I46" s="65" t="n"/>
+      <c r="B46" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C46" s="144" t="n"/>
+      <c r="D46" s="144" t="n"/>
+      <c r="E46" s="144" t="n"/>
+      <c r="F46" s="144" t="n"/>
+      <c r="G46" s="144" t="n"/>
+      <c r="H46" s="144" t="n"/>
+      <c r="I46" s="144" t="n"/>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="10.8" customHeight="1" thickBot="1">
+    <row r="47" ht="28" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="62" t="n"/>
-      <c r="D47" s="62" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="62" t="n"/>
-      <c r="G47" s="62" t="n"/>
-      <c r="H47" s="62" t="n"/>
-      <c r="I47" s="63" t="n"/>
+      <c r="B47" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C47" s="146" t="n"/>
+      <c r="D47" s="146" t="n"/>
+      <c r="E47" s="146" t="n"/>
+      <c r="F47" s="146" t="n"/>
+      <c r="G47" s="146" t="n"/>
+      <c r="H47" s="146" t="n"/>
+      <c r="I47" s="146" t="n"/>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
@@ -5663,11 +5968,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G34">
+  <conditionalFormatting sqref="G8:G44">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>
